--- a/workspaces/nasdaq_hourly_24hrs/macd/macd_6_13.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/macd/macd_6_13.xlsx
@@ -625,76 +625,76 @@
         <v>23</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-10.12607627304119</v>
+        <v>-10.09311771823484</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.815267659224808</v>
+        <v>6.848768889108314</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.707003282104012</v>
+        <v>9.742205153282164</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.000467107176625</v>
+        <v>9.036505106992465</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.640004611171079</v>
+        <v>8.70535654183486</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.504606541138507</v>
+        <v>4.569750520629775</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.5886506505381561</v>
+        <v>-0.52260696943911</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-5.19334980298563</v>
+        <v>-5.126970039033253</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.825265206787904</v>
+        <v>-0.7588685392269738</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.596168958137618</v>
+        <v>-1.528839662723286</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.654517635095829</v>
+        <v>-5.587484012506742</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.729933916330069</v>
+        <v>2.797369846755551</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.27717858750004</v>
+        <v>10.34598816130282</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.389637938996948</v>
+        <v>1.458710724617767</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>9.405510590440137</v>
+        <v>9.475414722849827</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.664404707485311</v>
+        <v>5.733644940518289</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>5.532706663125239</v>
+        <v>5.602140874103583</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>1.089447372643463</v>
+        <v>1.159033963827554</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-7.376998374977852</v>
+        <v>-7.307637655376787</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>1.492769903267757</v>
+        <v>1.561969658795356</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.9505172056621376</v>
+        <v>1.020390628523337</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-3.470323706172287</v>
+        <v>-3.400323392290893</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-7.543216741588232</v>
+        <v>-7.473495517584439</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-3.27358250699212</v>
+        <v>-3.203728159284843</v>
       </c>
     </row>
     <row r="7">
@@ -707,76 +707,76 @@
         <v>18</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.385953566235827</v>
+        <v>7.41905306691244</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.535790766422096</v>
+        <v>1.569248478917835</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.625855141680667</v>
+        <v>5.661024994006411</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.91818274889156</v>
+        <v>4.954190044519905</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>15.60424851730707</v>
+        <v>15.66964520733933</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.27005702852291</v>
+        <v>10.33523493607431</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15.03164910746498</v>
+        <v>15.09778478800876</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>14.75882415596264</v>
+        <v>14.82531502077916</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>14.80443544880571</v>
+        <v>14.87091335157398</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.506113228689209</v>
+        <v>8.573490123939735</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.247986515316633</v>
+        <v>3.315058240865397</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.970480641396854</v>
+        <v>3.037914876005964</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>12.92496080223717</v>
+        <v>12.99377912119559</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>18.24686399968181</v>
+        <v>18.3159956088783</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>17.59548559682846</v>
+        <v>17.66541491873402</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>12.65217462052535</v>
+        <v>12.72143351266371</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>23.61027572278434</v>
+        <v>23.67975448289376</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>12.42153865722008</v>
+        <v>12.49114847582733</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>29.28273811846872</v>
+        <v>29.35216393355238</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>23.92940202635272</v>
+        <v>23.99863347456487</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>23.39393335780229</v>
+        <v>23.463830542112</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>23.32510582563548</v>
+        <v>23.39512507715681</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>23.60682053731383</v>
+        <v>23.67655278590298</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>23.53801169590644</v>
+        <v>23.60786604361372</v>
       </c>
     </row>
     <row r="8">
@@ -789,76 +789,76 @@
         <v>23</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-14.44261911457904</v>
+        <v>-14.40970536557542</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.495420935054995</v>
+        <v>2.528883895507114</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.255056784044179</v>
+        <v>-3.219957195000013</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.677724025907665</v>
+        <v>4.713727699676298</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.315721591420768</v>
+        <v>4.381037359927689</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>21.80042334109224</v>
+        <v>21.86567473967308</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>16.71281745279149</v>
+        <v>16.77896162803111</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>16.44057260598538</v>
+        <v>16.50707141496663</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>16.48674406018166</v>
+        <v>16.55322942921374</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>15.72131103676519</v>
+        <v>15.78872257603463</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>15.99932740263193</v>
+        <v>16.06645721567023</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>15.72570647873026</v>
+        <v>15.79319433719861</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.942953946713509</v>
+        <v>6.011742359403904</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.389242469238518</v>
+        <v>1.458310955498945</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>5.068797437920985</v>
+        <v>5.138684215183737</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>5.663965669102886</v>
+        <v>5.73320274211234</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.193624042795143</v>
+        <v>1.263044530174625</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.089286377917844</v>
+        <v>1.158870168495888</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>5.64664427085085</v>
+        <v>5.716026441656545</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>5.835118333594309</v>
+        <v>5.904322855690722</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>5.294246235768206</v>
+        <v>5.364123190400967</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>5.220004456512235</v>
+        <v>5.290010210413605</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.496299283762433</v>
+        <v>5.566024783678486</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>5.422069666919931</v>
+        <v>5.491924014627209</v>
       </c>
     </row>
     <row r="9">
@@ -871,76 +871,76 @@
         <v>41</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.250836463424115</v>
+        <v>7.283928581754758</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11.76418502035612</v>
+        <v>11.797721079282</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.33714879730503</v>
+        <v>10.37235045000958</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12.05481553026571</v>
+        <v>12.09087178569597</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>11.69513658794739</v>
+        <v>11.76049883737382</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>14.31043808369017</v>
+        <v>14.3756371588191</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>13.54635993617183</v>
+        <v>13.61248103867209</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8.419146060589952</v>
+        <v>8.485593747117989</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6.035143748344865</v>
+        <v>6.101567438948599</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.4095695626627531</v>
+        <v>0.4768975851825914</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.746335783001022</v>
+        <v>-1.679295416446607</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.264826632476911</v>
+        <v>5.332264877935046</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.576667979020932</v>
+        <v>6.645455368365312</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.926394521344456</v>
+        <v>3.995468607138363</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>8.135301951771801</v>
+        <v>8.205195994385569</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>8.731414690678598</v>
+        <v>8.800658331780326</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>6.166938037766144</v>
+        <v>6.236368836663686</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>6.064142390748955</v>
+        <v>6.133735006372007</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>8.717034796644661</v>
+        <v>8.786421059581791</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>4.034436732049699</v>
+        <v>4.103637171430321</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.493056271748145</v>
+        <v>3.562930125410944</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>8.29333875394402</v>
+        <v>8.363346128921471</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>11.00888327731524</v>
+        <v>11.07861051925585</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>8.49736128940291</v>
+        <v>8.567215637110742</v>
       </c>
     </row>
     <row r="10">
@@ -953,404 +953,404 @@
         <v>37</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>13.79466126844629</v>
+        <v>10.95512660261584</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.727288831577525</v>
+        <v>1.318152225514766</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.072501271143459</v>
+        <v>-4.037417906812948</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5885278058065779</v>
+        <v>0.6244945852631361</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-5.148157378127728</v>
+        <v>-5.082923962648081</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.276131003201712</v>
+        <v>-2.211051342457239</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-5.733598511930438</v>
+        <v>-5.667608283752841</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-11.39082013414082</v>
+        <v>-11.32450047972114</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-8.662835553059978</v>
+        <v>-8.596502963348989</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-4.05354821728141</v>
+        <v>-3.986251463569623</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.089645249436813</v>
+        <v>-1.022608694332618</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.368741396139221</v>
+        <v>-1.301338930719332</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.897222045827398</v>
+        <v>2.965989337295483</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.677497897366536</v>
+        <v>2.746562609345141</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2.021363742378291</v>
+        <v>2.091233035336309</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>2.615601495756891</v>
+        <v>2.684823258308924</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>2.483148315091519</v>
+        <v>2.552566182223281</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>2.379259932852804</v>
+        <v>2.448841433474058</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>10.69121545843819</v>
+        <v>10.76060367497698</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>10.881411809353</v>
+        <v>10.95062103107502</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>10.34220723045491</v>
+        <v>10.41208762789145</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>10.26956829796686</v>
+        <v>10.33957643208013</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>15.95122777915733</v>
+        <v>16.02095660475932</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>13.17765133554607</v>
+        <v>13.24750568325212</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.005795</t>
+          <t>X ≈ -0.005796</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>43</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-10.65984144269518</v>
+        <v>-10.80284125713131</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.828580121822291</v>
+        <v>-4.214059573753119</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.671584277788142</v>
+        <v>1.190687609844829</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.584454323400855</v>
+        <v>6.35514741143524</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>10.84708155262233</v>
+        <v>9.616609857801421</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.411391159823452</v>
+        <v>6.476522542791287</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.332215101714752</v>
+        <v>3.398255426981073</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.056740305849146</v>
+        <v>3.123139430377641</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7842852047788611</v>
+        <v>0.8506633704950985</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.645060713476362</v>
+        <v>4.712396974339264</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.60364705167045</v>
+        <v>2.670695254591728</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.959313179415616</v>
+        <v>7.026748451212001</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8.158361034078517</v>
+        <v>8.227145807518632</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.65096063843162</v>
+        <v>-3.58192613676016</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-4.309017530998929</v>
+        <v>-4.239175619815668</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-6.036514769001663</v>
+        <v>-5.96732459376949</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.530751586551432</v>
+        <v>-1.461348524267194</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.635877767400629</v>
+        <v>-1.566308990366572</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.742735917400729</v>
+        <v>-3.673378199630442</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.088280511872696</v>
+        <v>1.157472738169815</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.5460865152127852</v>
+        <v>0.615954107410694</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>7.442778789211665</v>
+        <v>7.512783932246457</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>5.395037358515758</v>
+        <v>5.464761725073259</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>5.320957432340542</v>
+        <v>5.390811780048345</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.005205</t>
+          <t>X ≈ -0.005206</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>58</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-10.4964033490692</v>
+        <v>-10.47663265326329</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-21.10281330033057</v>
+        <v>-21.0960244608826</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-13.97676731769006</v>
+        <v>-13.95481220446061</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-14.69143459551037</v>
+        <v>-14.66469961228806</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-23.62757395858493</v>
+        <v>-23.56979999977139</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-14.87794706650641</v>
+        <v>-14.81298273198298</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-13.93562400571098</v>
+        <v>-13.86971498114822</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-14.21652670627958</v>
+        <v>-14.15025147971546</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-19.32729616088231</v>
+        <v>-19.26105257292419</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-16.6709908298071</v>
+        <v>-16.60378592443219</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-12.96910972723608</v>
+        <v>-12.90215342799895</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-6.382213032296583</v>
+        <v>-6.314850188827393</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-7.504888415047965</v>
+        <v>-7.436180376598408</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-11.1645422207834</v>
+        <v>-11.09554700137566</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-8.386661960087409</v>
+        <v>-8.316842899952647</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-9.515470469740102</v>
+        <v>-9.446298928677876</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-9.651901446683887</v>
+        <v>-9.582527350035697</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-8.038824313289929</v>
+        <v>-7.969276152708105</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-7.825808824189096</v>
+        <v>-7.756463733327642</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-7.641522225332331</v>
+        <v>-7.572347267329064</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-6.464014346529574</v>
+        <v>-6.394157646842778</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-9.988025028445172</v>
+        <v>-9.918035403853743</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-9.716440078461652</v>
+        <v>-9.646722559617857</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-9.795321637426902</v>
+        <v>-9.725467289719624</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.004615</t>
+          <t>X ≈ -0.004616</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>67</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.021822044785452</v>
+        <v>3.058818966179501</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.207124095875756</v>
+        <v>1.242153391896792</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-9.117160106307139</v>
+        <v>-9.090953323320377</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-6.864704776506336</v>
+        <v>-6.833183021302702</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-7.229088753684529</v>
+        <v>-7.166157235905892</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.111424364904671</v>
+        <v>-1.04637893124945</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.847998445426391</v>
+        <v>-4.782046785261961</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.610749968852261</v>
+        <v>-6.544445120788502</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.600758920820255</v>
+        <v>-3.534437803896104</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.401126358661806</v>
+        <v>-1.333850736513561</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.614876315539419</v>
+        <v>-2.547880130268304</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.408613007516728</v>
+        <v>-1.341238321416959</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.529584399610386</v>
+        <v>-2.460866088783959</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.200356497894795</v>
+        <v>3.269400119864017</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-3.408156331154103</v>
+        <v>-3.33832933744592</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-4.304328023743828</v>
+        <v>-4.235148855622334</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.460926020898881</v>
+        <v>-1.391536360095749</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.56615284075162</v>
+        <v>-1.496595475041651</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.1389474094760956</v>
+        <v>0.2083034787276361</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>3.30688985297504</v>
+        <v>3.376078796160733</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.765414899451628</v>
+        <v>2.835279951502152</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>4.182012112843076</v>
+        <v>4.25201133965404</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>4.458124104273217</v>
+        <v>4.527846446928763</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>5.876320153618202</v>
+        <v>5.946174501325153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.004025</t>
+          <t>X ≈ -0.004026</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>84</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7370572550209644</v>
+        <v>-0.7049549566271338</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.073945473036645</v>
+        <v>-1.041932571630234</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.411887343913619</v>
+        <v>5.796607220789213</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.156148641645316</v>
+        <v>1.529611120635145</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.6119651063901657</v>
+        <v>0.00713921210546431</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.979498649672301</v>
+        <v>1.380986908426848</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.396731246464768</v>
+        <v>2.46271467171001</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.305414323280438</v>
+        <v>3.371767011477111</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.901293067187396</v>
+        <v>6.967664957976169</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.578263054417</v>
+        <v>2.64554573231981</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.037347764872599</v>
+        <v>4.104365723720861</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.573317067379996</v>
+        <v>2.640698147946949</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.453866370658204</v>
+        <v>1.522589766747174</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.138764577577973</v>
+        <v>-1.069751871762499</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.951795526745855</v>
+        <v>3.021635780523624</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>3.546345563981149</v>
+        <v>3.615541729529319</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.33667341745727</v>
+        <v>-1.267292733742401</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.122325812082991</v>
+        <v>2.191885179807386</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.338471993669309</v>
+        <v>2.407826785213018</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-2.229569723870583</v>
+        <v>-2.160395320582346</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.984251425697437</v>
+        <v>2.054111965563166</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>4.288399990720471</v>
+        <v>4.358397147975985</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>4.564616190549948</v>
+        <v>4.634337523791075</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>8.061821219715675</v>
+        <v>8.131675567422953</v>
       </c>
     </row>
     <row r="15">
@@ -1363,1634 +1363,1634 @@
         <v>92</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-10.70514308590009</v>
+        <v>-10.68702983262071</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.724059877785223</v>
+        <v>-6.700037425414742</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-10.32766036393063</v>
+        <v>-10.30680606548643</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-7.808292044904249</v>
+        <v>-7.78015640852761</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.018455357451373</v>
+        <v>-5.956918062044203</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-6.911268664738117</v>
+        <v>-6.847875613678838</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.610766084059996</v>
+        <v>-6.544021455548766</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-6.893991137970268</v>
+        <v>-6.826873143613035</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7.93590970213792</v>
+        <v>-7.868797553101366</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-9.799580560699361</v>
+        <v>-9.7315228289429</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-12.77359867000499</v>
+        <v>-12.7058282551525</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-11.97353776467155</v>
+        <v>-11.9053839934159</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-9.860858214903203</v>
+        <v>-9.791320891741158</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.58721417190889</v>
+        <v>-3.517335664475794</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-3.168718943009907</v>
+        <v>-3.09801388843912</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-6.906992696746762</v>
+        <v>-6.836950179799622</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.5462351802753886</v>
+        <v>0.6165110850366489</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>2.173715766056375</v>
+        <v>1.596755961752315</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-3.035433081163298</v>
+        <v>-3.610037648221308</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.764222843198496</v>
+        <v>-2.336418255642116</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.221643257431332</v>
+        <v>-1.798140968351007</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-3.470352982428359</v>
+        <v>-3.400366077701619</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-3.196755460582956</v>
+        <v>-3.127039223307214</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-3.27358250699212</v>
+        <v>-3.203728159284587</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.002846</t>
+          <t>X ≈ -0.002847</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>110</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.9364018049463425</v>
+        <v>-0.9052168873335589</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-6.685062019037133</v>
+        <v>-6.661690536150189</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.504364394787501</v>
+        <v>-4.476118387239914</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.604770582399574</v>
+        <v>-1.570677392793591</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-4.676987885585127</v>
+        <v>-4.615217831629572</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-6.301954357814793</v>
+        <v>-6.239147904955544</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.552164568227965</v>
+        <v>-2.486254179081435</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7873135901273329</v>
+        <v>0.8536186753399875</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.789428865558783</v>
+        <v>-2.723149587334007</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.6555638977093</v>
+        <v>-2.588339844117847</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.5731382148983073</v>
+        <v>-0.5061685771024003</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.758684625607799</v>
+        <v>-1.691344474444804</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7432448429196725</v>
+        <v>0.8119521112731647</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.241202293301406</v>
+        <v>3.310227633789168</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.1340289621741988</v>
+        <v>-0.06420448467092399</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.4469533501727057</v>
+        <v>-0.3777719388851821</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.3261655038391211</v>
+        <v>0.395555639374507</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.6860089448393367</v>
+        <v>-0.6166187456328913</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.066659155723272</v>
+        <v>4.137588506622293</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>4.254858621237126</v>
+        <v>4.325705444815384</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.9894541033016893</v>
+        <v>1.059825460202042</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.9028955873738269</v>
+        <v>-0.8329105042865876</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.445974892783013</v>
+        <v>-2.376260478922148</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-5.249867091972362</v>
+        <v>-5.180012744265085</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.002256</t>
+          <t>X ≈ -0.002257</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>99</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-7.242138324552975</v>
+        <v>-7.22061441047682</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.570354544279844</v>
+        <v>-3.543102861459602</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.017929817287971</v>
+        <v>-1.986498538903803</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.734735825297733</v>
+        <v>-1.7005307426709</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-8.134005069935739</v>
+        <v>-8.074300174663541</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-7.943083325832134</v>
+        <v>-7.879836724523727</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-7.726848945123535</v>
+        <v>-7.659289819060085</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.002778609446047</v>
+        <v>-5.934820661700144</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.947867004107074</v>
+        <v>-2.879880969921473</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.7188026575435273</v>
+        <v>-0.6498297680645919</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.445659094830944</v>
+        <v>-1.376964176536525</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-5.750164870978516</v>
+        <v>-5.681114601193627</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.857981667167451</v>
+        <v>-1.787524294091313</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.089092649456767</v>
+        <v>-3.018325192858164</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.7396220033144019</v>
+        <v>-0.6680039684822745</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-4.169409166266824</v>
+        <v>-4.098452142867856</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.6788314867942518</v>
+        <v>-1.209921493572523</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>3.248997247171815</v>
+        <v>2.720225479175966</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>5.0742605084696</v>
+        <v>3.955237734722687</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>3.245765451691739</v>
+        <v>2.129562261495366</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>3.713536900107385</v>
+        <v>3.186041084590592</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>3.639166334024225</v>
+        <v>3.109843025550724</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>3.915319767187562</v>
+        <v>3.985035278238236</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>3.841041998936731</v>
+        <v>3.910896346644009</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001666</t>
+          <t>X ≈ -0.001667</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>138</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-6.3371935305615</v>
+        <v>-6.315338028108329</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-8.845519536911645</v>
+        <v>-8.827252172670867</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-7.440858633652873</v>
+        <v>-7.418411271352213</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.038427913768857</v>
+        <v>-7.421476059009592</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.127057942402452</v>
+        <v>-4.897017705324473</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.07951724558712</v>
+        <v>-3.248889257473962</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.881614077744665</v>
+        <v>0.2847499296693812</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.003061202643735</v>
+        <v>-3.193610881012319</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.962424661720895</v>
+        <v>-2.732997653697495</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.183331351124195</v>
+        <v>-4.540642471228196</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.743536994043517</v>
+        <v>-1.675902842746247</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.301285776258098</v>
+        <v>-1.233267199713396</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.15264655594072</v>
+        <v>-3.083264262175668</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.652984093392604</v>
+        <v>-2.583283261806287</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.146987175586403</v>
+        <v>-1.076451107426273</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>2.051462178352025</v>
+        <v>1.689795872301964</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>2.640495627236405</v>
+        <v>2.280340015333913</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>5.428020783274775</v>
+        <v>5.073463597141711</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>5.643101302527391</v>
+        <v>5.294888781609636</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>5.832267902542625</v>
+        <v>5.909135074046262</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>3.12092213808684</v>
+        <v>3.193746029484487</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>3.046465424886179</v>
+        <v>3.117914962985125</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.598163227694037</v>
+        <v>2.667875363016449</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.07424357996441</v>
+        <v>1.144097927671687</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001076</t>
+          <t>X ≈ -0.001077</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>168</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.853635219202445</v>
+        <v>4.893052068591437</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.733890421775911</v>
+        <v>2.769861408423644</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.056283699886919</v>
+        <v>3.094917874339131</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6259053001708637</v>
+        <v>-0.5920896810961196</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.554952807865661</v>
+        <v>2.623005929148093</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.565247731732931</v>
+        <v>1.632175262721944</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.7838194889796171</v>
+        <v>0.8505738752614178</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.621833566314976</v>
+        <v>2.346900530944296</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3002414415953467</v>
+        <v>-0.579029589429112</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.29079130525821</v>
+        <v>1.009681379313143</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.8045272739038367</v>
+        <v>-1.083918563034558</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.865263755284523</v>
+        <v>-2.796743530973664</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.623963280203064</v>
+        <v>-1.554052513213442</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.629801307854052</v>
+        <v>-3.559574504705097</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.9666053587479766</v>
+        <v>-1.25338094656594</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.413152716278375</v>
+        <v>1.129671026059349</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.097511212297853</v>
+        <v>-1.383116624715022</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.795375881675263</v>
+        <v>-2.080256938636744</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-2.171124927766201</v>
+        <v>-2.103872717455999</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.1470449011760309</v>
+        <v>-0.1298970733903602</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.3948255799369278</v>
+        <v>-0.6764539617762111</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.470582146424384</v>
+        <v>-0.7525358479158655</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-3.170772331172472</v>
+        <v>-3.451892364318475</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-3.247702589807858</v>
+        <v>-3.17784824210058</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.0004865</t>
+          <t>X ≈ -0.0004877</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3126560575709902</v>
+        <v>0.3481695479494036</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9181821359339395</v>
+        <v>0.9530810556510119</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.5280592208631347</v>
+        <v>-0.487657631479415</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.133914952636552</v>
+        <v>-3.084420265853794</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-7.27967574553719</v>
+        <v>-7.18631705820939</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-7.561287269677635</v>
+        <v>-7.468540297447014</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-5.977190930573421</v>
+        <v>-5.889102578462918</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.785515907231421</v>
+        <v>-5.69752023385869</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.63724737576667</v>
+        <v>-2.832737585634767</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.413840970285626</v>
+        <v>-3.607466353737628</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.140850764074479</v>
+        <v>-3.332600892879768</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.677493680742863</v>
+        <v>-7.846948223482073</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-9.754212635659798</v>
+        <v>-9.63349587923841</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-6.668156402468284</v>
+        <v>-6.563004435752191</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-6.381963410059335</v>
+        <v>-6.281624566157447</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-6.25804995426531</v>
+        <v>-6.162021228293163</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-6.39242675279349</v>
+        <v>-6.298780068490153</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-8.389498810245833</v>
+        <v>-8.293360470872976</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-9.591345098862654</v>
+        <v>-9.492563429571298</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-9.403027333536194</v>
+        <v>-9.305717619603271</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-10.61527816372855</v>
+        <v>-10.7916600139844</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-8.801809565282383</v>
+        <v>-8.980713522563306</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-10.42572488078033</v>
+        <v>-10.59303126291145</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-8.136553864915051</v>
+        <v>-8.310372950096976</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0001033</t>
+          <t>X ≈ 0.0001021</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.3259029504061104</v>
+        <v>-0.2809147457074488</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.121104440912383</v>
+        <v>-1.066668468806448</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.028005097396829</v>
+        <v>-2.957239939825691</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5774729797298122</v>
+        <v>-0.5256218573831006</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.673409537355596</v>
+        <v>2.732336128431179</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.507143312767646</v>
+        <v>1.57222338716798</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.991544923892931</v>
+        <v>-1.898046965574935</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8998627458699104</v>
+        <v>0.9695515822448328</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.396280346371817</v>
+        <v>1.460890333738277</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.973389668250796</v>
+        <v>2.034490907477043</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.159963719497583</v>
+        <v>3.20847875983052</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.966959755817101</v>
+        <v>2.02946353963992</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.8301490129080449</v>
+        <v>0.9040507624426368</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.750160169587332</v>
+        <v>-2.914985708892978</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-4.775216551863814</v>
+        <v>-4.926466776915568</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-4.628866952331478</v>
+        <v>-4.782728175710815</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-6.126686534562843</v>
+        <v>-6.271373793566326</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-7.593396459443504</v>
+        <v>-7.456202558243476</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-7.827583250038515</v>
+        <v>-7.69076162776949</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-8.999866708046824</v>
+        <v>-8.855267169152924</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-8.187738622010372</v>
+        <v>-8.046461985767493</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-7.99006394517221</v>
+        <v>-8.122307947176594</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-8.35124582846138</v>
+        <v>-8.748734135595349</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-7.522594364699628</v>
+        <v>-7.923665487917816</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.0006932</t>
+          <t>X ≈ 0.0006918</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>244</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.844632281512261</v>
+        <v>3.879478573115591</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6359576629073729</v>
+        <v>0.6690527306073051</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.001184326107797062</v>
+        <v>0.03320245934560973</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.553461516004425</v>
+        <v>2.590297573467119</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.771352672795473</v>
+        <v>1.837015795132658</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.782974767713085</v>
+        <v>2.849241975380657</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.683813922636368</v>
+        <v>-1.619362101695792</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.190410446215914</v>
+        <v>-3.126348583839956</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.555936515265557</v>
+        <v>-3.492022426699791</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.505434419763183</v>
+        <v>-4.683644735701392</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-6.688285896003016</v>
+        <v>-6.861058532431777</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-5.909861044836418</v>
+        <v>-6.328524204275929</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-7.199595758450172</v>
+        <v>-7.873431222042051</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-6.191991513692074</v>
+        <v>-6.620757894338148</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-8.898538583584795</v>
+        <v>-9.337808324863644</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-9.123065588262612</v>
+        <v>-9.308834713870638</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-6.389863169333289</v>
+        <v>-6.324925582084099</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-8.133212718688945</v>
+        <v>-8.069110548200449</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-7.507777706212835</v>
+        <v>-7.443383101702452</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-7.730511899754845</v>
+        <v>-7.666373357308096</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-8.682806626475255</v>
+        <v>-8.618755590847996</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-9.168446443356494</v>
+        <v>-9.104437617830861</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-8.0744571342697</v>
+        <v>-8.010290774201366</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-8.155977375131727</v>
+        <v>-8.086123027424541</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.001283</t>
+          <t>X ≈ 0.001281</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.217824234619549</v>
+        <v>-3.171499007174582</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.9696394990470836</v>
+        <v>1.005813755327331</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.403399309414709</v>
+        <v>3.433761197919246</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.659321912877964</v>
+        <v>3.687972046616544</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.965024140212307</v>
+        <v>3.026907947970528</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.538697254877725</v>
+        <v>1.603279177636431</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.373919228992641</v>
+        <v>2.439232469239982</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.1524591409073395</v>
+        <v>0.2249600861753649</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5187576711504391</v>
+        <v>0.589604980595162</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.3859961459796537</v>
+        <v>0.4587729023811988</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.826407628129488</v>
+        <v>1.701343903151958</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.51606348328783</v>
+        <v>2.388220521594143</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.034766493624062</v>
+        <v>1.906180273654236</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.1947074249413134</v>
+        <v>0.07162110405747768</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.474434263774732</v>
+        <v>1.548819334166488</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.718867532109186</v>
+        <v>2.788367546432141</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.3197878565435346</v>
+        <v>0.3963858933254869</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.184905853119879</v>
+        <v>1.259287124988241</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.2151630269541016</v>
+        <v>-0.1377247198938392</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.3216521460404</v>
+        <v>-1.241201490571008</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.8972613570094339</v>
+        <v>-0.8160057230531734</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.620079416722483</v>
+        <v>-1.537012974784858</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.5966364160092184</v>
+        <v>0.6729456086649463</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.5720206665531862</v>
+        <v>-0.6932092252034963</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.001873</t>
+          <t>X ≈ 0.001871</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.4689932006225916</v>
+        <v>-0.264641325650615</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.124681535779771</v>
+        <v>-1.242504940720693</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.884894820378662</v>
+        <v>-2.680523989751684</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.034585569469286</v>
+        <v>-0.8211307423134357</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7588297134676907</v>
+        <v>-0.5138343981404105</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-3.13576766456351</v>
+        <v>-2.899215478924027</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.306069694053356</v>
+        <v>-2.063447121013773</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.225649980597638</v>
+        <v>-2.984745382487098</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.902082633523648</v>
+        <v>-1.657084567131911</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.278482146857215</v>
+        <v>-4.037717284969006</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-5.286174161793191</v>
+        <v>-5.049831276247609</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.962703962703962</v>
+        <v>-4.042407046255079</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.9205285145244346</v>
+        <v>-0.9855048044295387</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1803468640203292</v>
+        <v>-0.2419534557957377</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.480303744083272</v>
+        <v>-1.543183570096595</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.526269335487527</v>
+        <v>-1.591883464873817</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.903739534466105</v>
+        <v>0.8465466650297344</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.4832951636804523</v>
+        <v>-0.5444676722319599</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.6943664607897873</v>
+        <v>0.6360539337727218</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.682692307692314</v>
+        <v>-1.749447523140248</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.3382098474123012</v>
+        <v>0.2803535757747468</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.6992836697687679</v>
+        <v>-0.7601226107147383</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-3.309123887902025</v>
+        <v>-3.379538573473837</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-3.705578047683311</v>
+        <v>-3.776914235057248</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.002463</t>
+          <t>X ≈ 0.002461</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.0868198184492</v>
+        <v>-2.257447903945796</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.546258635160456</v>
+        <v>1.755601384660885</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.471637536153615</v>
+        <v>4.270151505590391</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.400885935769629</v>
+        <v>-1.581142434800903</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.147108101746078</v>
+        <v>-4.288474409324529</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-6.737721266517049</v>
+        <v>-6.868306642199549</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.12963501761876</v>
+        <v>-5.268713824113547</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.614538869486445</v>
+        <v>-4.756411434874529</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.382546613987692</v>
+        <v>-3.529153501971614</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.6055227371476732</v>
+        <v>0.4410138259443954</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.4830566074376534</v>
+        <v>0.3198165511102715</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.5896880896880461</v>
+        <v>-0.3541897693337219</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9205285145244346</v>
+        <v>-0.6868380021977956</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.8422416585681916</v>
+        <v>1.068367706335849</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.56426280048327</v>
+        <v>2.781765910731629</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.572021262803112</v>
+        <v>1.795125164690432</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.2474513781779919</v>
+        <v>0.4754372767248114</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.1424679620826694</v>
+        <v>0.3705965729035796</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.625535859112446</v>
+        <v>-1.389796631152286</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.132936507936556</v>
+        <v>2.35436143178017</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.986561495763951</v>
+        <v>2.207072180810144</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.5137810432959</v>
+        <v>1.735969302404953</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.582207003428827</v>
+        <v>2.800957848879094</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.299916457811143</v>
+        <v>3.515639429647919</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.003053</t>
+          <t>X ≈ 0.003051</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7.569897733005185</v>
+        <v>7.416845194260347</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>6.756253318839356</v>
+        <v>6.601299165141327</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.924208357145538</v>
+        <v>2.759433962264154</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.645821742516937</v>
+        <v>3.969556865898305</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.715958656057516</v>
+        <v>5.076074085658753</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>7.773936666193507</v>
+        <v>8.147655656371569</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.871883931268648</v>
+        <v>10.26032235709655</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>9.593329285750087</v>
+        <v>9.982110912343472</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8.199438652208073</v>
+        <v>8.581290401950469</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.990196542874109</v>
+        <v>6.366067033606313</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.786086910467908</v>
+        <v>6.159357444998989</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.942399705557577</v>
+        <v>7.322915733858608</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.774846286113522</v>
+        <v>7.161292128541028</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.075020575557637</v>
+        <v>6.459444021325211</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.416089336520308</v>
+        <v>5.801300723744653</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.618804888534001</v>
+        <v>3.991841491841434</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.441648993428117</v>
+        <v>4.819462816402435</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>6.729010074940547</v>
+        <v>7.118468266427442</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.638913142178559</v>
+        <v>3.007436570428624</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>2.347488038277454</v>
+        <v>2.713513149627445</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>4.196632126887216</v>
+        <v>4.574813135507632</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>6.034552669330786</v>
+        <v>6.422044097175494</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.35239003676984</v>
+        <v>5.734980348119095</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.405635300372197</v>
+        <v>2.774532710280432</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.003642</t>
+          <t>X ≈ 0.003641</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.016226668908693</v>
+        <v>-2.660454956569225</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.569650448025953</v>
+        <v>2.887121186257453</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.419423668150323</v>
+        <v>4.717075993435593</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7.652998776009809</v>
+        <v>7.272095830202019</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.945623727827851</v>
+        <v>7.589900128896559</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.527525182939904</v>
+        <v>3.201702916301095</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.044132735096397</v>
+        <v>5.697728088619925</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.712946510630516</v>
+        <v>9.34108527131788</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.491304680916329</v>
+        <v>4.153814283297933</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.059574533304726</v>
+        <v>2.727303836019573</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.018144326735893</v>
+        <v>1.694173935697869</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.028524107471441</v>
+        <v>4.683398388459025</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.535611836352764</v>
+        <v>6.17461540657019</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.972149762160505</v>
+        <v>6.607131301365428</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>8.286902733649519</v>
+        <v>7.909772317510324</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>9.53985752011301</v>
+        <v>9.157754010695186</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>9.405763825964158</v>
+        <v>9.023836873717755</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>9.300780409868878</v>
+        <v>8.918996169896573</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>11.49058778332697</v>
+        <v>11.09567186454642</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>11.0197368421053</v>
+        <v>10.62892290327258</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>10.47653643310735</v>
+        <v>10.08637673530655</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>7.769002430096315</v>
+        <v>7.396151688930139</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>6.727988122894196</v>
+        <v>6.36343685892848</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>7.967836257309976</v>
+        <v>7.594794148188917</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.004232</t>
+          <t>X ≈ 0.00423</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>106</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.81644463198505</v>
+        <v>4.849718924303879</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-8.726278052470619</v>
+        <v>-8.692605043857277</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-9.222582290141638</v>
+        <v>-9.187227866473151</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-8.992979376919727</v>
+        <v>-8.956785659500824</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.641268029868279</v>
+        <v>-4.575594999972601</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6805185112011145</v>
+        <v>-0.6150439082148438</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.376804035990141</v>
+        <v>1.443196087140088</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.675335515188848</v>
+        <v>-2.608600263273416</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.577215676581311</v>
+        <v>-3.510509307773809</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.464258634520519</v>
+        <v>-2.396632530980078</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.076691820235403</v>
+        <v>-4.009365341648376</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-3.412389497295159</v>
+        <v>-3.344718518681226</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-6.423673168612488</v>
+        <v>-6.35467303836753</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-8.531822432477028</v>
+        <v>-8.462544367644306</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-4.473772539438805</v>
+        <v>-4.403706533149339</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-6.708901169062763</v>
+        <v>-6.639508290451687</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-6.842994863211764</v>
+        <v>-6.773425427429238</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-6.947978279307044</v>
+        <v>-6.87826613125042</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-7.675251342790297</v>
+        <v>-7.605770976741162</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-5.601415094339679</v>
+        <v>-5.53213271394295</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-5.201219276922536</v>
+        <v>-5.131282655493884</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-2.446985653319864</v>
+        <v>-2.376939937657703</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-2.172210486837677</v>
+        <v>-2.102465225175592</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-5.078340505351484</v>
+        <v>-5.008486157644207</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.004822</t>
+          <t>X ≈ 0.00482</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>68</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.203533170456716</v>
+        <v>-2.170258878137886</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.343644256075429</v>
+        <v>3.37731726468877</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.978409149187144</v>
+        <v>-3.943054725518657</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.692202462380337</v>
+        <v>-4.656008744961433</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-9.469236953286703</v>
+        <v>-9.403563923391026</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.399719399103439</v>
+        <v>-3.334244796117169</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-5.643173766451589</v>
+        <v>-5.576781715301642</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-5.92172841197015</v>
+        <v>-5.854993160054718</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-7.350800582241632</v>
+        <v>-7.28409421343413</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.242283051834548</v>
+        <v>-2.174656948294107</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4973355494251379</v>
+        <v>-0.4300090708381106</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.247017688194155</v>
+        <v>-2.179346709580223</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.371508906681299</v>
+        <v>-3.302508776436341</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.6516892471274147</v>
+        <v>-0.5824111822946918</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.310620486164716</v>
+        <v>-1.24055447987525</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.225616034044897</v>
+        <v>2.295008912655973</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.562110575190175</v>
+        <v>3.631680010972701</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.5159506885066136</v>
+        <v>0.5856628365632375</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>5.143838557320741</v>
+        <v>5.213318923369876</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>5.330882352941174</v>
+        <v>5.400164733337903</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.846505473354988</v>
+        <v>1.91644209478364</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.2999621824182555</v>
+        <v>0.3700078980804165</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.895850886393724</v>
+        <v>-0.826105624731639</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>3.439972480220199</v>
+        <v>3.509826827927476</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.005412</t>
+          <t>X ≈ 0.00541</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>58</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.2258455436817783</v>
+        <v>-0.1925712513629492</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-7.457572782464041</v>
+        <v>-7.4238997738507</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.171692270691146</v>
+        <v>3.207046694359633</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-7.886928628708851</v>
+        <v>-7.850734911289948</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.355646689595019</v>
+        <v>-1.289973659699342</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.003931716515218</v>
+        <v>4.069406319501489</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.665486139676744</v>
+        <v>-3.599094088526797</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.952510938942631</v>
+        <v>3.019246190858063</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.442302866034233</v>
+        <v>6.509009234841734</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.39260538629923</v>
+        <v>7.460231489839671</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.666964653414666</v>
+        <v>7.734291132001694</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.663732818905189</v>
+        <v>5.731403797519121</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.090965738349183</v>
+        <v>1.159965868594142</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.31788478938369</v>
+        <v>4.387162854216413</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-1.513460242756963</v>
+        <v>-1.443394236467498</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.8057377378988519</v>
+        <v>0.875130616509928</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.671644043749879</v>
+        <v>0.741213479532405</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>5.739074420758101</v>
+        <v>5.808786568814725</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>9.403473445758884</v>
+        <v>9.472953811808019</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>9.590517241379317</v>
+        <v>9.659799621776045</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>9.047316832381362</v>
+        <v>9.117253453810015</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>8.971361776738753</v>
+        <v>9.041407492400914</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>10.97027487425536</v>
+        <v>11.04002013591744</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>9.170195603952415</v>
+        <v>9.240049951659692</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.006002</t>
+          <t>X ≈ 0.005999</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>44</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>21.3258785942492</v>
+        <v>21.35915288656803</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>20.99070307960488</v>
+        <v>21.02437608821822</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.187366251882409</v>
+        <v>8.222720675550896</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>9.746300211416518</v>
+        <v>9.782493928835422</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>11.65375769911969</v>
+        <v>11.71943072901537</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>11.84092231212654</v>
+        <v>11.90639691511281</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>13.34078345279979</v>
+        <v>13.40717550394974</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.244046989099402</v>
+        <v>6.310782241014834</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>19.92192669048568</v>
+        <v>19.98863305929318</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>23.69354582517078</v>
+        <v>23.76117192871122</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>23.96790509228603</v>
+        <v>24.03523157087306</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>21.41608391608398</v>
+        <v>21.48375489469791</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>18.01886542486947</v>
+        <v>18.08786555511443</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.5247813411079</v>
+        <v>15.59405940594063</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>14.86585010207055</v>
+        <v>14.93591610836001</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>15.46091015169196</v>
+        <v>15.53030303030303</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>15.32681645754306</v>
+        <v>15.39638589332559</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>17.49456031417502</v>
+        <v>17.56427246223164</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>17.71068347710683</v>
+        <v>17.78016384315597</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>13.35227272727273</v>
+        <v>13.42155510766946</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>19.62725413645659</v>
+        <v>19.69719075788525</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>19.55129908081398</v>
+        <v>19.62134479647614</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>17.5533469745688</v>
+        <v>17.62309223623089</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>15.20467836257303</v>
+        <v>15.2745327102803</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.006592</t>
+          <t>X ≈ 0.006589</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>33</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.901636170006782</v>
+        <v>3.934910462325611</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.5361576250594169</v>
+        <v>0.5698306336727583</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.126760191276276</v>
+        <v>2.162114614944763</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-7.677942212825933</v>
+        <v>-7.641748495407029</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.047697093059149</v>
+        <v>1.113370122954827</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.234861706065857</v>
+        <v>1.300336309052128</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.46199557401183</v>
+        <v>0.528387625161777</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.244046989099324</v>
+        <v>6.310782241014756</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.255260023818977</v>
+        <v>3.321966392626479</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.511727643352621</v>
+        <v>5.579353746893062</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>14.87699600137705</v>
+        <v>14.94432247996408</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>11.5675990675991</v>
+        <v>11.63527004621304</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.44310784911189</v>
+        <v>10.51210797935685</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.130841947168527</v>
+        <v>1.20012001200125</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.4719107081311407</v>
+        <v>0.5419767144206062</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>1.066970757752564</v>
+        <v>1.13636363636364</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-2.097425966699433</v>
+        <v>-2.027856530916907</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>3.858196677811385</v>
+        <v>3.927908825868009</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>7.104622871046224</v>
+        <v>7.174103237095359</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>13.35227272727273</v>
+        <v>13.42155510766946</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>3.718163227365679</v>
+        <v>3.788099848794332</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>9.977589398811297</v>
+        <v>10.04733466047338</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>15.96225412014885</v>
+        <v>16.03210846785613</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.007181</t>
+          <t>X ≈ 0.007179</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>33</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.8713331397037436</v>
+        <v>0.9046074320225728</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.566460655362455</v>
+        <v>3.600133663975797</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.157063221579349</v>
+        <v>5.192417645247836</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.50387596899224</v>
+        <v>10.54006968641114</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>10.13860618396825</v>
+        <v>10.20427921386393</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.32577079697494</v>
+        <v>10.39124539996121</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.522601634617885</v>
+        <v>6.588993685767832</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.213743958796385</v>
+        <v>3.280479210711817</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2249569935159457</v>
+        <v>0.2916633623234475</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.5488784172535262</v>
+        <v>-0.4812523137130853</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-9.365428241047326</v>
+        <v>-9.298101762460298</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.614219114219111</v>
+        <v>-6.546548135605178</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-10.76901336300933</v>
+        <v>-10.70001323276437</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.929764113437628</v>
+        <v>-4.860486048604905</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-14.67960444338402</v>
+        <v>-14.60953843709455</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-17.11484742406567</v>
+        <v>-17.04545454545459</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-17.24894111821459</v>
+        <v>-17.17937168243206</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-17.35392453430978</v>
+        <v>-17.28421238625315</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-17.13780137137796</v>
+        <v>-17.06832100532883</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-13.9204545454545</v>
+        <v>-13.85117216505778</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-14.46365495445254</v>
+        <v>-14.39371833302389</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-17.56991304039809</v>
+        <v>-17.49986732473593</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-17.29513787391596</v>
+        <v>-17.22539261225388</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-11.31047315257837</v>
+        <v>-11.2406188048711</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.007771</t>
+          <t>X ≈ 0.007769</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>30</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.992545260915868</v>
+        <v>3.025819553234697</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>12.65736974627152</v>
+        <v>12.69104275488486</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>14.55100261551877</v>
+        <v>14.58635703918726</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>13.83720930232554</v>
+        <v>13.87340301974444</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>23.47193951730146</v>
+        <v>23.53761254719714</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>16.99243746364168</v>
+        <v>17.05791206662795</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>26.21957133158768</v>
+        <v>26.28596338273763</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>25.94101668606902</v>
+        <v>26.00775193798445</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>22.6491994177583</v>
+        <v>22.7159057865658</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>25.2086973403223</v>
+        <v>25.27632344386274</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>25.48305660743766</v>
+        <v>25.55038308602469</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.87062937062932</v>
+        <v>21.93830034924325</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>24.07947148547559</v>
+        <v>24.14847161572055</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>23.85811467444123</v>
+        <v>23.92739273927396</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>26.53251676873729</v>
+        <v>26.60258277502675</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>13.79424348502534</v>
+        <v>13.86363636363642</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>10.32681645754309</v>
+        <v>10.39638589332561</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>6.888499708114367</v>
+        <v>6.95821185617099</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.771289537712832</v>
+        <v>3.840769903761966</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>3.958333333333286</v>
+        <v>4.027615713730015</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>13.4151329243354</v>
+        <v>13.48506954576406</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>13.33917786869272</v>
+        <v>13.40922358435488</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>16.94728636850817</v>
+        <v>17.01703163017025</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>16.87134502923971</v>
+        <v>16.94119937694699</v>
       </c>
     </row>
   </sheetData>
@@ -3184,79 +3184,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02859680586934843</v>
+        <v>-0.02924261372799464</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.007898454641939168</v>
+        <v>0.0072010808152001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.02195112113606967</v>
+        <v>-0.02264770014926398</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.007347209095357243</v>
+        <v>-0.008078461736992892</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.0001294282807648983</v>
+        <v>-0.001213771712095024</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.05566097210114407</v>
+        <v>0.05425557883269505</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.07151115739918623</v>
+        <v>0.07006777182417068</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.01784076289315095</v>
+        <v>0.01645360910088556</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.01699502084809268</v>
+        <v>0.01560905066082796</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.003150039678395444</v>
+        <v>0.001761259238200807</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.06192952018823661</v>
+        <v>-0.06323528293814462</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.115692365915379</v>
+        <v>-0.1169417059987552</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.06290408462160002</v>
+        <v>-0.0642437734654564</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.177390631519323</v>
+        <v>-0.1786003266002609</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.04486418364371758</v>
+        <v>-0.04624798200857327</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.1166426914161107</v>
+        <v>-0.1179277160543819</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.06475570709633871</v>
+        <v>0.06325085465810076</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.007355829651501722</v>
+        <v>0.005915912503489551</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.03271186588135322</v>
+        <v>0.03124609423822733</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.0009314456035838248</v>
+        <v>-0.002353523145991687</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.01024324037593516</v>
+        <v>0.008793984914319708</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.01180934299438263</v>
+        <v>0.01035554741718414</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.05350917644005904</v>
+        <v>-0.05487937499456308</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.08180328469637033</v>
+        <v>-0.08314240149309882</v>
       </c>
     </row>
     <row r="7">
@@ -3266,79 +3266,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3328</v>
+        <v>3332</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.04118745727517137</v>
+        <v>0.04022591190335589</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.0391476666637729</v>
+        <v>-0.04002462734528223</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.08918848630269594</v>
+        <v>-0.09005214661652872</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.06960073351670815</v>
+        <v>-0.07051106140109908</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.05958124756252658</v>
+        <v>-0.06131314662552967</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.02491405260359159</v>
+        <v>0.02308619598115769</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.07607357374009638</v>
+        <v>0.07415886397575377</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.05385560153955993</v>
+        <v>0.05195743380289741</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.02281592987323222</v>
+        <v>0.02095508444456584</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.01420302554070929</v>
+        <v>0.01232663174874205</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.02327882107680068</v>
+        <v>-0.02510271367641081</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1353586533227258</v>
+        <v>-0.13705850243133</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1343649925118626</v>
+        <v>-0.1361031175529845</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1882204563756531</v>
+        <v>-0.1899022936404862</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1101762689213359</v>
+        <v>-0.1119737449772842</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.1565958435118873</v>
+        <v>-0.1583197241879901</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02696638258051109</v>
+        <v>0.02501722007009022</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.0001225674304734525</v>
+        <v>-0.002043785930013087</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.08392080083920916</v>
+        <v>0.08190465553508375</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.01125450180071397</v>
+        <v>-0.01315167236106873</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.003744952755269537</v>
+        <v>0.001811174949438055</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.03587456538947009</v>
+        <v>0.03389864934193554</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.001747375358796432</v>
+        <v>-0.003670440036707134</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.05974471434997497</v>
+        <v>-0.06160174350113579</v>
       </c>
     </row>
     <row r="8">
@@ -3348,79 +3348,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3310</v>
+        <v>3314</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.00124613100287263</v>
+        <v>0.0001477921718660014</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.04771228654158222</v>
+        <v>-0.04876539859233731</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1202672734035062</v>
+        <v>-0.121289137724311</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.09672463160835321</v>
+        <v>-0.09780273910374149</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.144762194924354</v>
+        <v>-0.1467558896464638</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.0307997158455251</v>
+        <v>-0.03292426790589076</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.005255840038465465</v>
+        <v>-0.00744200103106607</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02611099482891177</v>
+        <v>-0.02828409805153598</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.05756749953486917</v>
+        <v>-0.05970250421214018</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.03197654656100468</v>
+        <v>-0.03417335100908048</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.04106817940159857</v>
+        <v>-0.04324480697205502</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1522484138378104</v>
+        <v>-0.154303378958744</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2053824741751455</v>
+        <v>-0.2074181085902467</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2884716709403179</v>
+        <v>-0.2904171283554362</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.2064608349586479</v>
+        <v>-0.2085316797832064</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.2262507886335428</v>
+        <v>-0.228276138872161</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.1012812210822318</v>
+        <v>-0.1034635496133163</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.06767238677903009</v>
+        <v>-0.06990059362815515</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.07486430844094372</v>
+        <v>-0.07707683722421166</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1414453832226954</v>
+        <v>-0.1435717485966421</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1234524464262634</v>
+        <v>-0.1256228469603187</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.09077382212849017</v>
+        <v>-0.09298791544402008</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1301323368174465</v>
+        <v>-0.1322896367980064</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1880708821398898</v>
+        <v>-0.19016252206724</v>
       </c>
     </row>
     <row r="9">
@@ -3430,79 +3430,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3287</v>
+        <v>3291</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1023136395664181</v>
+        <v>0.1008547574189649</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.06550725584389738</v>
+        <v>-0.0667799636984725</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.09833233006771991</v>
+        <v>-0.09963329897702522</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1301326994887546</v>
+        <v>-0.131429357180906</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1759733683608999</v>
+        <v>-0.1783995373949381</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.183558502066866</v>
+        <v>-0.1859682597546666</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1222365780168886</v>
+        <v>-0.1247581005353027</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1413326932830401</v>
+        <v>-0.1438456832230415</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1733323811513756</v>
+        <v>-0.1758062521516166</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1422064262131144</v>
+        <v>-0.144755729107537</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1533070289260223</v>
+        <v>-0.1558316032408982</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2633506233081775</v>
+        <v>-0.2657565687100742</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2484039946133763</v>
+        <v>-0.2508823111924556</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.3002110762412258</v>
+        <v>-0.3026385643714278</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.2433731989003007</v>
+        <v>-0.2459020734581472</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.2674661760773915</v>
+        <v>-0.2699394674235478</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.1103420124023273</v>
+        <v>-0.1130137428175573</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.0757679303105192</v>
+        <v>-0.07848817415955978</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.1148992026678144</v>
+        <v>-0.1175634295712982</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.1832649650562175</v>
+        <v>-0.1858390156578977</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1613615032228779</v>
+        <v>-0.1639893491965054</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1279347288546049</v>
+        <v>-0.1306083824433273</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.1695019526596511</v>
+        <v>-0.1721137728268545</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.2273265050873761</v>
+        <v>-0.2298732453562025</v>
       </c>
     </row>
     <row r="10">
@@ -3512,79 +3512,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3246</v>
+        <v>3250</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.01202114548812006</v>
+        <v>0.01023751840426712</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2149272753522808</v>
+        <v>-0.2164552076253017</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2301421656260345</v>
+        <v>-0.2317414016565493</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2840399322120817</v>
+        <v>-0.2856183869833444</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3259165317030579</v>
+        <v>-0.3290133322766309</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3666311638093305</v>
+        <v>-0.3696685127274435</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2948836689231555</v>
+        <v>-0.2980586558299194</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2494595044071275</v>
+        <v>-0.2527093806519574</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.2517512108831568</v>
+        <v>-0.2549977356393356</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.149175870311673</v>
+        <v>-0.1525981247647366</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1331855936465729</v>
+        <v>-0.1366125212896918</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.333176645331335</v>
+        <v>-0.3363777623446751</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3346110035224896</v>
+        <v>-0.3378822634576437</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3535970372705037</v>
+        <v>-0.3568608394581716</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3492036613702822</v>
+        <v>-0.3525159260063333</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.3811304137659377</v>
+        <v>-0.3843685473519756</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.1896298996657038</v>
+        <v>-0.1931136461279337</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.1533207100897656</v>
+        <v>-0.1568577588985747</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.2264547460972111</v>
+        <v>-0.2298906185113836</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.2365384615384585</v>
+        <v>-0.239952407556558</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2075201997027918</v>
+        <v>-0.2110058717992445</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.2343032478917948</v>
+        <v>-0.237762885509774</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.3106953582138701</v>
+        <v>-0.3140459869731274</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.337527429170585</v>
+        <v>-0.3408519051042447</v>
       </c>
     </row>
     <row r="11">
@@ -3594,325 +3594,325 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3209</v>
+        <v>3213</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1468936829785221</v>
+        <v>-0.1158007312427358</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2488512379438674</v>
+        <v>-0.2341273131423236</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.18583948974441</v>
+        <v>-0.187916306514694</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2941007007713523</v>
+        <v>-0.2960989907720588</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2703157491173016</v>
+        <v>-0.2742686409215906</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3446144938007549</v>
+        <v>-0.3484636684386189</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2321748969719906</v>
+        <v>-0.2362244397598445</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1209988178068997</v>
+        <v>-0.1252097632645999</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1547708055666916</v>
+        <v>-0.1589393187625063</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1041581773114046</v>
+        <v>-0.1084508563128921</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.1221575452625814</v>
+        <v>-0.1264096397451553</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.3212365095320635</v>
+        <v>-0.3252655422295589</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3718742702180222</v>
+        <v>-0.3759287151314226</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3885457791158018</v>
+        <v>-0.3925989868611381</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.3765364734421723</v>
+        <v>-0.3806574484369776</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.4156829474687527</v>
+        <v>-0.4197124928264344</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.2204472240490034</v>
+        <v>-0.2247321190968066</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1825215464216114</v>
+        <v>-0.1868642544223107</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.3523362660622453</v>
+        <v>-0.3564540448602997</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.3647292250233392</v>
+        <v>-0.3688198887981784</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.3291593131075388</v>
+        <v>-0.3333384144349694</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.3554136396639294</v>
+        <v>-0.3595685359146401</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.4981964975353748</v>
+        <v>-0.5021552605162682</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.4933584090068308</v>
+        <v>-0.4973315909956852</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.0055</t>
+          <t>X &gt; -0.005501</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3166</v>
+        <v>3170</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.004108858699360951</v>
+        <v>0.02916543361946822</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2138138589145697</v>
+        <v>-0.1801408503012283</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.224648467004009</v>
+        <v>-0.2066166120047441</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3875239054584654</v>
+        <v>-0.3863209451237708</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4213100902337885</v>
+        <v>-0.4084351315982744</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4363732566263536</v>
+        <v>-0.441042345751832</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.2805857529238338</v>
+        <v>-0.2855249553023853</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1641582563151758</v>
+        <v>-0.1692725441247305</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1675248827760569</v>
+        <v>-0.1726342448313005</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.1686611502437643</v>
+        <v>-0.173844060324889</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.1591788963895908</v>
+        <v>-0.164351441150977</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.4201195280490353</v>
+        <v>-0.4249931768409141</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.4877302771936201</v>
+        <v>-0.4926265714323605</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.3442362911339387</v>
+        <v>-0.3493368204744982</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.3231262758821813</v>
+        <v>-0.3283179275002936</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.3393418961971406</v>
+        <v>-0.3444609722142715</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.2026509234843843</v>
+        <v>-0.2079578271654725</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.1627823431676347</v>
+        <v>-0.1681525434931004</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.3062885133750868</v>
+        <v>-0.3114610673665723</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.3844637223974772</v>
+        <v>-0.3895235427286678</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.3410467327593949</v>
+        <v>-0.3462152530593698</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.4613271818122726</v>
+        <v>-0.4663543895836995</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.5782372605834425</v>
+        <v>-0.5830945130021803</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.5723273228343544</v>
+        <v>-0.5772023054924986</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.00491</t>
+          <t>X &gt; -0.004911</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3108</v>
+        <v>3112</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1916932907348325</v>
+        <v>0.2249675830536617</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1760065939818674</v>
+        <v>0.2096796025952088</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.03198695556348952</v>
+        <v>0.04961582512972029</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1205912091833667</v>
+        <v>-0.1202072038976922</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.01175403600957026</v>
+        <v>0.02323555039210135</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1668715574715804</v>
+        <v>-0.1731848449801703</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.02576200174569721</v>
+        <v>-0.03234917718572916</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.09808027975237366</v>
+        <v>0.0912984000475916</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.1900255464807472</v>
+        <v>0.1831267651395763</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1392973830299411</v>
+        <v>0.1323695091218369</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.07987386686301079</v>
+        <v>0.07304975269129699</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.3088578088578018</v>
+        <v>-0.3152207775172542</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.3567794496532244</v>
+        <v>-0.363215864266671</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.14231295010444</v>
+        <v>-0.1490539829127044</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.1726484542335598</v>
+        <v>-0.1794315366255361</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.1681014015814739</v>
+        <v>-0.1748251748251732</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.02631355850833472</v>
+        <v>-0.03323898644359957</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.01580343896328884</v>
+        <v>-0.02275885154757873</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.1659628447691617</v>
+        <v>-0.1727045909444129</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2490359897172283</v>
+        <v>-0.2556534347508901</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2267828583711449</v>
+        <v>-0.2334965323526106</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.283544532164683</v>
+        <v>-0.2901983809629911</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.40770451816487</v>
+        <v>-0.4141708540356959</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.4002122423175081</v>
+        <v>-0.4067012228815798</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.00432</t>
+          <t>X &gt; -0.004321</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3041</v>
+        <v>3045</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1293392537333773</v>
+        <v>0.1626135460522065</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.153288779898709</v>
+        <v>0.1869617885120505</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2335630335461758</v>
+        <v>0.2507383646851054</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.02799662672937586</v>
+        <v>0.02750030998281261</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.171285922530295</v>
+        <v>0.181425802175994</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1460609563212927</v>
+        <v>-0.1539717074497773</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.08048260257083939</v>
+        <v>0.07215976854205763</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2458907456045551</v>
+        <v>0.2373065497671334</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2735449674965906</v>
+        <v>0.2649253944090049</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1732363474144663</v>
+        <v>0.1646311696990423</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1392452125456671</v>
+        <v>0.1307188174395009</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.2846277535108186</v>
+        <v>-0.2926450220357211</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.3089077194174052</v>
+        <v>-0.3170606704923955</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2159593996328724</v>
+        <v>-0.2242711996240487</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.101363012683521</v>
+        <v>-0.109925410958887</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.07697112085642743</v>
+        <v>-0.08548471945130842</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.005294147831740759</v>
+        <v>-0.00335198347654142</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.01835420981007729</v>
+        <v>0.00967039435524697</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.1726806964740106</v>
+        <v>-0.1810880197352276</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.327380952380949</v>
+        <v>-0.3355634707019917</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2927076363304124</v>
+        <v>-0.3010196930811091</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.3819306864611391</v>
+        <v>-0.3901419117614608</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.5149095552261542</v>
+        <v>-0.5229114645987849</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.5384982240760365</v>
+        <v>-0.5464853521169957</v>
       </c>
     </row>
     <row r="15">
@@ -3922,1719 +3922,1719 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2957</v>
+        <v>2961</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.1539511261498063</v>
+        <v>0.1872254184686355</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1881510312502712</v>
+        <v>0.2218240398636127</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.05805432807750321</v>
+        <v>0.09340875174599006</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.03245814812789405</v>
+        <v>-0.0151127626598182</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1587674742907836</v>
+        <v>0.1863701026035258</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2064420881790738</v>
+        <v>-0.1975166327228735</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.01468453490527111</v>
+        <v>0.004342608168506956</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1589783409631096</v>
+        <v>0.1483856856051489</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.08526940429941732</v>
+        <v>0.0747767543078055</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.104916346268638</v>
+        <v>0.09425061473106666</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.02851115289215045</v>
+        <v>0.01799124563010679</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3658138762550962</v>
+        <v>-0.3758604311132387</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.3589831416583067</v>
+        <v>-0.3692493353786261</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1897451165935067</v>
+        <v>-0.2002859323293436</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.1880946046050838</v>
+        <v>-0.1987640263200916</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.1798992918156301</v>
+        <v>-0.1904783775784153</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.04341564782643559</v>
+        <v>0.03250449170830905</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.04141366796838497</v>
+        <v>-0.0522364080689286</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.2440154364036857</v>
+        <v>-0.2545324113649627</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.2733451536643088</v>
+        <v>-0.2837951912727519</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.3573895981871402</v>
+        <v>-0.3678319387163995</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.5146015612948389</v>
+        <v>-0.5248522396972675</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.6592045037027177</v>
+        <v>-0.6692164004396304</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.7828089556548363</v>
+        <v>-0.7926743143734498</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.003141</t>
+          <t>X &gt; -0.003142</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2865</v>
+        <v>2869</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5026550240585621</v>
+        <v>0.5359293163773913</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4101138248388452</v>
+        <v>0.4437868334521866</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.3915572082397105</v>
+        <v>0.4269116319081974</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2172370415766167</v>
+        <v>0.2338882883753328</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3571285564968179</v>
+        <v>0.3833664466772788</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.008861243424213683</v>
+        <v>0.01573991180412548</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2274389701390618</v>
+        <v>0.214328489612214</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.3854611305135052</v>
+        <v>0.3720607683127426</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.342843044017485</v>
+        <v>0.3295027341898731</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4229665087262546</v>
+        <v>0.4093329280172355</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4396085712888365</v>
+        <v>0.4260049765719032</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.006929787875549209</v>
+        <v>-0.006144095201136679</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.05386184785777459</v>
+        <v>-0.0671124991341685</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.0806466338399332</v>
+        <v>-0.09391835639436152</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.09238171136485818</v>
+        <v>-0.1057940063427694</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.03611906534097642</v>
+        <v>0.02265351709023378</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.02726926144411834</v>
+        <v>0.01377719767337737</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.1125452239650002</v>
+        <v>-0.1051145182200486</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.1543782903939501</v>
+        <v>-0.1469316857495073</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.2254705472290013</v>
+        <v>-0.2179738870127466</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.3296369501416052</v>
+        <v>-0.321966330237359</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.4196873795341816</v>
+        <v>-0.4326433609602915</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.5777194467976585</v>
+        <v>-0.5904015870189951</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.7028260004286508</v>
+        <v>-0.7153592381337077</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.002551</t>
+          <t>X &gt; -0.002552</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2755</v>
+        <v>2759</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.5601128284834402</v>
+        <v>0.5933871208022694</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.693405782307579</v>
+        <v>0.7270787909209204</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5870386515547779</v>
+        <v>0.6223930752232647</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2899850773796615</v>
+        <v>0.3058354521769218</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.5581277610808399</v>
+        <v>0.5826575922422563</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2608357320399222</v>
+        <v>0.2651192738351327</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3384213255729591</v>
+        <v>0.3219994187736148</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3694162047212899</v>
+        <v>0.3528612866987473</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.4679065322401286</v>
+        <v>0.4512105106913609</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5458842382028095</v>
+        <v>0.5288486963879677</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.480044922098493</v>
+        <v>0.463170286794508</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.07742618913985666</v>
+        <v>0.06104403155377724</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.08568824930442531</v>
+        <v>-0.1021603813903482</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2132794403682539</v>
+        <v>-0.2296400160247245</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.09071884472638203</v>
+        <v>-0.1074521605232306</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.05540689318362979</v>
+        <v>0.0386182869913938</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.01533511020511469</v>
+        <v>-0.001444124757625787</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.08964830589016515</v>
+        <v>-0.08472109124816285</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.3229133608378305</v>
+        <v>-0.3177534404290583</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.4043584632113095</v>
+        <v>-0.3991281916525082</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.3823048324932401</v>
+        <v>-0.377057702817396</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.4003941298563731</v>
+        <v>-0.4166849029081376</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.5031248554878971</v>
+        <v>-0.5192002538876537</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.5212744504940474</v>
+        <v>-0.5373556550693905</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.001961</t>
+          <t>X &gt; -0.001962</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2656</v>
+        <v>2660</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8509346899859267</v>
+        <v>0.8842089823047559</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.8523335956856499</v>
+        <v>0.8860066042989914</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.6841364973437223</v>
+        <v>0.7194909210122091</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3654547194598834</v>
+        <v>0.3805084797295279</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.882119158020096</v>
+        <v>0.9048526369503946</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5666294017422473</v>
+        <v>0.5682586136236836</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.6390469870183395</v>
+        <v>0.6190474016854708</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6069340084120185</v>
+        <v>0.5868765171090828</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5952264042651194</v>
+        <v>0.5751872236916213</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.593024299452388</v>
+        <v>0.572716804651435</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5518237992355566</v>
+        <v>0.5316564942643396</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.294644380010233</v>
+        <v>0.2747559505921302</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.01962761362354115</v>
+        <v>-0.03943443125599089</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.1060861016258769</v>
+        <v>-0.1258506053079955</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.06653156584828679</v>
+        <v>-0.08658951804655857</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.2128830941947726</v>
+        <v>0.1925919608846414</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.04120954284930178</v>
+        <v>0.04353304047270967</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.2140933020321469</v>
+        <v>-0.1891157192451587</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.5240881398519264</v>
+        <v>-0.4767858187523686</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.540413533834581</v>
+        <v>-0.4932411070140219</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.5349736320141218</v>
+        <v>-0.5096692742284503</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.5509650959422885</v>
+        <v>-0.5479353784410108</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.6678183862276867</v>
+        <v>-0.6868390951209236</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.6838758542943708</v>
+        <v>-0.7029108987421822</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001371</t>
+          <t>X &gt; -0.001372</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.244882940357463</v>
+        <v>1.278157232676293</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.383828326542847</v>
+        <v>1.417501335156189</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.12943011453099</v>
+        <v>1.164784538199477</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7712274769601066</v>
+        <v>0.8074211943790104</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.156649118249774</v>
+        <v>1.222322148145452</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7116525301502818</v>
+        <v>0.7771271331365526</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5709475992025332</v>
+        <v>0.6373396503524802</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.7499758428543117</v>
+        <v>0.7937390313599764</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.7353994968410049</v>
+        <v>0.7562060631363892</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8547943867357688</v>
+        <v>0.8525120386210503</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6776219682079514</v>
+        <v>0.6524507799532628</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.3821099723712535</v>
+        <v>0.3572726812591114</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.1520787462016315</v>
+        <v>0.1271193025532611</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.03349766440422997</v>
+        <v>0.008616367965906591</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.007316762772873631</v>
+        <v>-0.03242579904004828</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.1121190300114137</v>
+        <v>0.1106672424962269</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.1012453736103538</v>
+        <v>-0.07886163142691771</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.5233116275970318</v>
+        <v>-0.4770760466287385</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.8620834309751686</v>
+        <v>-0.7926030649260341</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.8896708961141897</v>
+        <v>-0.8435693833765541</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.7353364661181487</v>
+        <v>-0.7123145208233694</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.7481237186088165</v>
+        <v>-0.7485251274960447</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.846811818603058</v>
+        <v>-0.8704039623782407</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.7802302950917124</v>
+        <v>-0.8039764094658537</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0007815</t>
+          <t>X &gt; -0.0007826</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2350</v>
+        <v>2354</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.9868955434017437</v>
+        <v>1.020169835720573</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.2873132490964</v>
+        <v>1.320986257709741</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9916805816204359</v>
+        <v>1.027035005288923</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.8711076074103232</v>
+        <v>0.907301324829227</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.056685280013397</v>
+        <v>1.122358309909075</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6506295540371383</v>
+        <v>0.716104157023409</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5557295236780249</v>
+        <v>0.6221215748279718</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.616157929006917</v>
+        <v>0.6828931809223491</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.8094368064824025</v>
+        <v>0.8514990069048594</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.8236252453265109</v>
+        <v>0.8412951952751371</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.7835798714738118</v>
+        <v>0.776371786589614</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.614262647369614</v>
+        <v>0.5823681458534722</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.2790468570254561</v>
+        <v>0.2471009784448412</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2953845696550346</v>
+        <v>0.2632706018693511</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.06126216664151229</v>
+        <v>0.05471118684964438</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.01910896222721448</v>
+        <v>0.03794309821474684</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.03002296471694876</v>
+        <v>0.01422028823001398</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.4323725660288815</v>
+        <v>-0.3626604179722577</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.7685008899279921</v>
+        <v>-0.6990205238788576</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.9637850467289724</v>
+        <v>-0.8945026663322437</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.759679372023875</v>
+        <v>-0.714873813057828</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.767964988450089</v>
+        <v>-0.7482388908645561</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.6806733649385279</v>
+        <v>-0.6861685963943955</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.6038322757247698</v>
+        <v>-0.6345581988105309</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0001916</t>
+          <t>X &gt; -0.0001928</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2139</v>
+        <v>2142</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.053405375804864</v>
+        <v>1.086679668123693</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.323725902147963</v>
+        <v>1.357398910761304</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.141594138574163</v>
+        <v>1.17694856224265</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.266179959055897</v>
+        <v>1.302373676474801</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.879019163319235</v>
+        <v>1.944692193214912</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.460687735338595</v>
+        <v>1.526162338324866</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.200164407197001</v>
+        <v>1.266556458346948</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.247646091440899</v>
+        <v>1.314381343356331</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.149432300851053</v>
+        <v>1.216138669658555</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.241626821527611</v>
+        <v>1.281602127296956</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.170702295083302</v>
+        <v>1.183048821158934</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.432196534808483</v>
+        <v>1.416642221623377</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.268769976687253</v>
+        <v>1.225012525517137</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9822976809771546</v>
+        <v>0.9388869921474949</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.6968491683637552</v>
+        <v>0.6818368542807818</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.6383144467433084</v>
+        <v>0.6515716870194481</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.5975914342003605</v>
+        <v>0.6390363832928898</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.3525519956961176</v>
+        <v>0.4222641437527415</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.1018217505980559</v>
+        <v>0.1713021166471904</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.1313025210084007</v>
+        <v>-0.06202014061167205</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.2125185452504113</v>
+        <v>0.282455166679064</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.02452739383678448</v>
+        <v>0.06655318286099998</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.2806197018415659</v>
+        <v>0.2943425545400657</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.1392272171780533</v>
+        <v>0.125139619710815</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0003982</t>
+          <t>X &gt; 0.0003969</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.211533479904091</v>
+        <v>1.24480777222292</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.604008692910483</v>
+        <v>1.637681701523825</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.619609684125813</v>
+        <v>1.654964107794299</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.47754194265822</v>
+        <v>1.513735660077124</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.78794783330985</v>
+        <v>1.853620863205528</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.45536192656612</v>
+        <v>1.52083652955239</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.56607167808798</v>
+        <v>1.632463729237926</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.287517032569419</v>
+        <v>1.354252284484851</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.121132889691836</v>
+        <v>1.187839258499338</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.157735301840738</v>
+        <v>1.19454936208863</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.9426473115652527</v>
+        <v>0.9488584845000361</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.370889651732966</v>
+        <v>1.345784756727717</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.319054818808894</v>
+        <v>1.262123729372632</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.410198007774547</v>
+        <v>1.384491023205292</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.32418343540391</v>
+        <v>1.33029696163787</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.242160151691955</v>
+        <v>1.279912608647642</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.368483124209703</v>
+        <v>1.438052559992229</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.263499708114423</v>
+        <v>1.333211856171047</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.010872871046232</v>
+        <v>1.080353237095366</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.8854166666666714</v>
+        <v>0.9546990470634</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.175549591002046</v>
+        <v>1.245486212430698</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.9433445353594365</v>
+        <v>1.013390251021598</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.270203035174895</v>
+        <v>1.33994829683698</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.017601760176014</v>
+        <v>1.055782710280376</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.0009881</t>
+          <t>X &gt; 0.0009867</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8279656544758041</v>
+        <v>0.8612399467946332</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.74502627578854</v>
+        <v>1.778699284401881</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.85571340860163</v>
+        <v>1.891067832270117</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.320810971973756</v>
+        <v>1.35700468939266</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.790365277587767</v>
+        <v>1.856038307483445</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.261966384333363</v>
+        <v>1.327440987319633</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.039487849178563</v>
+        <v>2.10587990032851</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.9398240802253</v>
+        <v>2.006559332140732</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.802449268682636</v>
+        <v>1.869155637490138</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.982698532928119</v>
+        <v>2.050324636468559</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.054257880309528</v>
+        <v>2.085863109876748</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.43148855917353</v>
+        <v>2.463046920501512</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.559980634242464</v>
+        <v>2.592120989602456</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.517621436573272</v>
+        <v>2.549932989721164</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.813344135483462</v>
+        <v>2.883410141772927</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.752079602765946</v>
+        <v>2.821472481377022</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.498654166373576</v>
+        <v>2.568223602156102</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.632334234765175</v>
+        <v>2.702046382821798</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.251798686479802</v>
+        <v>2.321279052528936</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.140513126491648</v>
+        <v>2.209795506888376</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.611632526562907</v>
+        <v>2.68156914799156</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.416345728676859</v>
+        <v>2.48639144433902</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.631455024037272</v>
+        <v>2.701200285699358</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.353932093916377</v>
+        <v>2.386704547989204</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.001578</t>
+          <t>X &gt; 0.001576</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1366</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.7431553146006</v>
+        <v>1.776429606919429</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.92042489512464</v>
+        <v>1.954097903737981</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.505614621375258</v>
+        <v>1.540969045043745</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.7918213081821008</v>
+        <v>0.8280150256010046</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.524648155661708</v>
+        <v>1.590321185557386</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.199367673500127</v>
+        <v>1.264842276486398</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.963836826951216</v>
+        <v>2.030228878101163</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.344140160934856</v>
+        <v>2.410875412850288</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.092830457289843</v>
+        <v>2.159536826097344</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.343885236857169</v>
+        <v>2.41151134039761</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.105799408804131</v>
+        <v>2.173125887391159</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.41235704266451</v>
+        <v>2.480028021278443</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.678788225348669</v>
+        <v>2.747788355593627</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.043082951649602</v>
+        <v>3.112361016482325</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.116216134281409</v>
+        <v>3.186282140570874</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.759592435732948</v>
+        <v>2.828985314344024</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.991530952418586</v>
+        <v>3.061100388201112</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.959753978490212</v>
+        <v>3.029466126546836</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.809844930587467</v>
+        <v>2.879325296636601</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.923682284040993</v>
+        <v>2.992964664437721</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.405372065379787</v>
+        <v>3.47530868680844</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.329417009737178</v>
+        <v>3.399462725399339</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.09174708105094</v>
+        <v>3.161492342713025</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.015805741782472</v>
+        <v>3.08566008948975</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.002168</t>
+          <t>X &gt; 0.002166</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.397984856108785</v>
+        <v>2.378110232539598</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.821822624196912</v>
+        <v>2.896414002910163</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.805272065234107</v>
+        <v>2.785409171888652</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.332465469308502</v>
+        <v>1.314161313583355</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.200592268724684</v>
+        <v>2.210598329187732</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.482633542073032</v>
+        <v>2.492351245142927</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.227793975483891</v>
+        <v>3.236990238977704</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.992882593722456</v>
+        <v>4.001432822660647</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.275385376012629</v>
+        <v>3.284626165712794</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.304206511732772</v>
+        <v>4.312658356974879</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.293935797823444</v>
+        <v>4.30235780956334</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.299471875373207</v>
+        <v>4.402755325546622</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.7442406189354</v>
+        <v>3.848313637837421</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.997267109608828</v>
+        <v>4.101168410679932</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.476855794670193</v>
+        <v>4.580465871393223</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>4.028272580534455</v>
+        <v>4.132198764900188</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.609548905360867</v>
+        <v>3.713921438349253</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.978948790973369</v>
+        <v>4.083014383817172</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.436058671172738</v>
+        <v>3.540611925878935</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>4.287239089184055</v>
+        <v>4.390964844851709</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>4.313298642235445</v>
+        <v>4.417139056032589</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.521973567617501</v>
+        <v>4.62565328419695</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.98650205478274</v>
+        <v>5.08970145639465</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>5.005437375855827</v>
+        <v>5.108655933029191</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.002758</t>
+          <t>X &gt; 0.002756</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>802</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.807175352353944</v>
+        <v>3.840449644672773</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.222623279106131</v>
+        <v>3.256296287719472</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.281675932226968</v>
+        <v>2.317030355895454</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.191324015542534</v>
+        <v>2.227517732961438</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.195131537251662</v>
+        <v>4.260804567147339</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.379802384672416</v>
+        <v>5.445276987658687</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.853819045635845</v>
+        <v>5.920211096785792</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.697458913832989</v>
+        <v>6.764194165748421</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.367403906536417</v>
+        <v>5.434110275343919</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.466386450879213</v>
+        <v>5.534012554419654</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.491369159391056</v>
+        <v>5.558695637978083</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.835716652424878</v>
+        <v>5.903387631038811</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.209978551144722</v>
+        <v>5.278978681389681</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.988621740110368</v>
+        <v>5.057899804943091</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.077820176883542</v>
+        <v>5.147886183173007</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>4.800062271392697</v>
+        <v>4.869455150003773</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.665968577243774</v>
+        <v>4.7355380130263</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.184426557657233</v>
+        <v>5.254138705713856</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>5.026484882683796</v>
+        <v>5.095965248732931</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>4.964152119700742</v>
+        <v>5.033434500097471</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>5.044393107211526</v>
+        <v>5.114329728640179</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>5.467191168775905</v>
+        <v>5.537236884438066</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.741966335258034</v>
+        <v>5.811711596920119</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>5.541336716687816</v>
+        <v>5.611191064395094</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.003347</t>
+          <t>X &gt; 0.003346</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.481021933203678</v>
+        <v>2.588109115524261</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.977212354478397</v>
+        <v>2.084982148824274</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.055218467120767</v>
+        <v>2.162114614944805</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.67869328208949</v>
+        <v>1.617510763852231</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.011568522360562</v>
+        <v>3.975322984907649</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.536001263529229</v>
+        <v>4.49898950770536</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.437671387798979</v>
+        <v>4.400441497215695</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.676823319008925</v>
+        <v>5.637381567614128</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.369266871384006</v>
+        <v>4.332067402727482</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.281772101424011</v>
+        <v>5.24265341019268</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.387497304458407</v>
+        <v>5.34836288400443</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.445671529145386</v>
+        <v>5.40631381725678</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.658448438820137</v>
+        <v>4.619852087100995</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.605725691866731</v>
+        <v>4.56712337900457</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>4.958598837315101</v>
+        <v>4.919081091525022</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>5.216390758774587</v>
+        <v>5.176767676767682</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.745028936463783</v>
+        <v>4.706150203089862</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>4.640045520368503</v>
+        <v>4.60130949926868</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>5.867973067785975</v>
+        <v>5.827301890294031</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.88638279932546</v>
+        <v>5.845797531911884</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>5.343182390327506</v>
+        <v>5.303251363945854</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>5.267227334684897</v>
+        <v>5.227405402536753</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>5.879270629328921</v>
+        <v>5.838580451719139</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>6.646499610465177</v>
+        <v>6.604499040246701</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.003937</t>
+          <t>X &gt; 0.003935</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>441</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.3757652155644</v>
+        <v>4.409039507883229</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.773016004774938</v>
+        <v>1.806689013388279</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.240345019146858</v>
+        <v>1.275699442815345</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3804777725043564</v>
+        <v>-0.3442840550854527</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.655612986689292</v>
+        <v>2.721286016584969</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.883593926226688</v>
+        <v>4.949068529212958</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.88397042455815</v>
+        <v>3.950362475708097</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.285687887883121</v>
+        <v>4.352423139798553</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.327203952905755</v>
+        <v>4.393910321713257</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.047699607895971</v>
+        <v>6.115325711436412</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.548816244625812</v>
+        <v>6.616142723212839</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.589450232307378</v>
+        <v>5.657121210921311</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.011444274591213</v>
+        <v>4.080444404836172</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.790087463556858</v>
+        <v>3.859365528389581</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>3.811428333363096</v>
+        <v>3.881494339652562</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>3.726216274140938</v>
+        <v>3.795609152752014</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.13860784076298</v>
+        <v>3.208177276545506</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.0336244246677</v>
+        <v>3.103336572724324</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.930019696443054</v>
+        <v>3.999500062492189</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>4.117063492063487</v>
+        <v>4.186345872460215</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>3.573863083065532</v>
+        <v>3.643799704494185</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>4.404937505880973</v>
+        <v>4.474983221543134</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>5.586742150821159</v>
+        <v>5.656487412483244</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>6.191072920396216</v>
+        <v>6.260927268103494</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.004527</t>
+          <t>X &gt; 0.004525</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>335</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.236326355443232</v>
+        <v>4.269600647762061</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.095180691545174</v>
+        <v>5.128853700158515</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.55100261551874</v>
+        <v>4.586357039187227</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.344671988892749</v>
+        <v>2.380865706311653</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.964476830734377</v>
+        <v>5.030149860630054</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.644178757173989</v>
+        <v>6.70965336016026</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.677282774373701</v>
+        <v>4.743674825523648</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>6.488280367661112</v>
+        <v>6.555015619576544</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.828303895370311</v>
+        <v>6.895010264177813</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.741035648779992</v>
+        <v>8.808661752320432</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.910917303955017</v>
+        <v>9.978243782542044</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.437793549733854</v>
+        <v>8.505464528347787</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.31330233124671</v>
+        <v>7.382302461491669</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.688960445585487</v>
+        <v>7.758238510418209</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>6.433014281175055</v>
+        <v>6.50308028746452</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>7.028074330796436</v>
+        <v>7.097467209407512</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>6.296965711274382</v>
+        <v>6.366535147056908</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>6.191982295179102</v>
+        <v>6.261694443235726</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>7.602135308857179</v>
+        <v>7.671615674906313</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>7.192164179104481</v>
+        <v>7.261446559501209</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>6.350456307419954</v>
+        <v>6.420392928848607</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>6.573008714463917</v>
+        <v>6.643054430126078</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>8.041813731692308</v>
+        <v>8.111558993354393</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>9.756917168543247</v>
+        <v>9.826771516250524</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.005117</t>
+          <t>X &gt; 0.005115</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>267</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.876440392002017</v>
+        <v>5.909714684320846</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.54126487735769</v>
+        <v>5.574937885971032</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.723287259713494</v>
+        <v>6.758641683381981</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.136834770490381</v>
+        <v>4.173028487909285</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8.640478843144237</v>
+        <v>8.706151873039914</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>9.202175291357008</v>
+        <v>9.267649894343279</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.305713653685011</v>
+        <v>7.372105704834958</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.648881854608391</v>
+        <v>9.715617106523823</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>10.43946159004301</v>
+        <v>10.50616795885051</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>11.53828535530355</v>
+        <v>11.60591145884399</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>12.56170829283087</v>
+        <v>12.6290347714179</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.15901888373799</v>
+        <v>11.22668986235192</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.03452766525084</v>
+        <v>10.1035277954958</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>9.813170854216487</v>
+        <v>9.88244891904921</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>8.405175944767201</v>
+        <v>8.475241951056667</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>8.251172323976597</v>
+        <v>8.320565202587673</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>6.993483124209689</v>
+        <v>7.063052559992215</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>7.637563378526409</v>
+        <v>7.707275526583032</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>8.228218376664209</v>
+        <v>8.297698742713344</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>7.666198501872657</v>
+        <v>7.735480882269385</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>7.497529928080702</v>
+        <v>7.567466549509355</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>8.170638542850078</v>
+        <v>8.240684258512239</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>10.31807288536216</v>
+        <v>10.38781814702425</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>11.36572705171167</v>
+        <v>11.43558139941894</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.005707</t>
+          <t>X &gt; 0.005705</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>209</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7.569897733005185</v>
+        <v>7.603172025324014</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9.14859781644698</v>
+        <v>9.182270825060321</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.708897352360843</v>
+        <v>7.74425177602933</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.473572938689216</v>
+        <v>7.50976665610812</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>11.41452324935895</v>
+        <v>11.48019627925463</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>10.64475006332268</v>
+        <v>10.71022466630895</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10.35035283079018</v>
+        <v>10.41674488194013</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.50720488383621</v>
+        <v>11.57394013575164</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>11.54872094885884</v>
+        <v>11.61542731766635</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.68876113617555</v>
+        <v>12.75638723971599</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.92005820233393</v>
+        <v>13.98738468092096</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.68402649981599</v>
+        <v>12.75169747842992</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.51647308037189</v>
+        <v>12.58547321061685</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>11.33817847029449</v>
+        <v>11.40745653512721</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>11.1577161307787</v>
+        <v>11.22778213706817</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>10.31736948183549</v>
+        <v>10.38676236044657</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>8.747869089121977</v>
+        <v>8.817438524904503</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>8.164416773505167</v>
+        <v>8.234128921561791</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>7.902071036915451</v>
+        <v>7.971551402964586</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>7.132177033492823</v>
+        <v>7.201459413889552</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>7.067445524016399</v>
+        <v>7.137382145445052</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>7.948428267416851</v>
+        <v>8.018473983079012</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>10.1370790319851</v>
+        <v>10.20682429364719</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>11.97501329080276</v>
+        <v>12.04486763851003</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.006297</t>
+          <t>X &gt; 0.006294</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>165</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.901636170006782</v>
+        <v>3.934910462325611</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.990703079604877</v>
+        <v>6.024376088218219</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.581305645821764</v>
+        <v>7.616660069490251</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.867512332628607</v>
+        <v>6.903706050047511</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>11.35072739608943</v>
+        <v>11.4164004259851</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>10.32577079697498</v>
+        <v>10.39124539996125</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>9.619296716070899</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12.91071365576603</v>
+        <v>12.97744890768146</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.315866084425025</v>
+        <v>9.382572453232527</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.754151885776828</v>
+        <v>9.821777989317269</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.24063236501337</v>
+        <v>11.3079588436004</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>10.35547785547786</v>
+        <v>10.42314883409179</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.04916845517253</v>
+        <v>11.11816858541749</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.22175103807758</v>
+        <v>10.2910291029103</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>10.16888040510087</v>
+        <v>10.23894641139034</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>8.94575863654044</v>
+        <v>9.015151515151516</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>6.993483124209689</v>
+        <v>7.063052559992215</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>5.676378495993205</v>
+        <v>5.746090644049829</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>5.286441052864411</v>
+        <v>5.355921418913546</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>5.473484848484844</v>
+        <v>5.542767228881573</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>3.718163227365679</v>
+        <v>3.788099848794332</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>4.854329383844281</v>
+        <v>4.924375099506442</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>8.159407580629455</v>
+        <v>8.229152842291541</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>11.113769271664</v>
+        <v>11.18362361937128</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.006886</t>
+          <t>X &gt; 0.006884</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>132</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.901636170006782</v>
+        <v>3.934910462325611</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.354339443241244</v>
+        <v>7.388012451854586</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>8.944942009458131</v>
+        <v>8.980296433126618</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.50387596899224</v>
+        <v>10.54006968641114</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>13.92648497184699</v>
+        <v>13.99215800174267</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.59849806970226</v>
+        <v>12.66397267268853</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.82563193764823</v>
+        <v>11.89202398879818</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.5773803224327</v>
+        <v>14.64411557434813</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.83101759957654</v>
+        <v>10.89772396838404</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.81475794638288</v>
+        <v>10.88238404992332</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>10.33154145592245</v>
+        <v>10.39886793450948</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>10.05244755244755</v>
+        <v>10.12011853106148</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>11.20068360668768</v>
+        <v>11.26968373693264</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>12.49447831080484</v>
+        <v>12.56375637563757</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>12.59312282934331</v>
+        <v>12.66318883563277</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>10.91545560623741</v>
+        <v>10.98484848484848</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>9.26621039693697</v>
+        <v>9.335779832719496</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>6.130923950538659</v>
+        <v>6.200636098595282</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>4.831895598318958</v>
+        <v>4.901375964368093</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>3.503787878787875</v>
+        <v>3.573070259184604</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>3.718163227365679</v>
+        <v>3.788099848794332</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>4.399783929298827</v>
+        <v>4.469829644960988</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>7.704862126083988</v>
+        <v>7.774607387746073</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>9.901648059542801</v>
+        <v>9.971502407250078</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.007476</t>
+          <t>X &gt; 0.007474</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>99</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.911737180107792</v>
+        <v>4.945011472426621</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>8.616965705867507</v>
+        <v>8.650638714480849</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.2075682720844</v>
+        <v>10.24292269575289</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.50387596899224</v>
+        <v>10.54006968641114</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>15.18911123447324</v>
+        <v>15.25478426436892</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.35607382727802</v>
+        <v>13.42154843026429</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>13.59330870532501</v>
+        <v>13.65970075647495</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>18.36525911031148</v>
+        <v>18.43199436222692</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.36637113493008</v>
+        <v>14.43307750373758</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.60263673426167</v>
+        <v>14.67026283780211</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.89719802157903</v>
+        <v>16.96452450016606</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>15.6080031080031</v>
+        <v>15.67567408661704</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>18.52391592992002</v>
+        <v>18.59291606016497</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.30255911888566</v>
+        <v>18.37183718371838</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>21.6840319202524</v>
+        <v>21.75409792654187</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>20.25888994967176</v>
+        <v>20.32828282828284</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>18.10459423532082</v>
+        <v>18.17416367110334</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>13.95920677882148</v>
+        <v>14.02891892687811</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>12.15512792155128</v>
+        <v>12.22460828760041</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>9.311868686868678</v>
+        <v>9.381151067265407</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>9.778769287971748</v>
+        <v>9.848705909400401</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>11.72301625253115</v>
+        <v>11.79306196819331</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>16.03819545941732</v>
+        <v>16.1079407210794</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>16.97235513024986</v>
+        <v>17.04220947795714</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.008066</t>
+          <t>X &gt; 0.008064</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>5.746168449321665</v>
+        <v>5.779442741640494</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>6.860268296996189</v>
+        <v>6.89394130560953</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8.319118557547718</v>
+        <v>8.354472981216205</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>9.054600606673411</v>
+        <v>9.090794324092315</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>11.58788154628705</v>
+        <v>11.65355457618273</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>11.77504615929384</v>
+        <v>11.84052076228011</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8.103629302602123</v>
+        <v>8.17002135375207</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>15.07145146867776</v>
+        <v>15.1381867205932</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>10.76514144674388</v>
+        <v>10.83184781555138</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>9.991306035974453</v>
+        <v>10.05893213951489</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>13.16421602772746</v>
+        <v>13.23154250631449</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>12.88512212425256</v>
+        <v>12.95279310286649</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>16.10845699272195</v>
+        <v>16.17745712296691</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>15.88710018168759</v>
+        <v>15.95637824652032</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>19.57599502960681</v>
+        <v>19.64606103589627</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>23.06960580386586</v>
+        <v>23.13899868247694</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>21.48623674739811</v>
+        <v>21.55580618318064</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>17.0334272443463</v>
+        <v>17.10313939240292</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>15.80027504495929</v>
+        <v>15.86975541100842</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>11.63949275362319</v>
+        <v>11.70877513401992</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>8.197741619987561</v>
+        <v>8.267678241416213</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>11.02033728898262</v>
+        <v>11.09038300464479</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>15.64293854242128</v>
+        <v>15.71268380408337</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>17.01627256547165</v>
+        <v>17.08612691317892</v>
       </c>
     </row>
   </sheetData>
@@ -5831,76 +5831,76 @@
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.398342362365149</v>
+        <v>1.431616654683978</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.3861085145980141</v>
+        <v>-0.3524355059846727</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.072741745953522</v>
+        <v>1.108096169622009</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3589484327603643</v>
+        <v>0.395142150179268</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.006321352263682911</v>
+        <v>0.05935167763199445</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.71770746389457</v>
+        <v>-2.652232860908299</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.490573595948597</v>
+        <v>-3.42418154479865</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.8705775168294849</v>
+        <v>-0.8038422649140529</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.8290614518068509</v>
+        <v>-0.7623550829993491</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1536215002574366</v>
+        <v>-0.08599539671699574</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.019288491495587</v>
+        <v>3.086614970082614</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.638745312658351</v>
+        <v>5.706416291272284</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.064978731852371</v>
+        <v>3.133978862097329</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.64072337009339</v>
+        <v>8.710001434926113</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>2.184690681780715</v>
+        <v>2.254756688070181</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.678301456039783</v>
+        <v>5.747694334650859</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-3.151444412022187</v>
+        <v>-3.081874976239661</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.3578771034797867</v>
+        <v>-0.2881649554231629</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-1.591029302866808</v>
+        <v>-1.521548936817673</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.04528985507246119</v>
+        <v>0.1145722354691898</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.4979105539254931</v>
+        <v>-0.4279739324968403</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.5738656095681023</v>
+        <v>-0.5038198939059413</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.599460281551707</v>
+        <v>2.669205543213792</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>3.972794304602075</v>
+        <v>4.042648652309353</v>
       </c>
     </row>
     <row r="7">
@@ -5913,76 +5913,76 @@
         <v>92</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.500208362272538</v>
+        <v>-1.466934069953709</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.425485688300533</v>
+        <v>1.459158696913875</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.246654789431787</v>
+        <v>3.282009213100274</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.532861476238629</v>
+        <v>2.569055193657533</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.167591691214582</v>
+        <v>2.23326472111026</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.9061132609960225</v>
+        <v>-0.8406386580097518</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.765935914789189</v>
+        <v>-2.699543863639242</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.95753403856861</v>
+        <v>-1.890798786653178</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.8290614518068509</v>
+        <v>-0.7623550829993491</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5159403408371475</v>
+        <v>-0.4483142372967066</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.8453754480173217</v>
+        <v>0.912701926604349</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.914107631498943</v>
+        <v>4.981778610112876</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>4.876572934750918</v>
+        <v>4.945573064995877</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.829129167194829</v>
+        <v>6.898407232027552</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>3.996284884679262</v>
+        <v>4.066350890968728</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>5.678301456039783</v>
+        <v>5.747694334650859</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.9775313685439215</v>
+        <v>-0.9079619327613955</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.004441737099924126</v>
+        <v>0.07415388515654797</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-3.040304665185651</v>
+        <v>-2.970824299136517</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.4076086956521721</v>
+        <v>0.4768910760489007</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1355917133457822</v>
+        <v>-0.06565509191712948</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.298503290727517</v>
+        <v>-1.228457575065356</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.06322839749373799</v>
+        <v>0.132973659155823</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>2.161200101703528</v>
+        <v>2.231054449410806</v>
       </c>
     </row>
     <row r="8">
@@ -5995,76 +5995,76 @@
         <v>110</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0377577693871558</v>
+        <v>-0.004483477068326636</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.44524853415033</v>
+        <v>1.478921542763672</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.641911706427834</v>
+        <v>3.677266130096321</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.928118393234676</v>
+        <v>2.96431211065358</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.381030426392449</v>
+        <v>4.446703456288127</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.931831403035595</v>
+        <v>0.9973060060218657</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1589652709815681</v>
+        <v>0.225357322131515</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.7895015345539136</v>
+        <v>0.8562367864693456</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.740108508667461</v>
+        <v>1.806814877474963</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.9662730978980321</v>
+        <v>1.033899201438473</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.240632365013369</v>
+        <v>1.307958843600396</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.597902097902107</v>
+        <v>4.66557307651604</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>6.200683606687683</v>
+        <v>6.269683736932642</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.706599522926048</v>
+        <v>8.775877587758771</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>6.229486465706948</v>
+        <v>6.299552471996414</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>6.824546515328329</v>
+        <v>6.893939393939405</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>3.054089184815766</v>
+        <v>3.123658620598292</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>2.040014859629565</v>
+        <v>2.109727007686189</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>2.25613802256138</v>
+        <v>2.325618388610515</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>4.261363636363633</v>
+        <v>4.330646016760362</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.718163227365679</v>
+        <v>3.788099848794332</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>2.73311726263217</v>
+        <v>2.803162978294331</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>3.916983338205199</v>
+        <v>3.986728599867284</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>5.659223817118551</v>
+        <v>5.729078164825829</v>
       </c>
     </row>
     <row r="9">
@@ -6077,76 +6077,76 @@
         <v>133</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.546301856878621</v>
+        <v>-2.513027564559792</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.629800823965773</v>
+        <v>1.663473832579115</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.445739457624008</v>
+        <v>2.481093881292495</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.235705542927086</v>
+        <v>3.27189926034599</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.374195156399281</v>
+        <v>4.439868186294959</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.561359769406067</v>
+        <v>4.626834372392338</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.036613938103919</v>
+        <v>3.103005989253866</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.509938991833479</v>
+        <v>3.576674243748911</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.303334756104228</v>
+        <v>4.370041124911729</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.529499345334798</v>
+        <v>3.597125448875239</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.803858612450135</v>
+        <v>3.871185091037162</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.532283505967712</v>
+        <v>6.599954484581644</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.159671986728704</v>
+        <v>6.228672116973662</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.442074574190578</v>
+        <v>7.511352639023301</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>6.031263635905155</v>
+        <v>6.101329642194621</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>6.626323685526536</v>
+        <v>6.695716564137612</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>2.73283149513702</v>
+        <v>2.802400930919546</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.875968379793612</v>
+        <v>1.945680527850236</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2.843971241973556</v>
+        <v>2.91345160802269</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>4.534774436090231</v>
+        <v>4.60405681648696</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.991574027092277</v>
+        <v>4.06151064852093</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>3.163739272201539</v>
+        <v>3.2337849878637</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>4.190394137931797</v>
+        <v>4.260139399593882</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>5.618212197159572</v>
+        <v>5.688066544866849</v>
       </c>
     </row>
     <row r="10">
@@ -6159,76 +6159,76 @@
         <v>174</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2258455436818352</v>
+        <v>-0.192571251363006</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4.036680091099129</v>
+        <v>4.07035309971247</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.321117558047483</v>
+        <v>4.35647198171597</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.331462175888795</v>
+        <v>5.367655893307699</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.115617678221071</v>
+        <v>6.181290708116748</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.877494934906025</v>
+        <v>6.942969537892296</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.52991615917383</v>
+        <v>5.596308210323777</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.676648869977114</v>
+        <v>4.743384121892547</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.718164934999749</v>
+        <v>4.78487130380725</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.794904236873997</v>
+        <v>2.862530340414438</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.494550860311172</v>
+        <v>2.561877338898199</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.2384454625834</v>
+        <v>6.306116441197332</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.263379531452578</v>
+        <v>6.332379661697537</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.616735364096378</v>
+        <v>6.686013428929101</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>6.532516768737231</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>3.545207262140735</v>
+        <v>3.614776697923261</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>2.865511202367287</v>
+        <v>2.935223350423911</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.231059652655432</v>
+        <v>4.300540018704567</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>4.418103448275865</v>
+        <v>4.487385828672593</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3.87490303927791</v>
+        <v>3.944839660706563</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>4.373660627313463</v>
+        <v>4.443706342975624</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>5.797861081151915</v>
+        <v>5.867606342814</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>6.296632385561601</v>
+        <v>6.366486733268879</v>
       </c>
     </row>
     <row r="11">
@@ -6241,322 +6241,322 @@
         <v>211</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.250049210362945</v>
+        <v>1.758213919431881</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.810608292875017</v>
+        <v>3.571545899538975</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.844841478077981</v>
+        <v>2.880195901746468</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.500716411330323</v>
+        <v>4.536910128749227</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.135446626306276</v>
+        <v>4.201119656201953</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.270478537891265</v>
+        <v>5.335953140877535</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.549745107259035</v>
+        <v>3.616137158408982</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.849389513873177</v>
+        <v>1.916124765788609</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.364839228184906</v>
+        <v>2.431545596992407</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.591003817415476</v>
+        <v>1.658629920955917</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.865363084530813</v>
+        <v>1.93268956311784</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.903804726079606</v>
+        <v>4.971475704693539</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.675048104748875</v>
+        <v>5.744048234993834</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.927624943003615</v>
+        <v>5.996903007836337</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5.742627353255408</v>
+        <v>5.812693359544873</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>6.337687402876789</v>
+        <v>6.407080281487865</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>3.359991812993265</v>
+        <v>3.429561248775791</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2.781074747608891</v>
+        <v>2.850786895665514</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>5.366866156986212</v>
+        <v>5.436346523035347</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>5.553909952606645</v>
+        <v>5.623192333003374</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>5.010709543608691</v>
+        <v>5.080646165037344</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>5.408688137255176</v>
+        <v>5.478733852917337</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>7.579197900893696</v>
+        <v>7.648943162555781</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>7.503256561625228</v>
+        <v>7.573110909332506</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.0055</t>
+          <t>X &lt; -0.005501</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>254</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.0513687903276363</v>
+        <v>-0.3589938315786796</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.683616465431648</v>
+        <v>2.225926475815115</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.818719150951807</v>
+        <v>2.563010735685289</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.860831349569679</v>
+        <v>4.810903019744487</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.28296313934878</v>
+        <v>5.106239998177607</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.470127752355566</v>
+        <v>5.535602355341837</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.51615925809682</v>
+        <v>3.582551309246767</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.056502250373534</v>
+        <v>2.123237502288966</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.098018315396168</v>
+        <v>2.164724684203669</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.111584479429887</v>
+        <v>2.179210582970327</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.992242959143653</v>
+        <v>2.05956943773068</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.256456142282914</v>
+        <v>5.324127120896847</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>6.100468860803637</v>
+        <v>6.169468991048596</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.304308900162994</v>
+        <v>4.373586964995717</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>4.03907844852727</v>
+        <v>4.109144454816736</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>4.240437710747074</v>
+        <v>4.30983058935815</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>2.531540866991854</v>
+        <v>2.60111030277438</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>2.032856663494996</v>
+        <v>2.10256881155162</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>3.823782976033108</v>
+        <v>3.893263342082243</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>4.798228346456696</v>
+        <v>4.867510726853425</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>4.255027937458742</v>
+        <v>4.324964558887395</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>5.753876031422429</v>
+        <v>5.82392174708459</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>7.209753560109284</v>
+        <v>7.279498821771369</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>7.133812220840817</v>
+        <v>7.203666568548094</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.00491</t>
+          <t>X &lt; -0.004911</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>312</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.916932907348247</v>
+        <v>-2.221288753810512</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.765707176805378</v>
+        <v>-2.076889734566592</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.3207922562761283</v>
+        <v>-0.4930080401778483</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.209004174120452</v>
+        <v>1.198243784075693</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1178040724420555</v>
+        <v>-0.2323555039209992</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.67192464312884</v>
+        <v>1.73739924611511</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2580328700491634</v>
+        <v>0.3244249211991104</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.9820602370078575</v>
+        <v>-0.9153249850924254</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.902082633523683</v>
+        <v>-1.835376264716182</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.393866762241835</v>
+        <v>-1.326240658701394</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.7989946746136738</v>
+        <v>-0.7316681960266465</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.088578088578096</v>
+        <v>3.156249067192029</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.566650972655047</v>
+        <v>3.635651102900006</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.422217238543766</v>
+        <v>1.491495303376489</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.724824461044939</v>
+        <v>1.794890467334405</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1.678858869640678</v>
+        <v>1.748251748251754</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.2627138934404627</v>
+        <v>0.3322833292229888</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.1577304773451829</v>
+        <v>0.2274426254018067</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.65590492232829</v>
+        <v>1.725385288377424</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.483974358974365</v>
+        <v>2.553256739371093</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.261286770489228</v>
+        <v>2.331223391917881</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.826357355872254</v>
+        <v>2.896403071534415</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>4.062670983892843</v>
+        <v>4.132416245554928</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>3.986729644624376</v>
+        <v>4.056583992331653</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.00432</t>
+          <t>X &lt; -0.004321</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>379</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.042542458382378</v>
+        <v>-1.297097113431967</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.238848371582456</v>
+        <v>-1.495206157212593</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.886992107436406</v>
+        <v>-2.010501599556228</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2261152359329941</v>
+        <v>-0.2210851692318911</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.382941749189229</v>
+        <v>-1.46238745280278</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.178893048514126</v>
+        <v>1.244367651500397</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.6493820545161597</v>
+        <v>-0.5829900033662128</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.983345671010966</v>
+        <v>-1.916610419095534</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.205681848732397</v>
+        <v>-2.138975479924895</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.396403803037444</v>
+        <v>-1.328777699497003</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.122044535922107</v>
+        <v>-1.05471805733508</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.29279295901987</v>
+        <v>2.360463937633803</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.48756295425305</v>
+        <v>2.556563084498009</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.738501657730566</v>
+        <v>1.807779722563289</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.8157181759492076</v>
+        <v>0.8857841822386732</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.619221497338394</v>
+        <v>0.6886143759494701</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.04257668229865885</v>
+        <v>0.0269927534838672</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.1475600983939387</v>
+        <v>-0.07784795033731484</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.387824278258201</v>
+        <v>1.457304644307335</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.630277044854878</v>
+        <v>2.699559425251607</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>2.350928878600989</v>
+        <v>2.420865500029642</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>3.066530551190574</v>
+        <v>3.136576266852735</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>4.132862445904891</v>
+        <v>4.202607707566976</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>4.320773349380495</v>
+        <v>4.390627697087773</v>
       </c>
     </row>
     <row r="15">
@@ -6569,1716 +6569,1716 @@
         <v>463</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.985949362740044</v>
+        <v>-1.188821527078019</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.207572782464084</v>
+        <v>-1.411521347679212</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3734034319974597</v>
+        <v>-0.5956558087785098</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2086995831031189</v>
+        <v>0.09657898540972809</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.020501087450079</v>
+        <v>-1.193570248501707</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.326490739379594</v>
+        <v>1.267682181570457</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.09432355682129412</v>
+        <v>-0.02793150567134717</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.02082636648673</v>
+        <v>-0.9540911145712982</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.5473448586995175</v>
+        <v>-0.4806384898920157</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.6732321053220716</v>
+        <v>-0.6056060017816307</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.1828901168244528</v>
+        <v>-0.1155636382374254</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.345791357670407</v>
+        <v>2.41346233628434</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.30121374609471</v>
+        <v>2.370213876339669</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.215926049531205</v>
+        <v>1.285204114363928</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.204942974640765</v>
+        <v>1.275008980930231</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.152054860115285</v>
+        <v>1.221447738726361</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.277935162327374</v>
+        <v>-0.208365726544848</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.2650295857242071</v>
+        <v>0.3347417337808309</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.561066355567476</v>
+        <v>1.630546721616611</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.748110151187909</v>
+        <v>1.817392531584638</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.284823349101394</v>
+        <v>2.354759970530047</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3.288781900370232</v>
+        <v>3.358827616032393</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4.211505230999229</v>
+        <v>4.281250492661314</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.999494777259933</v>
+        <v>5.069349124967211</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.003141</t>
+          <t>X &lt; -0.003142</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>555</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.598852588546492</v>
+        <v>-2.751167398129475</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.124198177127624</v>
+        <v>-2.282219277200674</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.031731197430901</v>
+        <v>-2.199357246527057</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.126819474652834</v>
+        <v>-1.207097874709895</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.851801489892708</v>
+        <v>-1.982100714451526</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.04593184091469737</v>
+        <v>-0.08152539596932229</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.178510203184558</v>
+        <v>-1.112118152034611</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.996633194026856</v>
+        <v>-1.929897942111424</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.775261013896312</v>
+        <v>-1.70855464508881</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.189384194449914</v>
+        <v>-2.121758090909474</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.274737157550405</v>
+        <v>-2.207410678963377</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.03584544951450397</v>
+        <v>0.03182552909942871</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.2785122528616526</v>
+        <v>0.3475123831066114</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4168676720431321</v>
+        <v>0.4861457368758551</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.4773608934374849</v>
+        <v>0.5474268997269505</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.1865718626965389</v>
+        <v>-0.1171789840854629</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.1408094417375452</v>
+        <v>-0.07124000595501911</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.5821934018081194</v>
+        <v>0.5433437506554597</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.7983165647399346</v>
+        <v>0.7592351315797856</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.165540540540547</v>
+        <v>1.125937056655722</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.703421212623674</v>
+        <v>1.662527579337166</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.168006697521598</v>
+        <v>2.238052413183759</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>2.983322404544275</v>
+        <v>3.05306766620636</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.62810178599652</v>
+        <v>3.697956133703798</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.002551</t>
+          <t>X &lt; -0.002552</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>665</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.326816016529243</v>
+        <v>-2.450370922955777</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.88485913928568</v>
+        <v>-3.006920484061965</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.445994381478258</v>
+        <v>-2.577822065290384</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.20783574271946</v>
+        <v>-1.268599969792135</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.323856278494254</v>
+        <v>-2.420471285138113</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.085640614436429</v>
+        <v>-1.103007473601963</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.408056296039994</v>
+        <v>-1.341664244890048</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.536460791408416</v>
+        <v>-1.469725539492984</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.945395176836229</v>
+        <v>-1.878688808028727</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.268780137155211</v>
+        <v>-2.20115403361477</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.994420870039875</v>
+        <v>-1.927094391452847</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.3215628215628143</v>
+        <v>-0.2538918429488817</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.355747761751843</v>
+        <v>0.4247478919968017</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.8851417014682426</v>
+        <v>0.9544197663009655</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.376360612581081</v>
+        <v>0.4464266188705466</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.2297805389987317</v>
+        <v>-0.1603876603876557</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.0635739328473548</v>
+        <v>0.00599550293517126</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.3722089812973763</v>
+        <v>0.351605249564436</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.340211843477313</v>
+        <v>1.318247381239516</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.67763157894737</v>
+        <v>1.655243341357689</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.585558989498281</v>
+        <v>1.563147623842106</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.659979873705296</v>
+        <v>1.730025589367457</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.08513098003705</v>
+        <v>2.154876241699135</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.159565580618214</v>
+        <v>2.229419928325491</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.001961</t>
+          <t>X &lt; -0.001962</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>764</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.958906841381477</v>
+        <v>-3.05869963607104</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.967630253728458</v>
+        <v>-3.068888160486438</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.385112117206155</v>
+        <v>-2.495355023069578</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.273612079682245</v>
+        <v>-1.321402175060712</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.073040925983996</v>
+        <v>-3.146392654363254</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.973229637618672</v>
+        <v>-1.978546266705408</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.224583383753533</v>
+        <v>-2.158191332603586</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.112003739832716</v>
+        <v>-2.045268487917284</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.070487674810082</v>
+        <v>-2.00378130600258</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.062054506700761</v>
+        <v>-1.99442840316032</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.91807333606522</v>
+        <v>-1.850746857478192</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.023764371221993</v>
+        <v>-0.9560933926080608</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.06817205044730912</v>
+        <v>0.1371721806922679</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.368327625332121</v>
+        <v>0.437605690164844</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.2309087722139864</v>
+        <v>0.300974778503452</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.7385683359221247</v>
+        <v>-0.6691754573110487</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.1431574327963929</v>
+        <v>-0.1512021118895746</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.7447088584412143</v>
+        <v>0.6566038596477881</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.82539075935339</v>
+        <v>1.654763819450871</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.881544502617807</v>
+        <v>1.711231532939102</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.861904303043929</v>
+        <v>1.770535168044269</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.916839299757342</v>
+        <v>1.905955610498722</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.322504518595487</v>
+        <v>2.392249780257572</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.377453231683049</v>
+        <v>2.447307579390326</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001371</t>
+          <t>X &lt; -0.001372</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>902</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.454823160136769</v>
+        <v>-3.531676807755112</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.844642694269986</v>
+        <v>-3.920979103038619</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.141305076788946</v>
+        <v>-3.225459153372945</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.147389157520401</v>
+        <v>-2.238316585951026</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.224095724989212</v>
+        <v>-3.392212014206294</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.985879331654196</v>
+        <v>-2.159065613576971</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.594998204836216</v>
+        <v>-1.772644675870481</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.094303402231148</v>
+        <v>-2.210069844193718</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.052787337208514</v>
+        <v>-2.107882759689637</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.385121644225194</v>
+        <v>-2.378950352535668</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.890011825233479</v>
+        <v>-1.822685346646452</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.065352969326476</v>
+        <v>-0.9976819907125432</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.4238397728025802</v>
+        <v>-0.3548396425576215</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.09332020414598219</v>
+        <v>-0.02404213931325927</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.02037548838403325</v>
+        <v>0.09044149467349882</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.3125705112914758</v>
+        <v>-0.3085490668272115</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.2825686699324095</v>
+        <v>0.2197854518244498</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.462143118967127</v>
+        <v>1.329072783323362</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.411348665576909</v>
+        <v>2.207215819876829</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.487527716186257</v>
+        <v>2.351740943932647</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>2.055192052199388</v>
+        <v>1.988019398271412</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.090101741567864</v>
+        <v>2.091394126990586</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>2.364876908049993</v>
+        <v>2.434622169712078</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>2.17807082377044</v>
+        <v>2.247925171477718</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0007815</t>
+          <t>X &lt; -0.0007826</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1070</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.150575699379608</v>
+        <v>-2.214904151150456</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.80781817732673</v>
+        <v>-2.870651536091174</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.165001084758778</v>
+        <v>-2.23391945850863</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.903531438415158</v>
+        <v>-1.975305467340377</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.311193012818947</v>
+        <v>-2.445766954187832</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.424383810322475</v>
+        <v>-1.561927736206329</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.217754573704852</v>
+        <v>-1.358193262344138</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.351424453955723</v>
+        <v>-1.492248062015499</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.774592403802977</v>
+        <v>-1.862407466446179</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.804933390780583</v>
+        <v>-1.841796531400114</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.716447729613193</v>
+        <v>-1.701241797912225</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.34498401227026</v>
+        <v>-1.277313033656327</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.6107391712778423</v>
+        <v>-0.5417390410328835</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.6462223763642427</v>
+        <v>-0.5769443115315198</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.1198459734243471</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.04188314439743834</v>
+        <v>-0.08307986932521771</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.0658658517648405</v>
+        <v>-0.03112340035473693</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.9494449817462609</v>
+        <v>0.793403925563851</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.689123337899645</v>
+        <v>1.530692384382192</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>2.120327102803742</v>
+        <v>1.960576607584805</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.670584637731011</v>
+        <v>1.568325215226594</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.688087526013639</v>
+        <v>1.643054430126071</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.495572972869603</v>
+        <v>1.508161415417753</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.326173689675905</v>
+        <v>1.396028037383182</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0001916</t>
+          <t>X &lt; -0.0001928</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.745109060071783</v>
+        <v>-1.794693267278127</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.194625105723304</v>
+        <v>-2.243522295153603</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.894128760060852</v>
+        <v>-1.946770849872863</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.102465871688331</v>
+        <v>-2.155895361134462</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.122487727280514</v>
+        <v>-3.221646712062039</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.42919951028037</v>
+        <v>-2.530247521531663</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.997482931978269</v>
+        <v>-2.101465777489118</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.07811959528599</v>
+        <v>-2.182503282433132</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.916017973545976</v>
+        <v>-2.020936318697281</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.068735371893048</v>
+        <v>-2.131370849966359</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.949655607883308</v>
+        <v>-1.968996758936605</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.384029014463799</v>
+        <v>-2.359605003743503</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.111004705000632</v>
+        <v>-2.042004574755673</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.633603752059827</v>
+        <v>-1.564325687227104</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.159790923570448</v>
+        <v>-1.13551246306853</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.063195602584877</v>
+        <v>-1.084603801995108</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.9961407409005432</v>
+        <v>-1.063241435866992</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.5881358059042796</v>
+        <v>-0.7022436303713988</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.1699939125339185</v>
+        <v>-0.2851042221120892</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.2193837753510124</v>
+        <v>0.1033025981261204</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.3553588789433135</v>
+        <v>-0.4708318809545133</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.04099387213470607</v>
+        <v>-0.1110256368288773</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.4687948180647581</v>
+        <v>-0.4914121214534788</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.2324801073722611</v>
+        <v>-0.209086634493417</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0003982</t>
+          <t>X &lt; 0.0003969</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.534555902129995</v>
+        <v>-1.572560836347272</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.033012335414888</v>
+        <v>-2.07023626394998</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.054139111574209</v>
+        <v>-2.093458871397914</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.875191753083385</v>
+        <v>-1.916070664466041</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.270634740124201</v>
+        <v>-2.34783840737817</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.849482395451254</v>
+        <v>-1.927595179748891</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.991488373193164</v>
+        <v>-2.070441802935903</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.638348393296013</v>
+        <v>-1.718721237037492</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.42757093300272</v>
+        <v>-1.508516655678356</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.473411638279096</v>
+        <v>-1.51804027256177</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.199052371163759</v>
+        <v>-1.20661184677995</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.742871622090682</v>
+        <v>-1.712493301550346</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.676098777043748</v>
+        <v>-1.607098646798789</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.793099453594117</v>
+        <v>-1.761996186382362</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.684845722979126</v>
+        <v>-1.692144778469867</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.581530166610435</v>
+        <v>-1.627208551430925</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.743521963160347</v>
+        <v>-1.827307025271395</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.610836281261406</v>
+        <v>-1.695209777383042</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.289618546450995</v>
+        <v>-1.374604516383762</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.130319148936167</v>
+        <v>-1.215531943210699</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.501700076329954</v>
+        <v>-1.586817204954841</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.205873174360939</v>
+        <v>-1.291971634768572</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.624776700556829</v>
+        <v>-1.709435700948177</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.300984528832629</v>
+        <v>-1.347807715251534</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.0009881</t>
+          <t>X &lt; 0.0009867</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1745</v>
+        <v>1748</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7862391860452433</v>
+        <v>-0.8159883563698216</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.658022132859713</v>
+        <v>-1.686194855817959</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.764190128245438</v>
+        <v>-1.793733458550328</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.256381168462845</v>
+        <v>-1.287887302836161</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.703996918566801</v>
+        <v>-1.762500703085912</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.201770372814906</v>
+        <v>-1.261256960756398</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.943307456291159</v>
+        <v>-2.002018476672859</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.849394532426288</v>
+        <v>-1.908678389109475</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.719401264835497</v>
+        <v>-1.77898638142505</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.892421991872759</v>
+        <v>-1.952523802020309</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.95955390290198</v>
+        <v>-1.987495701854151</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.320714592924155</v>
+        <v>-2.348226086231399</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.444745038740962</v>
+        <v>-2.472688793835793</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.405663356725647</v>
+        <v>-2.433829040274539</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.689768836891204</v>
+        <v>-2.750481159710539</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-2.63269715424412</v>
+        <v>-2.692931593842758</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.391630144398718</v>
+        <v>-2.452616955677293</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-2.521024101409388</v>
+        <v>-2.581886965569744</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.157812806483783</v>
+        <v>-2.21931756533855</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.052345537757439</v>
+        <v>-2.113936797685469</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.505492910428984</v>
+        <v>-2.566710389511051</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.319470470367946</v>
+        <v>-2.381252606121265</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.527403220794533</v>
+        <v>-2.588457220601555</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.259505018515732</v>
+        <v>-2.288396351504517</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.001578</t>
+          <t>X &lt; 0.001576</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2054</v>
+        <v>2058</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.146437245904863</v>
+        <v>-1.166075369078293</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.263632180510733</v>
+        <v>-1.283316219474088</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.9911660591800526</v>
+        <v>-1.012488559658365</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5215177950707499</v>
+        <v>-0.5443063161554136</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.004664438318343</v>
+        <v>-1.045921395990078</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7907028194986268</v>
+        <v>-0.8322613437767004</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.295316806188005</v>
+        <v>-1.336526577101779</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.546906019244943</v>
+        <v>-1.587876477316051</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.381733400028004</v>
+        <v>-1.423023301711986</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.548233671927889</v>
+        <v>-1.589828422289152</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.391641021977001</v>
+        <v>-1.433360677052775</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.59500470487886</v>
+        <v>-1.636578877809839</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.772021654153164</v>
+        <v>-1.814151229454282</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.013978348814604</v>
+        <v>-2.055843882260568</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-2.063379175680275</v>
+        <v>-2.105690084189547</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.82812961552434</v>
+        <v>-1.870471413065793</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.982742009220679</v>
+        <v>-2.024921612727717</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.962632977969726</v>
+        <v>-2.004966438402597</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.864132188043939</v>
+        <v>-1.906523681631398</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.940597667638485</v>
+        <v>-1.982730228720634</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.261418688045111</v>
+        <v>-2.303382661902155</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-2.212054297325395</v>
+        <v>-2.254206836357042</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-2.055146721516103</v>
+        <v>-2.097425225908687</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.005642961672272</v>
+        <v>-2.048110632771127</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.002168</t>
+          <t>X &lt; 0.002166</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2366</v>
+        <v>2369</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.057964017722334</v>
+        <v>-1.048873869284805</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.245477824917742</v>
+        <v>-1.278007851555934</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.238691561272212</v>
+        <v>-1.229542542402733</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5886079650675455</v>
+        <v>-0.5803433176351618</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9725049271429071</v>
+        <v>-0.9766253087491918</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.097607279087654</v>
+        <v>-1.101562867040556</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.42765205629879</v>
+        <v>-1.431276069623422</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.766791878162671</v>
+        <v>-1.770025839793277</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.449918599881279</v>
+        <v>-1.453557300682448</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.906148598053079</v>
+        <v>-1.909296922622111</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.902399466543052</v>
+        <v>-1.905536309441359</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.905653219782735</v>
+        <v>-1.950821868312346</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.660256462918774</v>
+        <v>-1.705870120974161</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.773198456871924</v>
+        <v>-1.818719072411653</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.986781476876793</v>
+        <v>-2.032124261698826</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.788458003320677</v>
+        <v>-1.834021748830338</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.603229897282077</v>
+        <v>-1.649068652128982</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.768048914707386</v>
+        <v>-1.813717968390357</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.527459232145112</v>
+        <v>-1.573439587953771</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.90664556962026</v>
+        <v>-1.952156726219371</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.919044647073093</v>
+        <v>-1.96462129178515</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-2.012736545721651</v>
+        <v>-2.058230373187598</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-2.220436487427548</v>
+        <v>-2.265668791770615</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-2.229810225761639</v>
+        <v>-2.275066276633929</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.002758</t>
+          <t>X &lt; 0.002756</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2618</v>
+        <v>2622</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.156135794240008</v>
+        <v>-1.164476603034991</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.9789938900920916</v>
+        <v>-0.9877267862144663</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.6934081461334003</v>
+        <v>-0.7030867746606688</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.6662023731861666</v>
+        <v>-0.6761806290064598</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.275879974545262</v>
+        <v>-1.293890671280643</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.63679875284798</v>
+        <v>-1.654209145493283</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.781693690550256</v>
+        <v>-1.799169874809479</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.039241476421438</v>
+        <v>-2.056438104977346</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.634887175481282</v>
+        <v>-1.652694896027995</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.66566942766152</v>
+        <v>-1.683717021488825</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.673917926959959</v>
+        <v>-1.691868653380801</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.77956074343907</v>
+        <v>-1.797462748706579</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.589350626861197</v>
+        <v>-1.607953248186298</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.522402829363962</v>
+        <v>-1.54119895272202</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.550213849204646</v>
+        <v>-1.569215020488308</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.465974844499975</v>
+        <v>-1.484906095172249</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.425564494837921</v>
+        <v>-1.444618290774855</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.584569397576644</v>
+        <v>-1.603431979445403</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.53688176740846</v>
+        <v>-1.555753380085186</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.518401983218922</v>
+        <v>-1.5372484649955</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.543534251042978</v>
+        <v>-1.562549501855017</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.673544777617664</v>
+        <v>-1.692402431905236</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.75832646081593</v>
+        <v>-1.776970148962995</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.6975370690541</v>
+        <v>-1.716313971641824</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.003347</t>
+          <t>X &lt; 0.003346</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2827</v>
+        <v>2830</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5162266689086934</v>
+        <v>-0.5388492164813883</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4115433226415277</v>
+        <v>-0.4342494377284893</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4279299687509166</v>
+        <v>-0.4504721435556718</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.349654062619976</v>
+        <v>-0.337123296044993</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.83586090434288</v>
+        <v>-0.8288318192471564</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.9454652897268261</v>
+        <v>-0.9383426150200194</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.9252950537850921</v>
+        <v>-0.91811108161086</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.184085905090505</v>
+        <v>-1.176600369347426</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.9116732071536688</v>
+        <v>-0.9044808566678739</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.102460702620355</v>
+        <v>-1.094984573014919</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.124924613219669</v>
+        <v>-1.117456051037152</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.137472073541112</v>
+        <v>-1.129961438230296</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9733826371460026</v>
+        <v>-0.965924723596622</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9627054407038997</v>
+        <v>-0.9552363687072898</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.036829728676963</v>
+        <v>-1.029212458036575</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.091118067002924</v>
+        <v>-1.083509513742072</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.9928730272840696</v>
+        <v>-0.9853553826702068</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.9712484975568287</v>
+        <v>-0.9637439501289151</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.228710462287097</v>
+        <v>-1.220958491299697</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.233000706464146</v>
+        <v>-1.225265961169967</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.119613836559793</v>
+        <v>-1.11194186734339</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.104088303099381</v>
+        <v>-1.096426133159198</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.232817356149944</v>
+        <v>-1.225050084182676</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.394189695438932</v>
+        <v>-1.386244674878633</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.003937</t>
+          <t>X &lt; 0.003935</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2979</v>
+        <v>2983</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.6428089473897032</v>
+        <v>-0.6468351373840591</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2605465038672961</v>
+        <v>-0.2651413826636499</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1823307178145939</v>
+        <v>-0.1872781139419359</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.05594888218553962</v>
+        <v>0.05055919690065735</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3906355327318209</v>
+        <v>-0.3997625360806083</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.7186069140693903</v>
+        <v>-0.727270650244229</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.5717059269793481</v>
+        <v>-0.5807032839290898</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6310478659621026</v>
+        <v>-0.6400195413975212</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6373737285342145</v>
+        <v>-0.64633570776369</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.8910910548219562</v>
+        <v>-0.8998527323134624</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.9652499879278125</v>
+        <v>-0.9738714756131017</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.8241215487955671</v>
+        <v>-0.8329851265496799</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.5916544899982412</v>
+        <v>-0.6010273822754755</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.559193232328056</v>
+        <v>-0.5686535910523816</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.5625300853457631</v>
+        <v>-0.5721052820142845</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.5501377224292341</v>
+        <v>-0.5596334457919241</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.4635385324100838</v>
+        <v>-0.4731793240657467</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.4481837089710083</v>
+        <v>-0.4578693304019481</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.5808105516526112</v>
+        <v>-0.5902876598256483</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.6086573918873555</v>
+        <v>-0.6180711515751511</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.5285290474956028</v>
+        <v>-0.5381499228673619</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.6516529487063139</v>
+        <v>-0.6611281744390354</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.8267628484940062</v>
+        <v>-0.8359621142443387</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.9165032419921957</v>
+        <v>-0.925601382914401</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.004527</t>
+          <t>X &lt; 0.004525</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3085</v>
+        <v>3089</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4566181882475817</v>
+        <v>-0.4596131802700114</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5493677282483631</v>
+        <v>-0.5522873640479347</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.4908518596905367</v>
+        <v>-0.4940288129028048</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.252967831329812</v>
+        <v>-0.2565423002941145</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5357924414613535</v>
+        <v>-0.5421815325968637</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.7173057955698567</v>
+        <v>-0.7234418653536281</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5051224143827113</v>
+        <v>-0.5116326679170697</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.7009267730301474</v>
+        <v>-0.7072239074261262</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.7378973564351767</v>
+        <v>-0.7441457598258836</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.9449005944954081</v>
+        <v>-0.9509834634313066</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.071709908594237</v>
+        <v>-1.077598861106246</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.912709344256001</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.791329548116174</v>
+        <v>-0.7977649434192671</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.8322461225431752</v>
+        <v>-0.8386608263924131</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.6965286956023391</v>
+        <v>-0.7032059058426725</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.7612043002963986</v>
+        <v>-0.7677273216504759</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.6822391698825854</v>
+        <v>-0.6888854245038942</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.6710818728194781</v>
+        <v>-0.6777601416749448</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.8241797179505355</v>
+        <v>-0.8306371205861609</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.7799854321786981</v>
+        <v>-0.7864806328590106</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.6889257975989906</v>
+        <v>-0.695611782394657</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.7133002654180132</v>
+        <v>-0.7199686943035388</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.8729771873353585</v>
+        <v>-0.8794084992795206</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.059503160927711</v>
+        <v>-1.065706849447686</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.005117</t>
+          <t>X &lt; 0.005115</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3153</v>
+        <v>3157</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4940206500832929</v>
+        <v>-0.4961930253816504</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.4659898337809452</v>
+        <v>-0.4682316500642543</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5655695331895174</v>
+        <v>-0.5678279828391979</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3481042810340185</v>
+        <v>-0.3507077766042741</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7273038622697143</v>
+        <v>-0.731908863382138</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7748283830943876</v>
+        <v>-0.7793582745794225</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6153392888119598</v>
+        <v>-0.6201487785730819</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.812954072319485</v>
+        <v>-0.8175448368868103</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.8798409862820407</v>
+        <v>-0.8843464202437161</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.9727572434057592</v>
+        <v>-0.9772243328638766</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.059373377822453</v>
+        <v>-1.063707345100497</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9413769484859529</v>
+        <v>-0.9458902471593404</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.846782201840071</v>
+        <v>-0.8515283842794759</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.8283644066000022</v>
+        <v>-0.8331587816186001</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.709734970668201</v>
+        <v>-0.7147471891762862</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.6969512845623953</v>
+        <v>-0.7019244578486337</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.5909050614443032</v>
+        <v>-0.596028771655476</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.6455300481375517</v>
+        <v>-0.6505983451146591</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.6956726746577999</v>
+        <v>-0.7006595712537802</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.6483607855559157</v>
+        <v>-0.6533924060632472</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.6342967334593013</v>
+        <v>-0.6394030280756269</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.6914613283489643</v>
+        <v>-0.6965060769302909</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.8734703425465185</v>
+        <v>-0.8782607489726004</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.962464041486534</v>
+        <v>-0.9671524338438005</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.005707</t>
+          <t>X &lt; 0.005705</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3211</v>
+        <v>3215</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4892110779833274</v>
+        <v>-0.4907544636481447</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.5914187886289639</v>
+        <v>-0.592862095285021</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4985023349763082</v>
+        <v>-0.5001695368325514</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4834344612151185</v>
+        <v>-0.4851750328057491</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.738586798487944</v>
+        <v>-0.741917446618487</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.688991255259964</v>
+        <v>-0.6923714677570629</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.6701436622165815</v>
+        <v>-0.6736075743581367</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.7452760522844102</v>
+        <v>-0.748670222337374</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.7481967384722594</v>
+        <v>-0.7515864734960545</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.8223104116157103</v>
+        <v>-0.8256689170333402</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.9023859070371643</v>
+        <v>-0.9056268272343431</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.8225136638105894</v>
+        <v>-0.8258769051725636</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.8119003332705574</v>
+        <v>-0.8153638874826186</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.7356967712795779</v>
+        <v>-0.7392739273927376</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.7242120097306639</v>
+        <v>-0.7278556037987727</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.66987580668021</v>
+        <v>-0.6735443168890285</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.5681493597347824</v>
+        <v>-0.5719567509947439</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.5304206110234944</v>
+        <v>-0.5342852979218833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.5135363329338603</v>
+        <v>-0.5174081500681851</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.4636469673405941</v>
+        <v>-0.4675691262823634</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.4595818651273902</v>
+        <v>-0.463552786947794</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.5170312816340257</v>
+        <v>-0.5209390930878257</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.6596044575606754</v>
+        <v>-0.663316628536144</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.7794387349043248</v>
+        <v>-0.7830100579933372</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.006297</t>
+          <t>X &lt; 0.006294</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3255</v>
+        <v>3259</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1963910823828883</v>
+        <v>-0.197824566204666</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.3016374757811491</v>
+        <v>-0.3029631376275574</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3818423173261891</v>
+        <v>-0.3831551559347233</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3459968045446473</v>
+        <v>-0.3473960043482265</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.572043378239087</v>
+        <v>-0.5746510281536032</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.5205475653837013</v>
+        <v>-0.5232088773248762</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4817326618924085</v>
+        <v>-0.4844883877141939</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.6512588667690054</v>
+        <v>-0.6538256701579925</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.470066637287502</v>
+        <v>-0.4728541401293072</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4923325362964661</v>
+        <v>-0.4951400452909738</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.5675349878296245</v>
+        <v>-0.5702363108783857</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.5230039320948379</v>
+        <v>-0.5257779142846672</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.5582096739447238</v>
+        <v>-0.5610085066036419</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.516566285232102</v>
+        <v>-0.5194309580850955</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.5140518587137421</v>
+        <v>-0.5169602686289494</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.4523598452433788</v>
+        <v>-0.4553106825834092</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3537476135789817</v>
+        <v>-0.3568290484993071</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.2872132633667235</v>
+        <v>-0.2903843663914927</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.2675652680130653</v>
+        <v>-0.2707497040811049</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2771172138692819</v>
+        <v>-0.2802809049235222</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.1883047675000995</v>
+        <v>-0.1916114270542835</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.2459208929488241</v>
+        <v>-0.2491634134984864</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.4134834922616264</v>
+        <v>-0.4165062021405177</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.563370792572826</v>
+        <v>-0.5662159856386211</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.006886</t>
+          <t>X &lt; 0.006884</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3288</v>
+        <v>3292</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1555469569437875</v>
+        <v>-0.1566842175043632</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2932848358029787</v>
+        <v>-0.2942720711058655</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3568245225894486</v>
+        <v>-0.357802332983006</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.4191389443491431</v>
+        <v>-0.4200752411250832</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.5558802589306993</v>
+        <v>-0.5578268970794369</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.5030253312766746</v>
+        <v>-0.5050285174606941</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4723096568137848</v>
+        <v>-0.4743871763437113</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5823892864894518</v>
+        <v>-0.5843480217091681</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4328472065225881</v>
+        <v>-0.4349862606067916</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4323283007033751</v>
+        <v>-0.4345053522655462</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4131364653686163</v>
+        <v>-0.4153254364161043</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4020979020978999</v>
+        <v>-0.4043146628632286</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4481631512830546</v>
+        <v>-0.4503779150091134</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5000822125610114</v>
+        <v>-0.5022458635930178</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.5041832615933615</v>
+        <v>-0.5063741067262981</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4371481007352287</v>
+        <v>-0.4393939393939377</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3712108565692631</v>
+        <v>-0.3735443885780541</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.245683655577146</v>
+        <v>-0.24817585355202</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.1936866744543195</v>
+        <v>-0.196233432604366</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1404921020656147</v>
+        <v>-0.1430962603799699</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.1491332561568726</v>
+        <v>-0.151753924139868</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.1765262853092509</v>
+        <v>-0.1791188564465216</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.3092252358294587</v>
+        <v>-0.3116453614280204</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.3975114184488078</v>
+        <v>-0.3998293796345749</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.007476</t>
+          <t>X &lt; 0.007474</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3321</v>
+        <v>3325</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1454132717795034</v>
+        <v>-0.1462234575179906</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2551838483041848</v>
+        <v>-0.2558748828006046</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.3023785933382257</v>
+        <v>-0.303063164040509</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3112492430201215</v>
+        <v>-0.3119482508085767</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4502161713212161</v>
+        <v>-0.4516219025635451</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3960021889489411</v>
+        <v>-0.3974673331128216</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.403156848959604</v>
+        <v>-0.4046410457483631</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.5448488618282425</v>
+        <v>-0.5461740322838864</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4263401505869524</v>
+        <v>-0.4278067882844283</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4334815702224546</v>
+        <v>-0.4349673617677112</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.5017464319545084</v>
+        <v>-0.5031419788844929</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4636040527129666</v>
+        <v>-0.4650559588178282</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.550380455300747</v>
+        <v>-0.5517681924329523</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.5439667825787069</v>
+        <v>-0.5453708789169696</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.6446604084399397</v>
+        <v>-0.6459675149153128</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.6024722454243019</v>
+        <v>-0.6038103810381017</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.5385681578415813</v>
+        <v>-0.5399886564943728</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4153776588828748</v>
+        <v>-0.4169507576586398</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3618032664562705</v>
+        <v>-0.3634343004421652</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.2772556390977385</v>
+        <v>-0.2789828644215433</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.2912449336670306</v>
+        <v>-0.2929753260308416</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.3492562771593697</v>
+        <v>-0.3509206897658999</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.4779594673336263</v>
+        <v>-0.4794606528523317</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.5059509659424037</v>
+        <v>-0.5074221769376663</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.008066</t>
+          <t>X &lt; 0.008064</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.117512040012798</v>
+        <v>-0.1180525604420311</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.140337537056844</v>
+        <v>-0.140859327831528</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1702310736864803</v>
+        <v>-0.1707519655521068</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1853359364759655</v>
+        <v>-0.1858562395147771</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2372592957548463</v>
+        <v>-0.2383210627612939</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2411630112767114</v>
+        <v>-0.2422164045648785</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1660185338122204</v>
+        <v>-0.167180152256492</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3088595638071894</v>
+        <v>-0.3098590577635534</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2206758050580362</v>
+        <v>-0.2217796733747832</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2048737344672205</v>
+        <v>-0.2060155291262973</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2700151325544624</v>
+        <v>-0.2710737627481308</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2643691426028596</v>
+        <v>-0.2654418544988957</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.3306018835508056</v>
+        <v>-0.3316234526098398</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.326155879957291</v>
+        <v>-0.3271887367042723</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.4020070407865717</v>
+        <v>-0.4029661746363971</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.473891872720074</v>
+        <v>-0.4747519801043438</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.441498015357503</v>
+        <v>-0.4424005433193017</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3501061900089013</v>
+        <v>-0.3511206837476308</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.324856668087655</v>
+        <v>-0.3258967629046339</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2393815201192169</v>
+        <v>-0.2405196440153006</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1686476361893625</v>
+        <v>-0.1698837994811555</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.2267829624037603</v>
+        <v>-0.2279524656897465</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.3220055964877844</v>
+        <v>-0.3230557754713246</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.3503798290115085</v>
+        <v>-0.3513987353232082</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/macd/macd_6_13.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/macd/macd_6_13.xlsx
@@ -618,2379 +618,2379 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.008744</t>
+          <t>X ≈ -0.008727</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-10.09311771823484</v>
+        <v>-3.51860992888129</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.848768889108314</v>
+        <v>8.654839098182464</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.742205153282164</v>
+        <v>7.41011949069275</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.036505106992465</v>
+        <v>6.823508444136792</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.70535654183486</v>
+        <v>6.551565548592968</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.569750520629775</v>
+        <v>2.56547718063814</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.52260696943911</v>
+        <v>1.77523810078943</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-5.126970039033253</v>
+        <v>1.472167801912846</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.7588685392269738</v>
+        <v>5.748066124904305</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.528839662723286</v>
+        <v>4.956968417009257</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.587484012506742</v>
+        <v>-3.071908806751658</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.797369846755551</v>
+        <v>4.955051587963013</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.34598816130282</v>
+        <v>12.15158816608612</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.458710724617767</v>
+        <v>3.598824645083319</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>9.475414722849827</v>
+        <v>11.23101640185002</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.733644940518289</v>
+        <v>7.637421946866823</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>5.602140874103583</v>
+        <v>7.53644405674644</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>1.159033963827554</v>
+        <v>3.246698414759976</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-7.307637655376787</v>
+        <v>-4.859082761162412</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>1.561969658795356</v>
+        <v>3.677167979585484</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>1.020390628523337</v>
+        <v>3.111343240948351</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-3.400323392290893</v>
+        <v>-1.127027259049207</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-7.473495517584439</v>
+        <v>-0.8838081902336583</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-3.203728159284843</v>
+        <v>3.120469701362715</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.008155</t>
+          <t>X ≈ -0.008138</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.41905306691244</v>
+        <v>2.688918527980356</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.569248478917835</v>
+        <v>2.445075607102552</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.661024994006411</v>
+        <v>7.409564099696034</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.954190044519905</v>
+        <v>6.82302185061576</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>15.66964520733933</v>
+        <v>18.98039525143345</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>10.33523493607431</v>
+        <v>12.92612833637927</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15.09778478800876</v>
+        <v>12.1390341815777</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>14.82531502077916</v>
+        <v>11.83907500099649</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>14.87091335157398</v>
+        <v>11.96980904762039</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.573490123939735</v>
+        <v>4.956722044885723</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.315058240865397</v>
+        <v>-0.996517172482271</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3.037914876005964</v>
+        <v>-1.27278454491919</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>12.99377912119559</v>
+        <v>10.07461650435331</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>18.3159956088783</v>
+        <v>16.06136483264806</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>17.66541491873402</v>
+        <v>15.38612022513062</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>12.72143351266371</v>
+        <v>9.715554103449819</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>23.67975448289376</v>
+        <v>22.08908136366242</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>12.49114847582733</v>
+        <v>9.48541788684696</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>29.35216393355238</v>
+        <v>28.42449685347312</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>23.99863347456487</v>
+        <v>22.40468023499481</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>23.463830542112</v>
+        <v>21.84447856720527</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>23.39512507715681</v>
+        <v>21.77592892409184</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>23.67655278590298</v>
+        <v>22.02600019037424</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>23.60786604361372</v>
+        <v>21.87046970136272</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.007565</t>
+          <t>X ≈ -0.00755</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-14.40970536557542</v>
+        <v>-11.79415163072552</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.528883895507114</v>
+        <v>4.514477574990572</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.219957195000013</v>
+        <v>-0.8718772460410165</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.713727699676298</v>
+        <v>6.822525919158203</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.381037359927689</v>
+        <v>6.55033026350133</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>21.86567473967308</v>
+        <v>23.28570388675872</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>16.77896162803111</v>
+        <v>18.35640657764694</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>16.50707141496663</v>
+        <v>18.05837349220288</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>16.55322942921374</v>
+        <v>18.19100889136993</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>15.78872257603463</v>
+        <v>17.40390259741982</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>16.06645721567023</v>
+        <v>17.68028423680494</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>15.79319433719861</v>
+        <v>17.4096343530024</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>6.011742359403904</v>
+        <v>7.997767256024837</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.458310955498945</v>
+        <v>3.598371959156175</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>5.138684215183737</v>
+        <v>7.074846183804546</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>5.73320274211234</v>
+        <v>7.636950516628076</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.263044530174625</v>
+        <v>3.378032774824646</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.158870168495888</v>
+        <v>3.246503527624213</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>5.716026441656545</v>
+        <v>7.622026998831174</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>5.904322855690722</v>
+        <v>7.838598270564248</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>5.364123190400967</v>
+        <v>7.274093899751676</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>5.290010210413605</v>
+        <v>7.201231362607707</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.566024783678486</v>
+        <v>7.446985009370955</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>5.491924014627209</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.006975</t>
+          <t>X ≈ -0.006961</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.283928581754758</v>
+        <v>6.412913986689404</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11.797721079282</v>
+        <v>11.13607075451065</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.37235045000958</v>
+        <v>9.892523975699042</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12.09087178569597</v>
+        <v>11.79136414986021</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>11.76049883737382</v>
+        <v>11.52074227599697</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>14.3756371588191</v>
+        <v>14.1666809077905</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>13.61248103867209</v>
+        <v>13.38039429066669</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8.485593747117989</v>
+        <v>8.105291858099676</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6.101567438948599</v>
+        <v>5.746391735592724</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.4768975851825914</v>
+        <v>-0.02304113916251538</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.679295416446607</v>
+        <v>-2.241994524032322</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.332264877935046</v>
+        <v>4.954029572622531</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.645455368365312</v>
+        <v>6.336148475805736</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.995468607138363</v>
+        <v>3.598142543367267</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>8.205195994385569</v>
+        <v>7.905509582083688</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>8.800658331780326</v>
+        <v>8.46788253613758</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>6.236368836663686</v>
+        <v>5.872556672118016</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>6.133735006372007</v>
+        <v>5.741814146894512</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>8.786421059581791</v>
+        <v>8.4538629931766</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>4.103637171430321</v>
+        <v>3.676826111477787</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.562930125410944</v>
+        <v>3.111109536942699</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>8.363346128921471</v>
+        <v>8.033969982608262</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>11.07861051925585</v>
+        <v>10.77925609730533</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>8.567215637110742</v>
+        <v>8.120469701362715</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.006385</t>
+          <t>X ≈ -0.006372</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>10.95512660261584</v>
+        <v>12.22412998460688</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.318152225514766</v>
+        <v>2.291907715476533</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.037417906812948</v>
+        <v>-1.37736751430748</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.6244945852631361</v>
+        <v>2.881223888130521</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-5.082923962648081</v>
+        <v>-4.666350010583983</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.211051342457239</v>
+        <v>-4.511825181125516</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-5.667608283752841</v>
+        <v>-7.72990846300948</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-11.32450047972114</v>
+        <v>-12.88941237249029</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-8.596502963348989</v>
+        <v>-10.33822415328854</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.986251463569623</v>
+        <v>-6.276474377654736</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.022608694332618</v>
+        <v>-3.577883819053007</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.301338930719332</v>
+        <v>-6.285236086293722</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.965989337295483</v>
+        <v>-2.536667758423434</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.746562609345141</v>
+        <v>-2.784859984877109</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2.091233035336309</v>
+        <v>-3.465846867672049</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>2.684823258308924</v>
+        <v>-2.906954719507397</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>2.552566182223281</v>
+        <v>-3.010976022863439</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>2.448841433474058</v>
+        <v>-3.144406839668612</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>10.76060367497698</v>
+        <v>4.374475266666479</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>10.95062103107502</v>
+        <v>4.590211430925088</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>10.41208762789145</v>
+        <v>4.024820264915093</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>10.33957643208013</v>
+        <v>3.951003816607468</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>16.02095660475932</v>
+        <v>11.5106532852348</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>13.24750568325212</v>
+        <v>8.913152628191988</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.005796</t>
+          <t>X ≈ -0.005784</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-10.80284125713131</v>
+        <v>-8.583763906656394</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.214059573753119</v>
+        <v>-2.750896300732819</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.190687609844829</v>
+        <v>-1.970561495420363</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.35514741143524</v>
+        <v>1.495638791272086</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>9.616609857801421</v>
+        <v>1.222580382812382</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.476522542791287</v>
+        <v>1.378876095974597</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.398255426981073</v>
+        <v>-1.44082321805945</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.123139430377641</v>
+        <v>-1.74403649042798</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.8506633704950985</v>
+        <v>-5.679900197574014</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.712396974339264</v>
+        <v>-2.410194597545996</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.670695254591728</v>
+        <v>-4.172381587195652</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>7.026748451212001</v>
+        <v>1.649650271972803</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8.227145807518632</v>
+        <v>2.572823283930113</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.58192613676016</v>
+        <v>-7.845912524310641</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-4.239175619815668</v>
+        <v>-8.528451059459684</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-5.96732459376949</v>
+        <v>-10.00691552656533</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.461348524267194</v>
+        <v>-6.040483396666438</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.566308990366572</v>
+        <v>-6.174879024320056</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.673378199630442</v>
+        <v>-8.000525857549086</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.157472738169815</v>
+        <v>-3.712124759579837</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.615954107410694</v>
+        <v>-4.280062204137259</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>7.512783932246457</v>
+        <v>1.762160338506789</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>5.464761725073259</v>
+        <v>-0.03385941104772172</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>5.390811780048345</v>
+        <v>1.844959497281081</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.005206</t>
+          <t>X ≈ -0.005194</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-10.47663265326329</v>
+        <v>-11.78933907156396</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-21.0960244608826</v>
+        <v>-18.65871248704471</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-13.95481220446061</v>
+        <v>-13.28866259335616</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-14.66469961228806</v>
+        <v>-15.53860340793953</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-23.56979999977139</v>
+        <v>-22.44337145532594</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-14.81298273198298</v>
+        <v>-12.35189772185152</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-13.86971498114822</v>
+        <v>-14.80327984716629</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-14.15025147971546</v>
+        <v>-11.79433447843926</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-19.26105257292419</v>
+        <v>-19.96416963777874</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-16.60378592443219</v>
+        <v>-17.44452777760248</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-12.90215342799895</v>
+        <v>-15.51915995473158</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-6.314850188827393</v>
+        <v>-7.499146331460281</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-7.436180376598408</v>
+        <v>-6.951823563179161</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-11.09554700137566</v>
+        <v>-8.862247623600005</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-8.316842899952647</v>
+        <v>-4.559482459898753</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-9.446298928677876</v>
+        <v>-4.001038467496478</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-9.582527350035697</v>
+        <v>-4.105592945486478</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-7.969276152708105</v>
+        <v>-2.575950416695335</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-7.756463733327642</v>
+        <v>-2.362866565888474</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-7.572347267329064</v>
+        <v>-2.149350908488231</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-6.394157646842778</v>
+        <v>-1.051737721210792</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-9.918035403853743</v>
+        <v>-4.458393774711745</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-9.646722559617857</v>
+        <v>-4.216199469790112</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-9.725467289719624</v>
+        <v>-4.379530298637277</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.004616</t>
+          <t>X ≈ -0.004606</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.058818966179501</v>
+        <v>1.999416373313977</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.242153391896792</v>
+        <v>-2.381504630162723</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-9.090953323320377</v>
+        <v>-10.52608674914458</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-6.833183021302702</v>
+        <v>-9.73906739787283</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-7.166157235905892</v>
+        <v>-8.634605321769392</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.04637893124945</v>
+        <v>-4.340591244337212</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.782046785261961</v>
+        <v>-6.51267850088756</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.544445120788502</v>
+        <v>-9.581120337659868</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.534437803896104</v>
+        <v>-6.691916846656298</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.333850736513561</v>
+        <v>-4.721726351137619</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.547880130268304</v>
+        <v>-3.069391543087022</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.341238321416959</v>
+        <v>-1.964153940768384</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.460866088783959</v>
+        <v>-3.075899702520267</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.269400119864017</v>
+        <v>2.213777865671737</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-3.33832933744592</v>
+        <v>-4.005019905182905</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-4.235148855622334</v>
+        <v>-4.831777101512216</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.391536360095749</v>
+        <v>-2.165208755916289</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.496595475041651</v>
+        <v>0.4738211942860744</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.2083034787276361</v>
+        <v>2.074460834402672</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>3.376078796160733</v>
+        <v>5.063524918032549</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.835279951502152</v>
+        <v>4.498398300792871</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>4.25201133965404</v>
+        <v>5.81276923069634</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>4.527846446928763</v>
+        <v>6.058264471832821</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>5.946174501325153</v>
+        <v>7.287136368029699</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.004026</t>
+          <t>X ≈ -0.004018</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7049549566271338</v>
+        <v>0.9963670133365099</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.041932571630234</v>
+        <v>0.7527838127155064</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.796607220789213</v>
+        <v>6.2780108650351</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.529611120635145</v>
+        <v>2.304319738048072</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.00713921210546431</v>
+        <v>0.9031687652674165</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.380986908426848</v>
+        <v>2.186775701567242</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.46271467171001</v>
+        <v>1.398485998883636</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.371767011477111</v>
+        <v>2.226596151020665</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.967664957976169</v>
+        <v>6.877654951157567</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.64554573231981</v>
+        <v>2.693987839862778</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.104365723720861</v>
+        <v>2.965514690682433</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.640698147946949</v>
+        <v>1.557326050383161</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.522589766747174</v>
+        <v>0.4469327405468562</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.069751871762499</v>
+        <v>-2.065123735485557</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>3.021635780523624</v>
+        <v>1.786099339171997</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>3.615541729529319</v>
+        <v>2.346486139678724</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.267292733742401</v>
+        <v>-2.29090857610219</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.191885179807386</v>
+        <v>-0.1562672636923423</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.407826785213018</v>
+        <v>0.05746346054540652</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-2.160395320582346</v>
+        <v>-4.267695715519089</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>2.054111965563166</v>
+        <v>-0.2949812383844517</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>4.358397147975985</v>
+        <v>3.036649125438295</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>4.634337523791075</v>
+        <v>2.145328257003541</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>8.131675567422953</v>
+        <v>6.529560610453366</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.003436</t>
+          <t>X ≈ -0.003429</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-10.68702983262071</v>
+        <v>-11.43021548422225</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.700037425414742</v>
+        <v>-5.891143450273688</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-10.30680606548643</v>
+        <v>-9.708198754182703</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-7.78015640852761</v>
+        <v>-7.164121591650101</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.956918062044203</v>
+        <v>-6.393268797145289</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-6.847875613678838</v>
+        <v>-8.334225109838862</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.544021455548766</v>
+        <v>-5.986428949489991</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-6.826873143613035</v>
+        <v>-5.244356866030756</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7.868797553101366</v>
+        <v>-6.166283695674565</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-9.7315228289429</v>
+        <v>-6.960569063186888</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-12.7058282551525</v>
+        <v>-9.836091135577028</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-11.9053839934159</v>
+        <v>-9.068538907013433</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-9.791320891741158</v>
+        <v>-7.036497190271028</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.517335664475794</v>
+        <v>-0.9918907422367838</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-3.09801388843912</v>
+        <v>-0.622966656171549</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-6.836950179799622</v>
+        <v>-4.262297521843252</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.6165110850366489</v>
+        <v>2.983658213199718</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>1.596755961752315</v>
+        <v>4.952687779339158</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-3.610037648221308</v>
+        <v>-0.08585560699130923</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-2.336418255642116</v>
+        <v>1.179593634174907</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.798140968351007</v>
+        <v>1.664691086151961</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-3.400366077701619</v>
+        <v>-1.56555517599012</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-3.127039223307214</v>
+        <v>-1.3224214474942</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-3.203728159284587</v>
+        <v>-1.484793456532266</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.002847</t>
+          <t>X ≈ -0.00284</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.9052168873335589</v>
+        <v>-0.8664767032012932</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-6.661690536150189</v>
+        <v>-5.58465119692994</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.476118387239914</v>
+        <v>-4.158390241996585</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.570677392793591</v>
+        <v>-1.567919797222508</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-4.615217831629572</v>
+        <v>-4.525163667228988</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-6.239147904955544</v>
+        <v>-5.268344517390553</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.486254179081435</v>
+        <v>-1.582195036676573</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.8536186753399875</v>
+        <v>1.697309264876523</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.723149587334007</v>
+        <v>-1.759087040950845</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.588339844117847</v>
+        <v>-1.655299345157232</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.5061685771024003</v>
+        <v>0.4082826140923572</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.691344474444804</v>
+        <v>-0.7661724477471239</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8119521112731647</v>
+        <v>1.711990274016173</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.310227633789168</v>
+        <v>4.158010445305749</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.06420448467092399</v>
+        <v>0.7855554407827938</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.3777719388851821</v>
+        <v>0.4475265905153023</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.395555639374507</v>
+        <v>1.242648354075769</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.6166187456328913</v>
+        <v>0.2111579772438859</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.137588506622293</v>
+        <v>4.921648744185461</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>4.325705444815384</v>
+        <v>5.137670771732331</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.059825460202042</v>
+        <v>1.872939234279436</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.8329105042865876</v>
+        <v>0.8983370528403114</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.376260478922148</v>
+        <v>-0.6588228544751615</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-5.180012744265085</v>
+        <v>-3.523674442781221</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.002257</t>
+          <t>X ≈ -0.002251</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-7.22061441047682</v>
+        <v>-7.329219146497117</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.543102861459602</v>
+        <v>-3.755576102480298</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.986498538903803</v>
+        <v>-2.137805620061926</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.7005307426709</v>
+        <v>-0.8188186360055383</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-8.074300174663541</v>
+        <v>-5.864125202696776</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-7.879836724523727</v>
+        <v>-5.712909488707453</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-7.659289819060085</v>
+        <v>-5.54922374546755</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.934820661700144</v>
+        <v>-3.943208332013974</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.879880969921473</v>
+        <v>-0.9483964919368333</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.6498297680645919</v>
+        <v>1.128918508908939</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.376964176536525</v>
+        <v>0.4428258146342259</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-5.681114601193627</v>
+        <v>-3.663373173279112</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.787524294091313</v>
+        <v>0.01197271588338111</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.018325192858164</v>
+        <v>-1.19381826842271</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.6680039684822745</v>
+        <v>1.001160713664262</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-4.098452142867856</v>
+        <v>-2.2730655971869</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.209921493572523</v>
+        <v>0.4993789071952364</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.720225479175966</v>
+        <v>4.204145737905044</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.955237734722687</v>
+        <v>5.379146208333637</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>2.129562261495366</v>
+        <v>3.675272379140452</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>3.186041084590592</v>
+        <v>4.070534167870456</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>3.109843025550724</v>
+        <v>3.997100090958902</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>3.985035278238236</v>
+        <v>4.242311847725404</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>3.910896346644009</v>
+        <v>4.082008162900962</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001667</t>
+          <t>X ≈ -0.001662</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-6.315338028108329</v>
+        <v>-6.641422487410431</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-8.827252172670867</v>
+        <v>-8.954924720402815</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-7.418411271352213</v>
+        <v>-6.762733779259264</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.421476059009592</v>
+        <v>-5.976492780549783</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.897017705324473</v>
+        <v>-3.791824184959545</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.248889257473962</v>
+        <v>-2.261346207704129</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.2847499296693812</v>
+        <v>1.087007791569825</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.193610881012319</v>
+        <v>-2.666680359175515</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.732997653697495</v>
+        <v>-2.54058995672515</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.540642471228196</v>
+        <v>-4.714819965223569</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.675902842746247</v>
+        <v>-2.373723434019325</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.233267199713396</v>
+        <v>-1.96041117024923</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.083264262175668</v>
+        <v>-3.764244935836977</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.583283261806287</v>
+        <v>-3.321727994375159</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.076451107426273</v>
+        <v>-1.926750076420902</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.689795872301964</v>
+        <v>0.7095631240378708</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>2.280340015333913</v>
+        <v>1.298293316172618</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>5.073463597141711</v>
+        <v>3.93671047861335</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>5.294888781609636</v>
+        <v>4.151878450508164</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>5.909135074046262</v>
+        <v>4.367990233640477</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>3.193746029484487</v>
+        <v>1.722404473609927</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>3.117914962985125</v>
+        <v>1.648206578424414</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.667875363016449</v>
+        <v>1.19847099037257</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.144097927671687</v>
+        <v>-0.3517525208593497</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001077</t>
+          <t>X ≈ -0.001074</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.893052068591437</v>
+        <v>4.477670308122164</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.769861408423644</v>
+        <v>3.093839032878407</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.094917874339131</v>
+        <v>4.128062788773548</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5920896810961196</v>
+        <v>0.1171059376724415</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.623005929148093</v>
+        <v>2.697674719449388</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.632175262721944</v>
+        <v>2.28024321079787</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8505738752614178</v>
+        <v>2.0613744782761</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.346900530944296</v>
+        <v>3.47229600903561</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.579029589429112</v>
+        <v>0.1744636399782209</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.009681379313143</v>
+        <v>1.668616481108636</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.083918563034558</v>
+        <v>0.2240623969498046</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.796743530973664</v>
+        <v>-2.340139024197683</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.554052513213442</v>
+        <v>-1.164117329333067</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.559574504705097</v>
+        <v>-3.129270348800731</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.25338094656594</v>
+        <v>-0.9478526310280913</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.129671026059349</v>
+        <v>1.329779188635015</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.383116624715022</v>
+        <v>-1.065830809081369</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.080256938636744</v>
+        <v>-1.773206975408137</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-2.103872717455999</v>
+        <v>-1.560381228374631</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.1298970733903602</v>
+        <v>-0.1990410409793526</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.6764539617762111</v>
+        <v>-0.7652105409775345</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.7525358479158655</v>
+        <v>-0.8403408276564406</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-3.451892364318475</v>
+        <v>-3.469181408053743</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-3.17784824210058</v>
+        <v>-3.632403861855671</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.0004877</t>
+          <t>X ≈ -0.0004848</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3481695479494036</v>
+        <v>0.7040652058899113</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9530810556510119</v>
+        <v>0.9295249739506701</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.487657631479415</v>
+        <v>-0.7915157315684596</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.084420265853794</v>
+        <v>-2.791899616503358</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-7.18631705820939</v>
+        <v>-6.355101482629408</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-7.468540297447014</v>
+        <v>-6.875131808889726</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-5.889102578462918</v>
+        <v>-5.787460624030139</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.69752023385869</v>
+        <v>-5.622560139716327</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.832737585634767</v>
+        <v>-2.202182181864984</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.607466353737628</v>
+        <v>-2.994506803085429</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.332600892879768</v>
+        <v>-3.19731218218039</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.846948223482073</v>
+        <v>-7.245332398115352</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-9.63349587923841</v>
+        <v>-9.30304165576014</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-6.563004435752191</v>
+        <v>-6.252633724676336</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-6.281624566157447</v>
+        <v>-5.992058849812274</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-6.162021228293163</v>
+        <v>-5.908031194211929</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-6.298780068490153</v>
+        <v>-6.014442836506838</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-8.293360470872976</v>
+        <v>-8.04140453794426</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-9.492563429571298</v>
+        <v>-9.723102486808841</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-9.305717619603271</v>
+        <v>-9.040300556982579</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-10.7916600139844</v>
+        <v>-10.55692391360912</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-8.980713522563306</v>
+        <v>-8.742696845605479</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-10.59303126291145</v>
+        <v>-10.39768682350113</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-8.310372950096976</v>
+        <v>-8.194696175414542</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0001021</t>
+          <t>X ≈ 0.0001039</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2809147457074488</v>
+        <v>0.1781156214593977</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.066668468806448</v>
+        <v>-0.9294372408979896</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.957239939825691</v>
+        <v>-2.173609539274651</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5256218573831006</v>
+        <v>0.2686009198357269</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.732336128431179</v>
+        <v>3.462424127299904</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.57222338716798</v>
+        <v>2.748505128568645</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.898046965574935</v>
+        <v>-0.2046899913139271</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.9695515822448328</v>
+        <v>2.523415405061741</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.460890333738277</v>
+        <v>2.650771913131358</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.034490907477043</v>
+        <v>3.16229115223689</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.20847875983052</v>
+        <v>4.300580287313593</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.02946353963992</v>
+        <v>3.160868088970219</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.9040507624426368</v>
+        <v>2.052180076387678</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.914985708892978</v>
+        <v>-1.671086405789168</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-4.926466776915568</v>
+        <v>-3.656543165194158</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-4.782728175710815</v>
+        <v>-3.969812992373591</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-6.271373793566326</v>
+        <v>-5.381018942271787</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-7.456202558243476</v>
+        <v>-7.258724775509826</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-7.69076162776949</v>
+        <v>-7.920425144500626</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-8.855267169152924</v>
+        <v>-9.453984374933434</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-8.046461985767493</v>
+        <v>-9.152775070715933</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-8.122307947176594</v>
+        <v>-9.66923808412681</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-8.748734135595349</v>
+        <v>-9.430650375763769</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-7.923665487917816</v>
+        <v>-8.287827241868726</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.0006918</t>
+          <t>X ≈ 0.0006926</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.879478573115591</v>
+        <v>4.524132500850286</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6690527306073051</v>
+        <v>1.156071937995229</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.03320245934560973</v>
+        <v>0.6969034015786093</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.590297573467119</v>
+        <v>2.845858713622327</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.837015795132658</v>
+        <v>2.577087200098241</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.849241975380657</v>
+        <v>3.900728200222126</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.619362101695792</v>
+        <v>-0.01306648002631761</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.126348583839956</v>
+        <v>-1.493386982849138</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.492022426699791</v>
+        <v>-2.151984328335168</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.683644735701392</v>
+        <v>-3.334981900005651</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-6.861058532431777</v>
+        <v>-5.814341737003083</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.328524204275929</v>
+        <v>-5.697757298315665</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-7.873431222042051</v>
+        <v>-7.595250742876466</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-6.620757894338148</v>
+        <v>-7.060919932868906</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-9.337808324863644</v>
+        <v>-10.10338998344923</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-9.308834713870638</v>
+        <v>-9.94512546025274</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-6.324925582084099</v>
+        <v>-6.906019121300396</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-8.069110548200449</v>
+        <v>-8.225178936254835</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-7.443383101702452</v>
+        <v>-7.623511139693804</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-7.666373357308096</v>
+        <v>-7.41482048158214</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-8.618755590847996</v>
+        <v>-8.774596607749139</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-9.104437617830861</v>
+        <v>-8.066478597988421</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-8.010290774201366</v>
+        <v>-7.828395319404287</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-8.086123027424541</v>
+        <v>-7.600874172155073</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.001281</t>
+          <t>X ≈ 0.001282</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.171499007174582</v>
+        <v>-3.680550054920886</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.005813755327331</v>
+        <v>0.5857113317952596</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.433761197919246</v>
+        <v>2.878839429512261</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.687972046616544</v>
+        <v>3.252404178419965</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.026907947970528</v>
+        <v>2.658855337180093</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.603279177636431</v>
+        <v>0.8799648279752219</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.439232469239982</v>
+        <v>1.567898319753489</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2249600861753649</v>
+        <v>-0.4792699177706865</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.589604980595162</v>
+        <v>0.2905158205004454</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.4587729023811988</v>
+        <v>0.4710043530921126</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.701343903151958</v>
+        <v>1.708714240633114</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.388220521594143</v>
+        <v>2.406772750918464</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.906180273654236</v>
+        <v>1.948791399783246</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.07162110405747768</v>
+        <v>0.08568434572178063</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.548819334166488</v>
+        <v>1.350207887280618</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.788367546432141</v>
+        <v>2.23044916724767</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.3963858933254869</v>
+        <v>-0.1431714426685957</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.259287124988241</v>
+        <v>1.020077609683646</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.1377247198938392</v>
+        <v>-1.040144458194391</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.241201490571008</v>
+        <v>-1.803290438404289</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.8160057230531734</v>
+        <v>-0.7458762711287434</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.537012974784858</v>
+        <v>-1.474613150817163</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.6729456086649463</v>
+        <v>-0.2574582371967509</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.6932092252034963</v>
+        <v>-1.724807171601448</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.001871</t>
+          <t>X ≈ 0.00187</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.264641325650615</v>
+        <v>-0.414663762081382</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.242504940720693</v>
+        <v>-1.618299497268993</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.680523989751684</v>
+        <v>-2.860557528337132</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.8211307423134357</v>
+        <v>-0.8892178787824037</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5138343981404105</v>
+        <v>-0.8293284752535826</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.899215478924027</v>
+        <v>-3.247442236548828</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.063447121013773</v>
+        <v>-2.094280444915952</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.984745382487098</v>
+        <v>-3.031657211217578</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.657084567131911</v>
+        <v>-1.627845178739776</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.037717284969006</v>
+        <v>-3.699135368253025</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-5.049831276247609</v>
+        <v>-4.402363048975758</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-4.042407046255079</v>
+        <v>-3.067713425391069</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.9855048044295387</v>
+        <v>-0.3048325437923083</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.2419534557957377</v>
+        <v>0.7414434141885593</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.543183570096595</v>
+        <v>-0.5812544916875311</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.591883464873817</v>
+        <v>-0.6765610363976364</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.8465466650297344</v>
+        <v>1.159110567786719</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.5444676722319599</v>
+        <v>-0.9188766918407154</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.6360539337727218</v>
+        <v>0.5880110320513836</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.749447523140248</v>
+        <v>-1.471768504830507</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.2803535757747468</v>
+        <v>-0.09150861588776138</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.7601226107147383</v>
+        <v>-1.145967563392546</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-3.379538573473837</v>
+        <v>-3.184854038079862</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-3.776914235057248</v>
+        <v>-3.67920456573826</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.002461</t>
+          <t>X ≈ 0.002458</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.257447903945796</v>
+        <v>-2.069792452658483</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.755601384660885</v>
+        <v>1.650616719184882</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.270151505590391</v>
+        <v>4.367922834601174</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.581142434800903</v>
+        <v>-1.777605985261303</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.288474409324529</v>
+        <v>-4.409932680358672</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-6.868306642199549</v>
+        <v>-6.626820258640365</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.268713824113547</v>
+        <v>-5.026765299991169</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.756411434874529</v>
+        <v>-4.52620149090513</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.529153501971614</v>
+        <v>-2.986395457353687</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4410138259443954</v>
+        <v>0.5974046866242091</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.3198165511102715</v>
+        <v>0.4653805549374681</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3541897693337219</v>
+        <v>-0.207206271336247</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.6868380021977956</v>
+        <v>0.2735260759441402</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.068367706335849</v>
+        <v>1.620688647562815</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.781765910731629</v>
+        <v>2.944008775354369</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.795125164690432</v>
+        <v>1.89784887610552</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.4754372767248114</v>
+        <v>0.590337616976413</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.3705965729035796</v>
+        <v>0.8578463889819758</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.389796631152286</v>
+        <v>-0.5377271231863432</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.35436143178017</v>
+        <v>2.080700499846436</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.207072180810144</v>
+        <v>2.718879919500885</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.735969302404953</v>
+        <v>1.8368321570033</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.800957848879094</v>
+        <v>3.285411341101721</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.515639429647919</v>
+        <v>3.92692131426594</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.003051</t>
+          <t>X ≈ 0.003047</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7.416845194260347</v>
+        <v>6.310546699165911</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>6.601299165141327</v>
+        <v>6.057611752118206</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.759433962264154</v>
+        <v>1.890422777186124</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.969556865898305</v>
+        <v>3.736422707521143</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.076074085658753</v>
+        <v>4.47464576109175</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>8.147655656371569</v>
+        <v>7.074666903795602</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10.26032235709655</v>
+        <v>8.729700539612395</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>9.982110912343472</v>
+        <v>8.443521726453895</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8.581290401950469</v>
+        <v>7.088262106133215</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.366067033606313</v>
+        <v>5.152408018129663</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.159357444998989</v>
+        <v>5.42167214787731</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.322915733858608</v>
+        <v>6.620311061743962</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.161292128541028</v>
+        <v>6.0048057498772</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.459444021325211</v>
+        <v>5.762753508185405</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.801300723744653</v>
+        <v>6.079457821088702</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.991841491841434</v>
+        <v>5.161498759376599</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.819462816402435</v>
+        <v>6.042610959551304</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>7.118468266427442</v>
+        <v>7.887845455608229</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.007436570428624</v>
+        <v>3.66619982293102</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>2.713513149627445</v>
+        <v>3.382983694882114</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>4.574813135507632</v>
+        <v>4.301683424311989</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>6.422044097175494</v>
+        <v>5.217313096682325</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.734980348119095</v>
+        <v>4.963792937836082</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.774532710280432</v>
+        <v>1.814499552108984</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.003641</t>
+          <t>X ≈ 0.003636</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.660454956569225</v>
+        <v>-1.882596562198124</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.887121186257453</v>
+        <v>3.069384988221721</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.717075993435593</v>
+        <v>5.071402801865588</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7.272095830202019</v>
+        <v>9.028623529150877</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.589900128896559</v>
+        <v>9.417620441841933</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.201702916301095</v>
+        <v>5.675006536527761</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.697728088619925</v>
+        <v>6.833770678141192</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.34108527131788</v>
+        <v>10.43654254242489</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.153814283297933</v>
+        <v>5.356628314854063</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.727303836019573</v>
+        <v>4.568721616014784</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.694173935697869</v>
+        <v>3.29112548863116</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.683398388459025</v>
+        <v>6.272103251500099</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.17461540657019</v>
+        <v>7.776563321072025</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.607131301365428</v>
+        <v>8.193183670799449</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>7.909772317510324</v>
+        <v>8.83610388690736</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>9.157754010695186</v>
+        <v>10.06500879808362</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>9.023836873717755</v>
+        <v>10.6333415246833</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>8.918996169896573</v>
+        <v>10.51492723015599</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>11.09567186454642</v>
+        <v>12.72204215605099</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>10.62892290327258</v>
+        <v>11.62632571171065</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>10.08637673530655</v>
+        <v>12.39576196486752</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>7.396151688930139</v>
+        <v>9.667619150339469</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>6.36343685892848</v>
+        <v>8.343891628069066</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>7.594794148188917</v>
+        <v>8.620469701362715</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.00423</t>
+          <t>X ≈ 0.004225</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.849718924303879</v>
+        <v>4.945148929489754</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-8.692605043857277</v>
+        <v>-9.357586258856955</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-9.187227866473151</v>
+        <v>-8.737062818110196</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-8.956785659500824</v>
+        <v>-10.27985441824107</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.575594999972601</v>
+        <v>-5.849110658882417</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6150439082148438</v>
+        <v>-1.936264554748988</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.443196087140088</v>
+        <v>1.013611105436397</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.608600263273416</v>
+        <v>-3.030789597531651</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.510509307773809</v>
+        <v>-3.838643654880528</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.396632530980078</v>
+        <v>-3.682479944491007</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.009365341648376</v>
+        <v>-5.279985059666394</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-3.344718518681226</v>
+        <v>-4.051914980740463</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-6.35467303836753</v>
+        <v>-6.133757887570198</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-8.462544367644306</v>
+        <v>-8.28899102595706</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-4.403706533149339</v>
+        <v>-3.328889481557084</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-6.639508290451687</v>
+        <v>-6.578464727501213</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-6.773425427429238</v>
+        <v>-7.661242161076743</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-6.87826613125042</v>
+        <v>-7.823144634861833</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-7.605770976741162</v>
+        <v>-7.641937459608833</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-5.53213271394295</v>
+        <v>-5.545576743923426</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-5.131282655493884</v>
+        <v>-4.222045603853239</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-2.376939937657703</v>
+        <v>-1.768718097318533</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-2.102465225175592</v>
+        <v>-1.525083612040078</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-5.008486157644207</v>
+        <v>-4.571837990944971</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.00482</t>
+          <t>X ≈ 0.004814</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.170258878137886</v>
+        <v>-3.419110513872639</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.37731726468877</v>
+        <v>3.593201152794435</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.943054725518657</v>
+        <v>-4.901412753062424</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.656008744961433</v>
+        <v>-5.525837674080528</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-9.403563923391026</v>
+        <v>-8.651616989751929</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.334244796117169</v>
+        <v>-5.584991438363467</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-5.576781715301642</v>
+        <v>-7.841781435193482</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-5.854993160054718</v>
+        <v>-8.119253830993706</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-7.28409421343413</v>
+        <v>-7.986750246708105</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.174656948294107</v>
+        <v>-4.402252462736996</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4300090708381106</v>
+        <v>-2.668309463535493</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.179346709580223</v>
+        <v>-4.415748751806902</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.302508776436341</v>
+        <v>-4.607312415577191</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.5824111822946918</v>
+        <v>-1.964896500509752</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.24055447987525</v>
+        <v>-2.685336856585884</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.295008912655973</v>
+        <v>0.7805318569879773</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.631680010972701</v>
+        <v>2.122693616168057</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.5856628365632375</v>
+        <v>-0.9696893740985431</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>5.213318923369876</v>
+        <v>3.67621026028452</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>5.400164733337903</v>
+        <v>5.365933512127071</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.91644209478364</v>
+        <v>1.808166583075355</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.3700078980804165</v>
+        <v>1.733004061120113</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.826105624731639</v>
+        <v>0.4841012329656067</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>3.509826827927476</v>
+        <v>4.799574178974659</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.00541</t>
+          <t>X ≈ 0.005402</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1925712513629492</v>
+        <v>0.8041229358916837</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-7.4238997738507</v>
+        <v>-8.271611495997625</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.207046694359633</v>
+        <v>2.826193003459949</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-7.850734911289948</v>
+        <v>-10.11356333374719</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.289973659699342</v>
+        <v>-3.354068389419403</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.069406319501489</v>
+        <v>2.099732881699836</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.599094088526797</v>
+        <v>-5.756124529711059</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.019246190858063</v>
+        <v>0.9894415001581365</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.509009234841734</v>
+        <v>4.64775810943123</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.460231489839671</v>
+        <v>5.605325422368452</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.734291132001694</v>
+        <v>5.872415974022601</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.731403797519121</v>
+        <v>3.83964297991966</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.159965868594142</v>
+        <v>-2.572116802652324</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.387162854216413</v>
+        <v>1.888547556350026</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-1.443394236467498</v>
+        <v>-4.149359412517306</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.875130616509928</v>
+        <v>-1.856731137321511</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.741213479532405</v>
+        <v>-1.998404058063187</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>5.808786568814725</v>
+        <v>3.225167657714302</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>9.472953811808019</v>
+        <v>7.033911641160245</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>9.659799621776045</v>
+        <v>7.256119722041348</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>9.117253453810015</v>
+        <v>7.886864005056353</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>9.041407492400914</v>
+        <v>7.811701483101025</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>11.04002013591744</v>
+        <v>11.69169960474309</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>9.240049951659692</v>
+        <v>11.52956061045362</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.005999</t>
+          <t>X ≈ 0.005992</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>21.35915288656803</v>
+        <v>22.43873045201992</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>21.02437608821822</v>
+        <v>22.14249943998126</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.222720675550896</v>
+        <v>3.386572252803148</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>9.782493928835422</v>
+        <v>5.29794079305973</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>11.71943072901537</v>
+        <v>7.425505039355741</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>11.90639691511281</v>
+        <v>7.607600733521203</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>13.40717550394974</v>
+        <v>9.291127372185912</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.310782241014834</v>
+        <v>1.449732623415329</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>19.98863305929318</v>
+        <v>16.61286701157227</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>23.76117192871122</v>
+        <v>20.77403281814786</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>24.03523157087306</v>
+        <v>21.02110574458487</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>21.48375489469791</v>
+        <v>15.77472544423499</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>18.08786555511443</v>
+        <v>12.13090049955192</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.59405940594063</v>
+        <v>9.404057787221355</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>14.93591610836001</v>
+        <v>10.42942953159665</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>15.53030303030303</v>
+        <v>11.00459269318902</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>15.39638589332559</v>
+        <v>10.92803430543811</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>17.56427246223164</v>
+        <v>13.36627942674883</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>17.78016384315597</v>
+        <v>13.62071647149872</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>13.42155510766946</v>
+        <v>10.41235046447913</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>19.69719075788525</v>
+        <v>17.53721365540605</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>19.62134479647614</v>
+        <v>17.46205113345079</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>17.62309223623089</v>
+        <v>15.14158305462654</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>15.2745327102803</v>
+        <v>12.41534149623451</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.006589</t>
+          <t>X ≈ 0.00658</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.934910462325611</v>
+        <v>7.253221022754495</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.5698306336727583</v>
+        <v>3.789321107465817</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.162114614944763</v>
+        <v>5.129782714916736</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-7.641748495407029</v>
+        <v>-7.158121213995194</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.113370122954827</v>
+        <v>-2.035755478662104</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.300336309052128</v>
+        <v>-1.740413568165714</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.528387625161777</v>
+        <v>0.3364767379406928</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.310782241014756</v>
+        <v>2.626712003874616</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.321966392626479</v>
+        <v>-2.643282961873702</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.579353746893062</v>
+        <v>-0.636566291003156</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>14.94432247996408</v>
+        <v>8.320789830867653</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>11.63527004621304</v>
+        <v>5.172235558057196</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.51210797935685</v>
+        <v>3.849730983859082</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.20012001200125</v>
+        <v>-5.152828337089659</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.5419767144206062</v>
+        <v>-5.904186871223793</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>1.13636363636364</v>
+        <v>-3.197963624706134</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-2.027856530916907</v>
+        <v>-4.177608543417364</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>3.927908825868009</v>
+        <v>3.538724882744951</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>7.174103237095359</v>
+        <v>8.614053612180257</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>13.42155510766946</v>
+        <v>14.7109929984157</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>3.788099848794332</v>
+        <v>5.320019085270218</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>8.186033033903222</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>10.04733466047338</v>
+        <v>11.37084398976983</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>16.03210846785613</v>
+        <v>17.09105793665683</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.007179</t>
+          <t>X ≈ 0.007168</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.9046074320225728</v>
+        <v>-0.4176267281105979</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.600133663975797</v>
+        <v>2.461466436185532</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.192417645247836</v>
+        <v>4.331772334293952</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.54006968641114</v>
+        <v>9.989370135485686</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>10.20427921386393</v>
+        <v>9.713811995386394</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.39124539996121</v>
+        <v>9.870745601384478</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.588993685767832</v>
+        <v>5.950663589151759</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.280479210711817</v>
+        <v>2.52074314574314</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2916633623234475</v>
+        <v>-0.4763279445727946</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4812523137130853</v>
+        <v>-1.27237943979209</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-9.298101762460298</v>
+        <v>-10.3751444251878</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.546548135605178</v>
+        <v>-7.526726379659095</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-10.70001323276437</v>
+        <v>-11.76661849710982</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.860486048604905</v>
+        <v>-5.764852558542934</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-14.60953843709455</v>
+        <v>-12.69700694042799</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-17.04545454545459</v>
+        <v>-15.26070292160833</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-17.17937168243206</v>
+        <v>-15.36458333333334</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-17.28421238625315</v>
+        <v>-15.49746743849494</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-17.06832100532883</v>
+        <v>-15.28300521134916</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-13.85117216505778</v>
+        <v>-11.94341876629018</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-14.39371833302389</v>
+        <v>-12.51086326767091</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-17.49986732473593</v>
+        <v>-15.7110257896262</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-17.22539261225388</v>
+        <v>-15.46739130434782</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-11.2406188048711</v>
+        <v>-9.379530298637285</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.007769</t>
+          <t>X ≈ 0.007758</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>30</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.025819553234697</v>
+        <v>6.457373271889402</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>12.69104275488486</v>
+        <v>12.87813310285219</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>14.58635703918726</v>
+        <v>14.95677233429395</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>13.87340301974444</v>
+        <v>14.36437013548573</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>23.53761254719714</v>
+        <v>24.08881199538639</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>17.05791206662795</v>
+        <v>17.57907893471781</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>26.28596338273763</v>
+        <v>26.7839969224851</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>26.00775193798445</v>
+        <v>26.4790764790765</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>22.7159057865658</v>
+        <v>23.27367205542725</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>25.27632344386274</v>
+        <v>25.81095389354125</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>25.55038308602469</v>
+        <v>26.08318890814559</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.93830034924325</v>
+        <v>22.47327362034095</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>24.14847161572055</v>
+        <v>24.69171483622352</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>23.92739273927396</v>
+        <v>24.44348077479041</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>26.60258277502675</v>
+        <v>23.76132639290535</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>13.86363636363642</v>
+        <v>10.98929707839167</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>10.39638589332561</v>
+        <v>7.552083333333321</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>6.95821185617099</v>
+        <v>4.085865894838371</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.840769903761966</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>4.027615713730015</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>13.48506954576406</v>
+        <v>10.61413673232909</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>13.40922358435488</v>
+        <v>10.5389742103738</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>17.01703163017025</v>
+        <v>14.11594202898551</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>16.94119937694699</v>
+        <v>13.95380303469602</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1477 +3180,1477 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.009039</t>
+          <t>X &gt; -0.009021</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3355</v>
+        <v>3379</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02924261372799464</v>
+        <v>-0.01528986744040139</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.0072010808152001</v>
+        <v>0.01917005276889228</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.02264770014926398</v>
+        <v>-0.04322766570604131</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.008078461736992892</v>
+        <v>-0.03104027934216447</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.001213771712095024</v>
+        <v>-0.02537281921043189</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.05425557883269505</v>
+        <v>0.03026135057494628</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.07006777182417068</v>
+        <v>0.04665887772655708</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.01645360910088556</v>
+        <v>0.02350455958702469</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.01560905066082796</v>
+        <v>0.02087299826754929</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.001761259238200807</v>
+        <v>0.007829814555094572</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.06323528293814462</v>
+        <v>-0.08622933084813411</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1169417059987552</v>
+        <v>-0.1395249641474052</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.0642437734654564</v>
+        <v>-0.08704622572339815</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1786003266002609</v>
+        <v>-0.1999735381829453</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.04624798200857327</v>
+        <v>-0.06787470902303028</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.1179277160543819</v>
+        <v>-0.138544669467791</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.06325085465810076</v>
+        <v>0.04076220712738632</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.005915912503489551</v>
+        <v>-0.01556197320689989</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.03124609423822733</v>
+        <v>0.00954798014020497</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.002353523145991687</v>
+        <v>-0.02444891704394792</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.008793984914319708</v>
+        <v>-0.01271128659462306</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.01035554741718414</v>
+        <v>-0.01115888634314643</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.05487937499456308</v>
+        <v>-0.04579367121172595</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.08314240149309882</v>
+        <v>-0.072042876322989</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.008449</t>
+          <t>X &gt; -0.008433</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3332</v>
+        <v>3355</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.04022591190335589</v>
+        <v>0.009771140450673954</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.04002462734528223</v>
+        <v>-0.04260522505224884</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.09005214661652872</v>
+        <v>-0.09654520125106814</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.07051106140109908</v>
+        <v>-0.08007430895871437</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.06131314662552967</v>
+        <v>-0.07242096252706176</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.02308619598115769</v>
+        <v>0.01212567846718571</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.07415886397575377</v>
+        <v>0.03429348239018992</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.05195743380289741</v>
+        <v>0.01314154384459698</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.02095508444456584</v>
+        <v>-0.0200964905668144</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.01232663174874205</v>
+        <v>-0.02757385950120295</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.02510271367641081</v>
+        <v>-0.06487126604286431</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.13705850243133</v>
+        <v>-0.1759690289016973</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1361031175529845</v>
+        <v>-0.1745953242042972</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1899022936404862</v>
+        <v>-0.2271482494790362</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1119737449772842</v>
+        <v>-0.1487013518429734</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.1583197241879901</v>
+        <v>-0.1941700640406765</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02501722007009022</v>
+        <v>-0.0128581697402339</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.002043785930013087</v>
+        <v>-0.03889856018490434</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.08190465553508375</v>
+        <v>0.04437574103179287</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.01315167236106873</v>
+        <v>-0.05092844178884093</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.001811174949438055</v>
+        <v>-0.03505921764113396</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.03389864934193554</v>
+        <v>-0.003176519444494375</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.003670440036707134</v>
+        <v>-0.03979893247654331</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.06160174350113579</v>
+        <v>-0.09488052218422638</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.00786</t>
+          <t>X &gt; -0.007844</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3314</v>
+        <v>3339</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.0001477921718660014</v>
+        <v>-0.003066942268837636</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.04876539859233731</v>
+        <v>-0.05452582802154637</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.121289137724311</v>
+        <v>-0.1325133799917566</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.09780273910374149</v>
+        <v>-0.113152936857233</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1467558896464638</v>
+        <v>-0.1637192732258796</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.03292426790589076</v>
+        <v>-0.04975633486812114</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.00744200103106607</v>
+        <v>-0.02371066591378934</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02828409805153598</v>
+        <v>-0.0435266009036539</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.05970250421214018</v>
+        <v>-0.0775503655626153</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.03417335100908048</v>
+        <v>-0.0514578770124956</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.04324480697205502</v>
+        <v>-0.06040695502068871</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.154303378958744</v>
+        <v>-0.1707132492502197</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2074181085902467</v>
+        <v>-0.2237080493486374</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2904171283554362</v>
+        <v>-0.3052004235772685</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.2085316797832064</v>
+        <v>-0.2231419464017037</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.228276138872161</v>
+        <v>-0.2416560139298127</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.1034635496133163</v>
+        <v>-0.1187674337517421</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.06990059362815515</v>
+        <v>-0.08453769260554367</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.07707683722421166</v>
+        <v>-0.09161765154055246</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1435717485966421</v>
+        <v>-0.1585324366461478</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1256228469603187</v>
+        <v>-0.1399027649779185</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.09298791544402008</v>
+        <v>-0.1075388096800722</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1322896367980064</v>
+        <v>-0.1455350169226719</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.19016252206724</v>
+        <v>-0.2001352701856547</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.00727</t>
+          <t>X &gt; -0.007255</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3291</v>
+        <v>3315</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1008547574189649</v>
+        <v>0.08229837674260665</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.0667799636984725</v>
+        <v>-0.08760458569040708</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.09963329897702522</v>
+        <v>-0.1271605194230716</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.131429357180906</v>
+        <v>-0.1633659964483059</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1783995373949381</v>
+        <v>-0.2123277766592011</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1859682597546666</v>
+        <v>-0.2187008432599882</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1247581005353027</v>
+        <v>-0.1567793880391193</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1438456832230415</v>
+        <v>-0.1745810812157345</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1758062521516166</v>
+        <v>-0.2098114280562413</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.144755729107537</v>
+        <v>-0.1778315275061217</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1558316032408982</v>
+        <v>-0.1888463482646827</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2657565687100742</v>
+        <v>-0.2979917839271664</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2508823111924556</v>
+        <v>-0.2832300425097074</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.3026385643714278</v>
+        <v>-0.3334615810993284</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.2459020734581472</v>
+        <v>-0.2759780595615666</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.2699394674235478</v>
+        <v>-0.2986956992189249</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.1130137428175573</v>
+        <v>-0.1440836343568179</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.07848817415955978</v>
+        <v>-0.1086538281366174</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.1175634295712982</v>
+        <v>-0.1474630426744667</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.1858390156578977</v>
+        <v>-0.2164302155218749</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1639893491965054</v>
+        <v>-0.1935787589307125</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1306083824433273</v>
+        <v>-0.1604529828731032</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.1721137728268545</v>
+        <v>-0.2005034877012619</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.2298732453562025</v>
+        <v>-0.2543417616840387</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.00668</t>
+          <t>X &gt; -0.006667</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3250</v>
+        <v>3275</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.01023751840426712</v>
+        <v>0.004977880743254559</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2164552076253017</v>
+        <v>-0.224687643280653</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2317414016565493</v>
+        <v>-0.2495383453176956</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2856183869833444</v>
+        <v>-0.3093779677009252</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3290133322766309</v>
+        <v>-0.3556324490580494</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3696685127274435</v>
+        <v>-0.3944001623567885</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2980586558299194</v>
+        <v>-0.3221189138859089</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2527093806519574</v>
+        <v>-0.2757093003218856</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.2549977356393356</v>
+        <v>-0.2825589476122659</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.1525981247647366</v>
+        <v>-0.1797220971347429</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1366125212896918</v>
+        <v>-0.1637697293240024</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3363777623446751</v>
+        <v>-0.3621386096560144</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3378822634576437</v>
+        <v>-0.3640774137257736</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3568608394581716</v>
+        <v>-0.3814811734592212</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3525159260063333</v>
+        <v>-0.375904626177082</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.3843685473519756</v>
+        <v>-0.4057684104904524</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.1931136461279337</v>
+        <v>-0.2175693174893425</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.1568577588985747</v>
+        <v>-0.1801099255415721</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.2298906185113836</v>
+        <v>-0.2525174064711209</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.239952407556558</v>
+        <v>-0.2639814378363781</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2110058717992445</v>
+        <v>-0.233941364071157</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.237762885509774</v>
+        <v>-0.260537538176699</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.3140459869731274</v>
+        <v>-0.3346074215639376</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.3408519051042447</v>
+        <v>-0.3566295352785076</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.00609</t>
+          <t>X &gt; -0.006078</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3213</v>
+        <v>3234</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1158007312427358</v>
+        <v>-0.1499340661517365</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2341273131423236</v>
+        <v>-0.2565925318734372</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.187916306514694</v>
+        <v>-0.2352399544925348</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2960989907720588</v>
+        <v>-0.3498277747785608</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2742686409215906</v>
+        <v>-0.300982040887817</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3484636684386189</v>
+        <v>-0.3422002780743156</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2362244397598445</v>
+        <v>-0.2282044514511341</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1252097632645999</v>
+        <v>-0.1157953157953244</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1589393187625063</v>
+        <v>-0.1550752514364007</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1084508563128921</v>
+        <v>-0.1024287008758336</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.1264096397451553</v>
+        <v>-0.120486279206844</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.3252655422295589</v>
+        <v>-0.2870467739905394</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3759287151314226</v>
+        <v>-0.3365337513471118</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3925989868611381</v>
+        <v>-0.3510116214282561</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.3806574484369776</v>
+        <v>-0.3367309613962277</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.4197124928264344</v>
+        <v>-0.3740588747236941</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.2247321190968066</v>
+        <v>-0.1821550704515076</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1868642544223107</v>
+        <v>-0.1425291668900002</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.3564540448602997</v>
+        <v>-0.3111774867428068</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.3688198887981784</v>
+        <v>-0.3255219163828258</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.3333384144349694</v>
+        <v>-0.287933085403381</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.3595685359146401</v>
+        <v>-0.3139306103925747</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.5021552605162682</v>
+        <v>-0.4847792487064027</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.4973315909956852</v>
+        <v>-0.4741499646855232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.005501</t>
+          <t>X &gt; -0.005489</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3170</v>
+        <v>3185</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.02916543361946822</v>
+        <v>-0.0201828378362805</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1801408503012283</v>
+        <v>-0.2182186277371301</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2066166120047441</v>
+        <v>-0.2085427000167215</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3863209451237708</v>
+        <v>-0.3782195681024163</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4084351315982744</v>
+        <v>-0.3244214627908875</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.441042345751832</v>
+        <v>-0.3686783761366001</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.2855249553023853</v>
+        <v>-0.2095487781186947</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1692725441247305</v>
+        <v>-0.09074545157019998</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1726342448313005</v>
+        <v>-0.07007794457275196</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.173844060324889</v>
+        <v>-0.0669246101578338</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.164351441150977</v>
+        <v>-0.0581494283147137</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.4249931768409141</v>
+        <v>-0.3168421131592112</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.4926265714323605</v>
+        <v>-0.3812930903513703</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.3493368204744982</v>
+        <v>-0.2357054536916081</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.3283179275002936</v>
+        <v>-0.210704498349088</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.3444609722142715</v>
+        <v>-0.2258610800799801</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.2079578271654725</v>
+        <v>-0.09202694235589348</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.1681525434931004</v>
+        <v>-0.04972378446799297</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.3114610673665723</v>
+        <v>-0.1928798194996375</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.3895235427286678</v>
+        <v>-0.2734203341797965</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.3462152530593698</v>
+        <v>-0.2265157143459433</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.4663543895836995</v>
+        <v>-0.3458704711448704</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.5830945130021803</v>
+        <v>-0.4917164769780769</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.5772023054924986</v>
+        <v>-0.5098285717927027</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.004911</t>
+          <t>X &gt; -0.0049</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3112</v>
+        <v>3125</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2249675830536617</v>
+        <v>0.2057849618512861</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2096796025952088</v>
+        <v>0.1358388543615661</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.04961582512972029</v>
+        <v>0.04259560193540324</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1202072038976922</v>
+        <v>-0.08714019837754705</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.02323555039210135</v>
+        <v>0.1002623770657749</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1731848449801703</v>
+        <v>-0.1386005646988764</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.03234917718572916</v>
+        <v>0.07065085840701357</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.0912984000475916</v>
+        <v>0.1339634577456863</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.1831267651395763</v>
+        <v>0.3118886159368088</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1323695091218369</v>
+        <v>0.2667253706570989</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.07304975269129699</v>
+        <v>0.2387019737924874</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.3152207775172542</v>
+        <v>-0.178941872167826</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.363215864266671</v>
+        <v>-0.2551389052730855</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1490539829127044</v>
+        <v>-0.07007584402937539</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.1794315366255361</v>
+        <v>-0.1272079614873434</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.1748251748251732</v>
+        <v>-0.1533776742415824</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.03323898644359957</v>
+        <v>-0.01496647509578963</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.02275885154757873</v>
+        <v>-0.001220233129238579</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.1727045909444129</v>
+        <v>-0.1512160739689747</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2556534347508901</v>
+        <v>-0.2374024671530748</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2334965323526106</v>
+        <v>-0.2106714518141359</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.2901983809629911</v>
+        <v>-0.2669100237163846</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.4141708540356959</v>
+        <v>-0.4202064035160902</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.4067012228815798</v>
+        <v>-0.4355302986372891</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.004321</t>
+          <t>X &gt; -0.004312</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3045</v>
+        <v>3053</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1626135460522065</v>
+        <v>0.163485105439463</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1869617885120505</v>
+        <v>0.1952062735838993</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2507383646851054</v>
+        <v>0.291840649193098</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.02750030998281261</v>
+        <v>0.1404846815319374</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.181425802175994</v>
+        <v>0.3062599120530578</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1539717074497773</v>
+        <v>-0.03950350314173789</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.07215976854205763</v>
+        <v>0.225907888826022</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2373065497671334</v>
+        <v>0.3630777824326188</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2649253944090049</v>
+        <v>0.4770618859357256</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1646311696990423</v>
+        <v>0.3843698265919926</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1307188174395009</v>
+        <v>0.316717936195154</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.2926450220357211</v>
+        <v>-0.1368405721549735</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.3170606704923955</v>
+        <v>-0.1886158861437721</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2242711996240487</v>
+        <v>-0.1239367896888766</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.109925410958887</v>
+        <v>-0.03575612396815586</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.08548471945130842</v>
+        <v>-0.04304529338226359</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.00335198347654142</v>
+        <v>0.03574346405228823</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.00967039435524697</v>
+        <v>-0.01242330642563161</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.1810880197352276</v>
+        <v>-0.2037050151424964</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.3355634707019917</v>
+        <v>-0.3624161493454636</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.3010196930811091</v>
+        <v>-0.3217271420164565</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.3901419117614608</v>
+        <v>-0.4102892920811883</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.5229114645987849</v>
+        <v>-0.5729905184931994</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.5464853521169957</v>
+        <v>-0.6176567316539945</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.003731</t>
+          <t>X &gt; -0.003723</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2961</v>
+        <v>2965</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.1872254184686355</v>
+        <v>0.1387655074985048</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2218240398636127</v>
+        <v>0.1786575978862288</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.09340875174599006</v>
+        <v>0.1141735399202091</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.0151127626598182</v>
+        <v>0.07626293280565477</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1863701026035258</v>
+        <v>0.2885438988716444</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1975166327228735</v>
+        <v>-0.1055785689138773</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.004342608168506956</v>
+        <v>0.1911062450873757</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1483856856051489</v>
+        <v>0.3077693114593458</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.0747767543078055</v>
+        <v>0.2870948742191928</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.09425061473106666</v>
+        <v>0.315821298710766</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.01799124563010679</v>
+        <v>0.2381027205476371</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3758604311132387</v>
+        <v>-0.1871227518458198</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.3692493353786261</v>
+        <v>-0.207478712163585</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.2002859323293436</v>
+        <v>-0.06632314677822393</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.1987640263200916</v>
+        <v>-0.08982805676961192</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.1904783775784153</v>
+        <v>-0.113965619220167</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03250449170830905</v>
+        <v>0.1047975549573792</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.0522364080689286</v>
+        <v>-0.008154075990731258</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.2545324113649627</v>
+        <v>-0.2114563898003468</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.2837951912727519</v>
+        <v>-0.2465090323730266</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.3678319387163995</v>
+        <v>-0.322520949611615</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.5248522396972675</v>
+        <v>-0.5125930292621987</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.6692164004396304</v>
+        <v>-0.6536691195871995</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.7926743143734498</v>
+        <v>-0.8297832497334099</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.003142</t>
+          <t>X &gt; -0.003134</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5359293163773913</v>
+        <v>0.5217108713359551</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4437868334521866</v>
+        <v>0.379574357320088</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4269116319081974</v>
+        <v>0.4393043301431376</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2338882883753328</v>
+        <v>0.3159272289113346</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3833664466772788</v>
+        <v>0.5097188835830053</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.01573991180412548</v>
+        <v>0.1667982329634299</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.214328489612214</v>
+        <v>0.3955891173817534</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.3720607683127426</v>
+        <v>0.491550491550484</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3295027341898731</v>
+        <v>0.5007084505745638</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4093329280172355</v>
+        <v>0.5566774256725395</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4260049765719032</v>
+        <v>0.5715690677015957</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.006144095201136679</v>
+        <v>0.106861406600494</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.0671124991341685</v>
+        <v>0.01856893780860958</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.09391835639436152</v>
+        <v>-0.03568589187626969</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.1057940063427694</v>
+        <v>-0.07218061184167368</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.02265351709023378</v>
+        <v>0.02334850299209279</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.01377719767337737</v>
+        <v>0.009504257907543945</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.1051145182200486</v>
+        <v>-0.1723631269511259</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.1469316857495073</v>
+        <v>-0.215613907001341</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.2179738870127466</v>
+        <v>-0.2937145213354171</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.321966330237359</v>
+        <v>-0.3882997452205075</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.4326433609602915</v>
+        <v>-0.4777388815482055</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.5904015870189951</v>
+        <v>-0.6315327184892325</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.7153592381337077</v>
+        <v>-0.8081017272087081</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.002552</t>
+          <t>X &gt; -0.002545</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2759</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.5933871208022694</v>
+        <v>0.5775603895576324</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7270787909209204</v>
+        <v>0.6195268895860409</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6223930752232647</v>
+        <v>0.6242786315231683</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3058354521769218</v>
+        <v>0.3917181023802954</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.5826575922422563</v>
+        <v>0.7122821177766028</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2651192738351327</v>
+        <v>0.3854647227384618</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3219994187736148</v>
+        <v>0.4751592663851909</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3528612866987473</v>
+        <v>0.443040443040438</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.4512105106913609</v>
+        <v>0.5916244707120413</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5288486963879677</v>
+        <v>0.6456696045642047</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.463170286794508</v>
+        <v>0.5781384030950747</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.06104403155377724</v>
+        <v>0.1419852767826626</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.1021603813903482</v>
+        <v>-0.04956073537697137</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2296400160247245</v>
+        <v>-0.2044065491532621</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.1074521605232306</v>
+        <v>-0.1066890213528424</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.0386182869913938</v>
+        <v>0.00628298370428837</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.001444124757625787</v>
+        <v>-0.0401075560376043</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.08472109124816285</v>
+        <v>-0.1877929357824613</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.3177534404290583</v>
+        <v>-0.4222960941277449</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.3991281916525082</v>
+        <v>-0.5122298412087432</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.377057702817396</v>
+        <v>-0.4792738397201504</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.4166849029081376</v>
+        <v>-0.5331011246497397</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.5192002538876537</v>
+        <v>-0.6304347826086882</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.5373556550693905</v>
+        <v>-0.6988488923306519</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.001962</t>
+          <t>X &gt; -0.001957</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2660</v>
+        <v>2655</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8842089823047559</v>
+        <v>0.8872798139454758</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.8860066042989914</v>
+        <v>0.7909056885219812</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7194909210122091</v>
+        <v>0.7324732688733917</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3805084797295279</v>
+        <v>0.4391364906259128</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.9048526369503946</v>
+        <v>0.9698890335314942</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5682586136236836</v>
+        <v>0.6243464244297456</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.6190474016854708</v>
+        <v>0.7111426310679292</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5868765171090828</v>
+        <v>0.6148558376188404</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5751872236916213</v>
+        <v>0.6519492089853003</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.572716804651435</v>
+        <v>0.6267400806275418</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5316564942643396</v>
+        <v>0.5834387832080452</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2747559505921302</v>
+        <v>0.2910463987436458</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.03943443125599089</v>
+        <v>-0.05197108525685934</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.1258506053079955</v>
+        <v>-0.1656499319012781</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.08658951804655857</v>
+        <v>-0.1500850185060614</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.1925919608846414</v>
+        <v>0.09556820118551457</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.04353304047270967</v>
+        <v>-0.06123998246933127</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.1891157192451587</v>
+        <v>-0.3598312115125921</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.4767858187523686</v>
+        <v>-0.6495465647326242</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.4932411070140219</v>
+        <v>-0.6762600600096249</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.5096692742284503</v>
+        <v>-0.6574960742924318</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.5479353784410108</v>
+        <v>-0.7105553342253685</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.6868390951209236</v>
+        <v>-0.8213069669984279</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.7029108987421822</v>
+        <v>-0.8861216357370907</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001372</t>
+          <t>X &gt; -0.001368</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2522</v>
+        <v>2511</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.278157232676293</v>
+        <v>1.319033350940792</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.417501335156189</v>
+        <v>1.349806357134149</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.164784538199477</v>
+        <v>1.162305931131897</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8074211943790104</v>
+        <v>0.8070578825212991</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.222322148145452</v>
+        <v>1.242962193014854</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7771271331365526</v>
+        <v>0.7898341739428005</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6373396503524802</v>
+        <v>0.6895876397846692</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.7937390313599764</v>
+        <v>0.8030442933489965</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.7562060631363892</v>
+        <v>0.8350338923235228</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8525120386210503</v>
+        <v>0.9330661047623607</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6524507799532628</v>
+        <v>0.7530251469200024</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.3572726812591114</v>
+        <v>0.4201622449941382</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.1271193025532611</v>
+        <v>0.1609191714072296</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.008616367965906591</v>
+        <v>0.01534379211156534</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.03242579904004828</v>
+        <v>-0.04819741661846422</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.1106672424962269</v>
+        <v>0.06035702281405975</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.07886163142691771</v>
+        <v>-0.1392060497749554</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.4770760466287385</v>
+        <v>-0.6062278675771751</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.7926030649260341</v>
+        <v>-0.924897103241058</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.8435693833765541</v>
+        <v>-0.9655360625128466</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.7123145208233694</v>
+        <v>-0.7939778261434682</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.7485251274960447</v>
+        <v>-0.8458248345923778</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.8704039623782407</v>
+        <v>-0.9371365272777581</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.8039764094658537</v>
+        <v>-0.916766459529363</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0007826</t>
+          <t>X &gt; -0.0007792</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2354</v>
+        <v>2337</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.020169835720573</v>
+        <v>1.083858840650009</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.320986257709741</v>
+        <v>1.21995540053188</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.027035005288923</v>
+        <v>0.9414921984705202</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.907301324829227</v>
+        <v>0.8584278604432853</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.122358309909075</v>
+        <v>1.134652402856688</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.716104157023409</v>
+        <v>0.6788666204927551</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.6221215748279718</v>
+        <v>0.587452034351422</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.6828931809223491</v>
+        <v>0.6043066816547409</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.8514990069048594</v>
+        <v>0.8842162731143262</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.8412951952751371</v>
+        <v>0.8783011216711145</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.776371786589614</v>
+        <v>0.7924087663016124</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5823681458534722</v>
+        <v>0.6256788991830007</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.2471009784448412</v>
+        <v>0.2595740071491264</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2632706018693511</v>
+        <v>0.249474241627496</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.05471118684964438</v>
+        <v>0.0187858984466942</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.03794309821474684</v>
+        <v>-0.03415707939083745</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.01422028823001398</v>
+        <v>-0.07021473265074007</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.3626604179722577</v>
+        <v>-0.5193411047348064</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.6990205238788576</v>
+        <v>-0.8775824957214908</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.8945026663322437</v>
+        <v>-1.022605011484544</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.714873813057828</v>
+        <v>-0.7961196779273223</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.7482388908645561</v>
+        <v>-0.8462331431960948</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.6861685963943955</v>
+        <v>-0.7486145720980346</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.6345581988105309</v>
+        <v>-0.7145752280339437</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0001928</t>
+          <t>X &gt; -0.0001905</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2142</v>
+        <v>2126</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.086679668123693</v>
+        <v>1.121552376367021</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.357398910761304</v>
+        <v>1.248779869021355</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.17694856224265</v>
+        <v>1.113488752204397</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.302373676474801</v>
+        <v>1.22071341906782</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.944692193214912</v>
+        <v>1.877991099864012</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.526162338324866</v>
+        <v>1.428581422280004</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.266556458346948</v>
+        <v>1.220145623682789</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.314381343356331</v>
+        <v>1.222307104660047</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.216138669658555</v>
+        <v>1.190533335203057</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.281602127296956</v>
+        <v>1.26266728917988</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.183048821158934</v>
+        <v>1.18837824895904</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.416642221623377</v>
+        <v>1.406856407992954</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.225012525517137</v>
+        <v>1.208638873035241</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9388869921474949</v>
+        <v>0.8947916362136183</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.6818368542807818</v>
+        <v>0.6153466895485948</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.6515716870194481</v>
+        <v>0.5488097306878288</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.6390363832928898</v>
+        <v>0.5197345288326289</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.4222641437527415</v>
+        <v>0.2272042312986855</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.1713021166471904</v>
+        <v>0.0003124798756104497</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.06202014061167205</v>
+        <v>-0.2268694705155312</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.282455166679064</v>
+        <v>0.1726148910890757</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.06655318286099998</v>
+        <v>-0.06252954902469554</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.2943425545400657</v>
+        <v>0.2090308865313446</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.125139619710815</v>
+        <v>0.02780742478698528</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0003969</t>
+          <t>X &gt; 0.0003983</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1920</v>
+        <v>1897</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.24480777222292</v>
+        <v>1.235441157006903</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.637681701523825</v>
+        <v>1.511727532791269</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.654964107794299</v>
+        <v>1.5102971384715</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.513735660077124</v>
+        <v>1.335649508853876</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.853620863205528</v>
+        <v>1.686723222540436</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.52083652955239</v>
+        <v>1.269244295901451</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.632463729237926</v>
+        <v>1.39214739270453</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.354252284484851</v>
+        <v>1.065241316156104</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.187839258499338</v>
+        <v>1.014257829485821</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.19454936208863</v>
+        <v>1.033350544509318</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.9488584845000361</v>
+        <v>0.8126827999431327</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.345784756727717</v>
+        <v>1.195117517669388</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.262123729372632</v>
+        <v>1.106809175846145</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.384491023205292</v>
+        <v>1.204536534273004</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.33029696163787</v>
+        <v>1.131036081607682</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.279912608647642</v>
+        <v>1.09428395503209</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.438052559992229</v>
+        <v>1.232055322128843</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.333211856171047</v>
+        <v>1.130882535230761</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.080353237095366</v>
+        <v>0.9564795415425351</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.9546990470634</v>
+        <v>0.886999434656687</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.245486212430698</v>
+        <v>1.298347258644874</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.013390251021598</v>
+        <v>1.097162730647625</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.33994829683698</v>
+        <v>1.372703532322362</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.055782710280376</v>
+        <v>1.031645241689546</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.0009867</t>
+          <t>X &gt; 0.000987</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1676</v>
+        <v>1644</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8612399467946332</v>
+        <v>0.7293347640675023</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.778699284401881</v>
+        <v>1.566460419338355</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.891067832270117</v>
+        <v>1.635472695304777</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.35700468939266</v>
+        <v>1.103238968217376</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.856038307483445</v>
+        <v>1.549702488767863</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.327440987319633</v>
+        <v>0.864277490674489</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.10587990032851</v>
+        <v>1.608399892583435</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.006559332140732</v>
+        <v>1.458996157791333</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.869155637490138</v>
+        <v>1.501520156693068</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.050324636468559</v>
+        <v>1.705606084936498</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.085863109876748</v>
+        <v>1.832535116152009</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.463046920501512</v>
+        <v>2.255882315993119</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.592120989602456</v>
+        <v>2.44599479594153</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.549932989721164</v>
+        <v>2.476531963827078</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.883410141772927</v>
+        <v>2.859934983346967</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.821472481377022</v>
+        <v>2.793171170401351</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.568223602156102</v>
+        <v>2.484447557036141</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.702046382821798</v>
+        <v>2.570714379686876</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.321279052528936</v>
+        <v>2.276879567304569</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.209795506888376</v>
+        <v>2.164590942447688</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.68156914799156</v>
+        <v>2.848502245383123</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.48639144433902</v>
+        <v>2.507382472828233</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.701200285699358</v>
+        <v>2.788687723007797</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.386704547989204</v>
+        <v>2.360129068759306</v>
       </c>
     </row>
     <row r="24">
@@ -4660,981 +4660,981 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1366</v>
+        <v>1337</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.776429606919429</v>
+        <v>1.741926117417862</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.954097903737981</v>
+        <v>1.791658601743549</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.540969045043745</v>
+        <v>1.349972629933276</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.8280150256010046</v>
+        <v>0.6097507711102708</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.590321185557386</v>
+        <v>1.295020421107012</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.264842276486398</v>
+        <v>0.8606753870459727</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.030228878101163</v>
+        <v>1.61769980496846</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.410875412850288</v>
+        <v>1.904058001618964</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.159536826097344</v>
+        <v>1.779589215190555</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.41151134039761</v>
+        <v>1.989093543183486</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.173125887391159</v>
+        <v>1.860966685923358</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.480028021278443</v>
+        <v>2.22123507326905</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.747788355593627</v>
+        <v>2.560161918320439</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.112361016482325</v>
+        <v>3.025514924753281</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.186282140570874</v>
+        <v>3.20659632851703</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.828985314344024</v>
+        <v>2.922382580250407</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.061100388201112</v>
+        <v>3.08779761904762</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>3.029466126546836</v>
+        <v>2.926769344825985</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.879325296636601</v>
+        <v>3.038529811005532</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.992964664437721</v>
+        <v>3.075690107684458</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.47530868680844</v>
+        <v>3.673838224866401</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.399462725399339</v>
+        <v>3.421722530015323</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.161492342713025</v>
+        <v>3.488139338402554</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.08566008948975</v>
+        <v>3.298106200988748</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.002166</t>
+          <t>X &gt; 0.002164</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1055</v>
+        <v>1030</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.378110232539598</v>
+        <v>2.384715528103555</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.896414002910163</v>
+        <v>2.808024753585144</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.785409171888652</v>
+        <v>2.604955890699301</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.314161313583355</v>
+        <v>1.05653074734041</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.210598329187732</v>
+        <v>1.928200140701875</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.492351245142927</v>
+        <v>2.08513374669996</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.236990238977704</v>
+        <v>2.724086151293243</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.001432822660647</v>
+        <v>3.375188652435298</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.284626165712794</v>
+        <v>2.79520315590571</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.312658356974879</v>
+        <v>3.684517111932045</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.30235780956334</v>
+        <v>3.727803801082615</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.402755325546622</v>
+        <v>3.797649819957073</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.848313637837421</v>
+        <v>3.414097160911311</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.101168410679932</v>
+        <v>3.706301287610913</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.580465871393223</v>
+        <v>4.335596524442074</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>4.132198764900188</v>
+        <v>3.995077425212479</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.713921438349253</v>
+        <v>3.662658711025394</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>4.083014383817172</v>
+        <v>4.072995881968382</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.540611925878935</v>
+        <v>3.768927155800597</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>4.390964844851709</v>
+        <v>4.431097674715623</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>4.417139056032589</v>
+        <v>4.796130924003819</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.62565328419695</v>
+        <v>4.783160256885431</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>5.08970145639465</v>
+        <v>5.477080082655085</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>5.108655933029191</v>
+        <v>5.377751254760774</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.002756</t>
+          <t>X &gt; 0.002753</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>802</v>
+        <v>782</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.840449644672773</v>
+        <v>3.797398365992287</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.256296287719472</v>
+        <v>3.175079987001091</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.317030355895454</v>
+        <v>2.045856399538614</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.227517732961438</v>
+        <v>1.955336258446835</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.260804567147339</v>
+        <v>3.938247378071459</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.445276987658687</v>
+        <v>4.848004070644208</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.920211096785792</v>
+        <v>5.182156688273466</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.764194165748421</v>
+        <v>5.881000360297726</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.434110275343919</v>
+        <v>4.628753611261629</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.534012554419654</v>
+        <v>4.663550208449109</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.558695637978083</v>
+        <v>4.762434191164445</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.903387631038811</v>
+        <v>5.067732058628096</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.278978681389681</v>
+        <v>4.410083898854872</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.057899804943091</v>
+        <v>4.367723199032824</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.147886183173007</v>
+        <v>4.776918470444322</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>4.869455150003773</v>
+        <v>4.660183154341034</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.7355380130263</v>
+        <v>4.637000950570339</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.254138705713856</v>
+        <v>5.092634084347708</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>5.095965248732931</v>
+        <v>5.134720328676252</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>5.033434500097471</v>
+        <v>5.176492175185643</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>5.114329728640179</v>
+        <v>5.454901063539268</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>5.537236884438066</v>
+        <v>5.717545638945232</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.811711596920119</v>
+        <v>6.172136154145157</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>5.611191064395094</v>
+        <v>5.837861005710543</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.003346</t>
+          <t>X &gt; 0.003342</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.588109115524261</v>
+        <v>2.927961507183518</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.084982148824274</v>
+        <v>2.177852990807381</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.162114614944805</v>
+        <v>2.09962947715109</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.617510763852231</v>
+        <v>1.339160051452112</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.975322984907649</v>
+        <v>3.752677541604882</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.49898950770536</v>
+        <v>4.077678374493722</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.400441497215695</v>
+        <v>3.954865269824026</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.637381567614128</v>
+        <v>4.99448264154146</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.332067402727482</v>
+        <v>3.777873736099515</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.24265341019268</v>
+        <v>4.494427282896986</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.34836288400443</v>
+        <v>4.53436735932403</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.40631381725678</v>
+        <v>4.530609202128467</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.619852087100995</v>
+        <v>3.858381502890175</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.56712337900457</v>
+        <v>3.885105140272636</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>4.919081091525022</v>
+        <v>4.326298144317775</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>5.176767676767682</v>
+        <v>4.486750389087767</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.706150203089862</v>
+        <v>4.150722789115648</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>4.60130949926868</v>
+        <v>4.125616036803194</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>5.827301890294031</v>
+        <v>5.642762706739575</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.845797531911884</v>
+        <v>5.796965849094434</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>5.303251363945854</v>
+        <v>5.85386275972634</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>5.227405402536753</v>
+        <v>5.890603712946692</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>5.838580451719139</v>
+        <v>6.590168833109225</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>6.604499040246701</v>
+        <v>7.229764021500408</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.003935</t>
+          <t>X &gt; 0.003931</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.409039507883229</v>
+        <v>4.602169651979906</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.806689013388279</v>
+        <v>1.867575033470601</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.275699442815345</v>
+        <v>1.065369619361825</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3442840550854527</v>
+        <v>-1.336987330577621</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.721286016584969</v>
+        <v>1.78111968769408</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.949068529212958</v>
+        <v>3.521763700931992</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.950362475708097</v>
+        <v>2.952926032590675</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.352423139798553</v>
+        <v>3.100494276964859</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.393910321713257</v>
+        <v>3.228423186648968</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.115325711436412</v>
+        <v>4.468570786452254</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.616142723212839</v>
+        <v>4.96705014494799</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.657121210921311</v>
+        <v>3.924520785873831</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.080444404836172</v>
+        <v>2.494745139253808</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.859365528389581</v>
+        <v>2.385773865147279</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>3.881494339652562</v>
+        <v>2.756760182859686</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>3.795609152752014</v>
+        <v>2.545361151618216</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.208177276545506</v>
+        <v>1.894590978593271</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.103336572724324</v>
+        <v>1.901957848861379</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.999500062492189</v>
+        <v>3.178976355471107</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>4.186345872460215</v>
+        <v>3.768186314541225</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>3.643799704494185</v>
+        <v>3.577099695292048</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>4.474983221543134</v>
+        <v>4.576097180211384</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>5.656487412483244</v>
+        <v>5.979824472914366</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>6.260927268103494</v>
+        <v>6.745759724564572</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.004525</t>
+          <t>X &gt; 0.004519</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.269600647762061</v>
+        <v>4.493087557603694</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.128853700158515</v>
+        <v>5.437656912376006</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.586357039187227</v>
+        <v>4.182962810484426</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.380865706311653</v>
+        <v>1.507227278342867</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.030149860630054</v>
+        <v>4.207859614434007</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.70965336016026</v>
+        <v>5.257650363289244</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.743674825523648</v>
+        <v>3.569711208199372</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>6.555015619576544</v>
+        <v>5.050505050505045</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.895010264177813</v>
+        <v>5.476053007808204</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.808661752320432</v>
+        <v>7.060953893541253</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.978243782542044</v>
+        <v>8.226046051002726</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.505464528347787</v>
+        <v>6.461368858436181</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.382302461491669</v>
+        <v>5.238978517815553</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.758238510418209</v>
+        <v>5.780806124091789</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>6.50308028746452</v>
+        <v>4.692257323836266</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>7.097467209407512</v>
+        <v>5.447128403692886</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>6.366535147056908</v>
+        <v>4.933755035246726</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>6.261694443235726</v>
+        <v>4.994956803929313</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>7.671615674906313</v>
+        <v>6.620490229380323</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>7.261446559501209</v>
+        <v>6.730361721514697</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>6.420392928848607</v>
+        <v>6.057561808781685</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>6.643054430126078</v>
+        <v>6.594020081933444</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>8.111558993354393</v>
+        <v>8.366706554979395</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>9.826771516250524</v>
+        <v>10.34524034356455</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.005115</t>
+          <t>X &gt; 0.005108</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.909714684320846</v>
+        <v>6.532000137561049</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.574937885971032</v>
+        <v>5.912958973498959</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.758641683381981</v>
+        <v>6.523936513398425</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.173028487909285</v>
+        <v>3.319594016082746</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8.706151873039914</v>
+        <v>7.52164781628192</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>9.267649894343279</v>
+        <v>8.051715750638209</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.372105704834958</v>
+        <v>6.510365081689073</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.715617106523823</v>
+        <v>8.444250608429712</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>10.50616795885051</v>
+        <v>8.945313846472025</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>11.60591145884399</v>
+        <v>10.01493399304373</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>12.6290347714179</v>
+        <v>11.03343766436448</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.22668986235192</v>
+        <v>9.264318396460354</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.1035277954958</v>
+        <v>7.776291950651377</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>9.88244891904921</v>
+        <v>7.776814108123723</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>8.475241951056667</v>
+        <v>6.593406593406591</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>8.320565202587673</v>
+        <v>6.649674436882236</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>7.063052559992215</v>
+        <v>5.658143939393931</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>7.707275526583032</v>
+        <v>6.532000242113426</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>8.297698742713344</v>
+        <v>7.379208529108851</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>7.735480882269385</v>
+        <v>7.081964375472268</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>7.567466549509355</v>
+        <v>7.152598270790619</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>8.240684258512239</v>
+        <v>7.846666518066108</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>10.38781814702425</v>
+        <v>10.39799331103679</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>11.43558139941894</v>
+        <v>11.77431585520888</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.005705</t>
+          <t>X &gt; 0.005697</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7.603172025324014</v>
+        <v>8.068747679472345</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9.182270825060321</v>
+        <v>9.718575440924866</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.74425177602933</v>
+        <v>7.51601404045509</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.50976665610812</v>
+        <v>6.923611841646867</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>11.48019627925463</v>
+        <v>10.43952289586032</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>10.71022466630895</v>
+        <v>9.648589203280217</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10.41674488194013</v>
+        <v>9.801374489625687</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.57394013575164</v>
+        <v>10.44432134479527</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>11.61542731766635</v>
+        <v>10.09831660519028</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.75638723971599</v>
+        <v>11.19799970712734</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.98738468092096</v>
+        <v>12.41810202030987</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.75169747842992</v>
+        <v>10.71971911797128</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.58547321061685</v>
+        <v>10.55269429909871</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>11.40745653512721</v>
+        <v>9.356592939087399</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>11.22778213706817</v>
+        <v>9.475612107191061</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>10.38676236044657</v>
+        <v>8.931880810449087</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>8.817438524904503</v>
+        <v>7.71233974358973</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>8.234128921561791</v>
+        <v>7.419199228171721</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>7.971551402964586</v>
+        <v>7.471849157582881</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>7.201459413889552</v>
+        <v>7.035239770295192</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>7.137382145445052</v>
+        <v>6.955600146963235</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>8.018473983079012</v>
+        <v>7.856047381105519</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>10.20682429364719</v>
+        <v>10.05090137857901</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>12.04486763851003</v>
+        <v>11.83998189648467</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.006294</t>
+          <t>X &gt; 0.006286</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.934910462325611</v>
+        <v>4.692667389536467</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.024376088218219</v>
+        <v>6.799701730303177</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.616660069490251</v>
+        <v>8.486184098999829</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.903706050047511</v>
+        <v>7.30554660607396</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>11.4164004259851</v>
+        <v>11.14763552479815</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>10.39124539996125</v>
+        <v>10.12809854256094</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.619296716070899</v>
+        <v>9.921251824445875</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12.97744890768146</v>
+        <v>12.55750785162549</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.382572453232527</v>
+        <v>8.567789702486074</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.821777989317269</v>
+        <v>8.948208795502026</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.3079588436004</v>
+        <v>10.39691439834166</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>10.42314883409179</v>
+        <v>9.532097149752701</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.11816858541749</v>
+        <v>10.18191091465489</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.2910291029103</v>
+        <v>9.345441559104124</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>10.23894641139034</v>
+        <v>9.25152247133672</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>9.015151515151516</v>
+        <v>8.444918380166826</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>7.063052559992215</v>
+        <v>6.956845238095234</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>5.746090644049829</v>
+        <v>6.021993639349375</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>5.355921418913546</v>
+        <v>6.027235752506257</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>5.542767228881573</v>
+        <v>6.241822197565241</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>3.788099848794332</v>
+        <v>4.469558419076066</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>4.924375099506442</v>
+        <v>5.599215174229222</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>8.229152842291541</v>
+        <v>8.85489785227869</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>11.18362361937128</v>
+        <v>11.7048070507603</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.006884</t>
+          <t>X &gt; 0.006874</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>132</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.934910462325611</v>
+        <v>4.03313084764698</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.388012451854586</v>
+        <v>7.575102799821899</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>8.980296433126618</v>
+        <v>9.350711728233343</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.54006968641114</v>
+        <v>11.03103680215239</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>13.99215800174267</v>
+        <v>14.54335744993185</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.66397267268853</v>
+        <v>13.18513954077842</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.89202398879818</v>
+        <v>12.3900575285457</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.64411557434813</v>
+        <v>15.11544011544011</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.89772396838404</v>
+        <v>11.45549023724542</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.88238404992332</v>
+        <v>11.41701449960185</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>10.39886793450948</v>
+        <v>10.93167375663042</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>10.12011853106148</v>
+        <v>10.65509180215912</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>11.26968373693264</v>
+        <v>11.81292695743563</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>12.56375637563757</v>
+        <v>13.07984441115403</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>12.66318883563277</v>
+        <v>13.15526578684474</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>10.98484848484848</v>
+        <v>11.44384253293713</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>9.335779832719496</v>
+        <v>9.824810606060602</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>6.200636098595282</v>
+        <v>6.66162347059597</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>4.901375964368093</v>
+        <v>5.360934182590228</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>3.573070259184604</v>
+        <v>4.060369112497696</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>3.788099848794332</v>
+        <v>4.25050036869272</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>4.469829644960988</v>
+        <v>4.932913604313192</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>7.774607387746073</v>
+        <v>8.206851119894601</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>9.971502407250078</v>
+        <v>10.31743939833242</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.007474</t>
+          <t>X &gt; 0.007463</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.945011472426621</v>
+        <v>5.457373271889402</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>8.650638714480849</v>
+        <v>9.211466436185532</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.24292269575289</v>
+        <v>10.95677233429395</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.54006968641114</v>
+        <v>11.36437013548573</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>15.25478426436892</v>
+        <v>16.08881199538639</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.42154843026429</v>
+        <v>14.24574560138448</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>13.65970075647495</v>
+        <v>14.45066358915176</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>18.43199436222692</v>
+        <v>19.14574314574314</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.43307750373758</v>
+        <v>15.27367205542725</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.67026283780211</v>
+        <v>15.47762056020791</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.96452450016606</v>
+        <v>17.74985557481224</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>15.67567408661704</v>
+        <v>16.47327362034095</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>18.59291606016497</v>
+        <v>19.35838150289018</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.37183718371838</v>
+        <v>19.11014744145707</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>21.75409792654187</v>
+        <v>21.42799305957201</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>20.32828282828284</v>
+        <v>19.98929707839167</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>18.17416367110334</v>
+        <v>17.88541666666666</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>14.02891892687811</v>
+        <v>13.75253256150506</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>12.22460828760041</v>
+        <v>11.96699478865084</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>9.381151067265407</v>
+        <v>9.181581233709821</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>9.848705909400401</v>
+        <v>9.614136732329086</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>11.79306196819331</v>
+        <v>11.5389742103738</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>16.1079407210794</v>
+        <v>15.78260869565218</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>17.04220947795714</v>
+        <v>16.62046970136272</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.008064</t>
+          <t>X &gt; 0.008052</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>5.779442741640494</v>
+        <v>5.028801843317979</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>6.89394130560953</v>
+        <v>7.640037864756962</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8.354472981216205</v>
+        <v>9.242486620008243</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>9.090794324092315</v>
+        <v>10.07865584977144</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>11.65355457618273</v>
+        <v>12.66024056681496</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>11.84052076228011</v>
+        <v>12.81717417281305</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8.17002135375207</v>
+        <v>9.164949303437467</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>15.1381867205932</v>
+        <v>16.00288600288599</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>10.83184781555138</v>
+        <v>11.84510062685582</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>10.05893213951489</v>
+        <v>11.04904913163648</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>13.23154250631449</v>
+        <v>14.17842700338367</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>12.95279310286649</v>
+        <v>13.90184504891238</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>16.17745712296691</v>
+        <v>17.07266721717588</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>15.95637824652032</v>
+        <v>16.82443315574277</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>19.64606103589627</v>
+        <v>20.42799305957201</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>23.13899868247694</v>
+        <v>23.84643993553453</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>21.55580618318064</v>
+        <v>22.31398809523809</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>17.10313939240292</v>
+        <v>17.89538970436222</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>15.86975541100842</v>
+        <v>16.68128050293654</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>11.70877513401992</v>
+        <v>12.61015266228125</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>8.267678241416213</v>
+        <v>9.185565303757656</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>11.09038300464479</v>
+        <v>11.96754563894523</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>15.71268380408337</v>
+        <v>16.49689440993789</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>17.08612691317892</v>
+        <v>17.76332684421987</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1477 +5824,1477 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.009039</t>
+          <t>X &lt; -0.009021</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.431616654683978</v>
+        <v>0.7430875576036868</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.3524355059846727</v>
+        <v>-0.9313907066716069</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.108096169622009</v>
+        <v>2.09962947715109</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.395142150179268</v>
+        <v>1.507227278342867</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.05935167763199445</v>
+        <v>1.231669138243532</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.652232860908299</v>
+        <v>-1.468540112901238</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.42418154479865</v>
+        <v>-2.263622125133956</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.8038422649140529</v>
+        <v>-1.139971139971145</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.7623550829993491</v>
+        <v>-1.012042230287037</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.08599539671699574</v>
+        <v>-0.379522296934951</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.086614970082614</v>
+        <v>4.178427003383675</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.706416291272284</v>
+        <v>6.758987906055239</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.133978862097329</v>
+        <v>4.215524360033029</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.710001434926113</v>
+        <v>9.681576012885635</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>2.254756688070181</v>
+        <v>3.285135916714864</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.747694334650859</v>
+        <v>6.703582792677381</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-3.081874976239661</v>
+        <v>-1.971726190476197</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2881649554231629</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-1.521548936817673</v>
+        <v>-0.4615766399205867</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.1145722354691898</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.4279739324968403</v>
+        <v>0.6141367323290865</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.5038198939059413</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.669205543213792</v>
+        <v>2.21118012422361</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>4.042648652309353</v>
+        <v>3.477612558505569</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.008449</t>
+          <t>X &lt; -0.008433</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.466934069953709</v>
+        <v>-0.3511373664084729</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.459158696913875</v>
+        <v>1.530615372355747</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.282009213100274</v>
+        <v>3.467410632166292</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.569055193657533</v>
+        <v>2.875008433358069</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.23326472111026</v>
+        <v>2.599450293258734</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.8406386580097518</v>
+        <v>-0.435105462445307</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.699543863639242</v>
+        <v>-1.230187474678026</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.890798786653178</v>
+        <v>-0.4712781308526104</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.7623550829993491</v>
+        <v>0.7204805660655538</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.4483142372967066</v>
+        <v>0.9882588580802505</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.912701926604349</v>
+        <v>2.324323659918626</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.981778610112876</v>
+        <v>6.303060854383503</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>4.945573064995877</v>
+        <v>6.251998524166773</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.898407232027552</v>
+        <v>8.131424037201747</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>4.066350890968728</v>
+        <v>5.321610080848608</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>5.747694334650859</v>
+        <v>6.946743886902311</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.9079619327613955</v>
+        <v>0.4598847517730462</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.07415388515654797</v>
+        <v>1.390830433845494</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-2.970824299136517</v>
+        <v>-1.586196700710857</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.4768910760489007</v>
+        <v>1.819879106050251</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.06565509191712948</v>
+        <v>1.252434604669517</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.228457575065356</v>
+        <v>0.1134422954801835</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.132973659155823</v>
+        <v>1.42090656799261</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>2.231054449410806</v>
+        <v>3.386427148171222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.00786</t>
+          <t>X &lt; -0.007844</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>110</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.004483477068326636</v>
+        <v>0.09373690825304237</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.478921542763672</v>
+        <v>1.666011890730985</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.677266130096321</v>
+        <v>4.047681425203045</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.96431211065358</v>
+        <v>3.455279226394822</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.446703456288127</v>
+        <v>4.997902904477307</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.9973060060218657</v>
+        <v>1.518472874111751</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.225357322131515</v>
+        <v>0.7233908618790323</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.8562367864693456</v>
+        <v>1.32756132756132</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.806814877474963</v>
+        <v>2.364581146336342</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.033899201438473</v>
+        <v>1.568529651117004</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.307958843600396</v>
+        <v>1.840764665721338</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.66557307651604</v>
+        <v>5.200546347613681</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>6.269683736932642</v>
+        <v>6.812926957435629</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.775877587758771</v>
+        <v>9.291965623275239</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>6.299552471996414</v>
+        <v>6.791629423208384</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>6.893939393939405</v>
+        <v>7.352933442028046</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>3.123658620598292</v>
+        <v>3.612689393939398</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>2.109727007686189</v>
+        <v>2.570714379686876</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>2.325618388610515</v>
+        <v>2.78517660683265</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>4.330646016760362</v>
+        <v>4.817944870073454</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.788099848794332</v>
+        <v>4.25050036869272</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>2.803162978294331</v>
+        <v>3.266246937646535</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>3.986728599867284</v>
+        <v>4.418972332015812</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>5.729078164825829</v>
+        <v>6.075015155908169</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.00727</t>
+          <t>X &lt; -0.007255</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.513027564559792</v>
+        <v>-2.050089414677757</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.663473832579115</v>
+        <v>2.181615689916867</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.481093881292495</v>
+        <v>3.165727558174552</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.27189926034599</v>
+        <v>4.065862672799156</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.439868186294959</v>
+        <v>5.282841846132662</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.626834372392338</v>
+        <v>5.439775452130746</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.103005989253866</v>
+        <v>3.898424783181603</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.576674243748911</v>
+        <v>4.339772996489408</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.370041124911729</v>
+        <v>5.213970562889934</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.597125448875239</v>
+        <v>4.417919067670596</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.871185091037162</v>
+        <v>4.69015408227493</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.599954484581644</v>
+        <v>7.398646754669301</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.228672116973662</v>
+        <v>7.030023293934953</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.511352639023301</v>
+        <v>8.274326545934677</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>6.101329642194621</v>
+        <v>6.845903507333212</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>6.695716564137612</v>
+        <v>7.407207526152874</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>2.802400930919546</v>
+        <v>3.571983830845774</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.945680527850236</v>
+        <v>2.692831068967749</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2.91345160802269</v>
+        <v>3.653561952829946</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>4.60405681648696</v>
+        <v>5.360685711321764</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>4.06151064852093</v>
+        <v>4.79324120994103</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>3.2337849878637</v>
+        <v>3.971810031269328</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>4.260139399593882</v>
+        <v>4.961713173264123</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>5.688066544866849</v>
+        <v>6.292111492407493</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.00668</t>
+          <t>X &lt; -0.006667</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>174</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.192571251363006</v>
+        <v>-0.094350866041637</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4.07035309971247</v>
+        <v>4.257443447679783</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.35647198171597</v>
+        <v>4.726887276822694</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.367655893307699</v>
+        <v>5.858623009048941</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.181290708116748</v>
+        <v>6.732490156305929</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.942969537892296</v>
+        <v>7.464136405982181</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.596308210323777</v>
+        <v>6.094341750071294</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.743384121892547</v>
+        <v>5.214708662984521</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.78487130380725</v>
+        <v>5.342637572668629</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.862530340414438</v>
+        <v>3.397160790092968</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.561877338898199</v>
+        <v>3.094683161019141</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.306116441197332</v>
+        <v>6.841089712294973</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.332379661697537</v>
+        <v>6.875622882200524</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.686013428929101</v>
+        <v>7.202101464445569</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>7.094659726238667</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>7.65596374505833</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>3.614776697923261</v>
+        <v>4.103807471264368</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>2.935223350423911</v>
+        <v>3.396210722424598</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.300540018704567</v>
+        <v>4.760098236926702</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>4.487385828672593</v>
+        <v>4.974684681985686</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3.944839660706563</v>
+        <v>4.407240180604951</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>4.443706342975624</v>
+        <v>4.906790302327828</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>5.867606342814</v>
+        <v>6.299850074962528</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>6.366486733268879</v>
+        <v>6.712423724351218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.00609</t>
+          <t>X &lt; -0.006078</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.758213919431881</v>
+        <v>2.271326760261495</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.571545899538975</v>
+        <v>3.885885040836698</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.880195901746468</v>
+        <v>3.561423497084654</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.536910128749227</v>
+        <v>5.294602693625258</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.201119656201953</v>
+        <v>4.553928274456155</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.335953140877535</v>
+        <v>5.175978159524007</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.616137158408982</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.916124765788609</v>
+        <v>1.750394308533842</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.431545596992407</v>
+        <v>2.343439497287712</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.658629920955917</v>
+        <v>1.547388002068374</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.93268956311784</v>
+        <v>1.819623016672708</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.971475704693539</v>
+        <v>4.33373873662002</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.744048234993834</v>
+        <v>5.079311735448314</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.996903007836337</v>
+        <v>5.296193953084973</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5.812693359544873</v>
+        <v>5.079155850269679</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>6.407080281487865</v>
+        <v>5.640459869089341</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>3.429561248775791</v>
+        <v>2.745881782945737</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2.850786895665514</v>
+        <v>2.147881398714368</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>5.436346523035347</v>
+        <v>4.687925021208976</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>5.623192333003374</v>
+        <v>4.90251146626796</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>5.080646165037344</v>
+        <v>4.335066964887226</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>5.478733852917337</v>
+        <v>4.725020722001709</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>7.648943162555781</v>
+        <v>7.294236602628921</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>7.573110909332506</v>
+        <v>7.132097608339457</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.005501</t>
+          <t>X &lt; -0.005489</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3589938315786796</v>
+        <v>0.245252059768184</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.225926475815115</v>
+        <v>2.650860375579477</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.563010735685289</v>
+        <v>2.532529910051529</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.810903019744487</v>
+        <v>4.591642862758455</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.106239998177607</v>
+        <v>3.937296843871245</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.535602355341837</v>
+        <v>4.473018328657204</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.582551309246767</v>
+        <v>2.541572680060852</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.123237502288966</v>
+        <v>1.1002886002886</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.164724684203669</v>
+        <v>0.849429631184826</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.179210582970327</v>
+        <v>0.8109538935412459</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.05956943773068</v>
+        <v>0.7044010293577045</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.324127120896847</v>
+        <v>3.836909983977314</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>6.169468991048596</v>
+        <v>4.615957260465933</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.373586964995717</v>
+        <v>2.852571683881308</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>4.109144454816736</v>
+        <v>2.549205180784135</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>4.30983058935815</v>
+        <v>2.731721320815915</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>2.60111030277438</v>
+        <v>1.112689393939391</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>2.10256881155162</v>
+        <v>0.6010174099899146</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>3.893263342082243</v>
+        <v>2.330631152287204</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>4.867510726853425</v>
+        <v>3.302793354921945</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>4.324964558887395</v>
+        <v>2.735348853541211</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>5.82392174708459</v>
+        <v>4.175337846737435</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>7.279498821771369</v>
+        <v>5.934123847167335</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>7.203666568548094</v>
+        <v>6.150772731665747</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.004911</t>
+          <t>X &lt; -0.0049</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.221288753810512</v>
+        <v>-1.999416851567389</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.076889734566592</v>
+        <v>-1.319397761345336</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4930080401778483</v>
+        <v>-0.4135980360764222</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.198243784075693</v>
+        <v>0.8458516169672023</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2323555039209992</v>
+        <v>-0.9729163996753343</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.73739924611511</v>
+        <v>1.344511033483244</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.3244249211991104</v>
+        <v>-0.6851388799840379</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.9153249850924254</v>
+        <v>-1.298701298701303</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.835376264716182</v>
+        <v>-3.022624240869042</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.326240658701394</v>
+        <v>-2.584107834853818</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.7316681960266465</v>
+        <v>-2.311872820249484</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.156249067192029</v>
+        <v>1.7325328796002</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.635651102900006</v>
+        <v>2.46949261400129</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.491495303376489</v>
+        <v>0.6780486760249644</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.794890467334405</v>
+        <v>1.230462195374486</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1.748251748251754</v>
+        <v>1.483124238885502</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.3322833292229888</v>
+        <v>0.1446759259259167</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.2274426254018067</v>
+        <v>0.01179182076431573</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.725385288377424</v>
+        <v>1.460821949144666</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.553256739371093</v>
+        <v>2.292692344820935</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.331223391917881</v>
+        <v>2.033889818748833</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.896403071534415</v>
+        <v>2.57601124741084</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>4.132416245554928</v>
+        <v>4.054213633923787</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>4.056583992331653</v>
+        <v>4.200716614942969</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.004321</t>
+          <t>X &lt; -0.004312</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.297097113431967</v>
+        <v>-1.269899455383324</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.495206157212593</v>
+        <v>-1.515806291087195</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.010501599556228</v>
+        <v>-2.26544988792827</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2210851692318911</v>
+        <v>-1.090175319059732</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.46238745280278</v>
+        <v>-2.37583446926007</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.244367651500397</v>
+        <v>0.3063516619905329</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.5829900033662128</v>
+        <v>-1.751356612868442</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.916610419095534</v>
+        <v>-2.813852813852819</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.138975479924895</v>
+        <v>-3.696024914269721</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.328777699497003</v>
+        <v>-2.97692489433755</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.05471805733508</v>
+        <v>-2.452164627207956</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.360463937633803</v>
+        <v>1.059132206199536</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.556563084498009</v>
+        <v>1.459391603900272</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.807779722563289</v>
+        <v>0.9586322899419173</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.8857841822386732</v>
+        <v>0.2764779080568616</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.6886143759494701</v>
+        <v>0.3327314218260113</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.0269927534838672</v>
+        <v>-0.2761994949495019</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.07784795033731484</v>
+        <v>0.0959669049394023</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.457304644307335</v>
+        <v>1.573055394711446</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.699559425251607</v>
+        <v>2.797742849871433</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>2.420865500029642</v>
+        <v>2.482823601015959</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>3.136576266852735</v>
+        <v>3.165236836636431</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>4.202607707566976</v>
+        <v>4.418972332015812</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>4.390627697087773</v>
+        <v>4.761883842776861</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.003731</t>
+          <t>X &lt; -0.003723</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.188821527078019</v>
+        <v>-0.8566763148874585</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.411521347679212</v>
+        <v>-1.102583150591329</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.5956558087785098</v>
+        <v>-0.7043846904994311</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.09657898540972809</v>
+        <v>-0.4703406083159223</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.193570248501707</v>
+        <v>-1.778956599654933</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.267682181570457</v>
+        <v>0.6507042790704247</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.02793150567134717</v>
+        <v>-1.177435584401955</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9540911145712982</v>
+        <v>-1.895579168306455</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.4806384898920157</v>
+        <v>-1.767650258622346</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.6056060017816307</v>
+        <v>-1.943867043097875</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.1155636382374254</v>
+        <v>-1.465020458245604</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.41346233628434</v>
+        <v>1.150959570754175</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.370213876339669</v>
+        <v>1.275736874791001</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.285204114363928</v>
+        <v>0.4076681026140889</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.275008980930231</v>
+        <v>0.5519600017207793</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.221447738726361</v>
+        <v>0.7000408800445612</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.208365726544848</v>
+        <v>-0.6435089531680447</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.3347417337808309</v>
+        <v>0.05005322266208623</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.630546721616611</v>
+        <v>1.297573301047528</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.817392531584638</v>
+        <v>1.512159746106512</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.354759970530047</v>
+        <v>1.977773095965453</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3.358827616032393</v>
+        <v>3.142279995497766</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4.281250492661314</v>
+        <v>4.005749191519946</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>5.069349124967211</v>
+        <v>5.083279618718088</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.003142</t>
+          <t>X &lt; -0.003134</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>555</v>
+        <v>579</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.751167398129475</v>
+        <v>-2.59598301038254</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.282219277200674</v>
+        <v>-1.891981839676539</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.199357246527057</v>
+        <v>-2.193486733063565</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.207097874709895</v>
+        <v>-1.576907930144671</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.982100714451526</v>
+        <v>-2.543312356945215</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.08152539596932229</v>
+        <v>-0.8319746058694122</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.112118152034611</v>
+        <v>-1.972479761452732</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.929897942111424</v>
+        <v>-2.450111776536652</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.70855464508881</v>
+        <v>-2.494894438527851</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.121758090909474</v>
+        <v>-2.77281121872128</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.207410678963377</v>
+        <v>-2.845999347467547</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.03182552909942871</v>
+        <v>-0.5319077268093082</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.3475123831066114</v>
+        <v>-0.09239569918236867</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4861457368758551</v>
+        <v>0.1775049544104306</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.5474268997269505</v>
+        <v>0.3589084309018844</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.1171789840854629</v>
+        <v>-0.1160569803302565</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.07124000595501911</v>
+        <v>-0.04722582037997114</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.5433437506554597</v>
+        <v>0.856159504510245</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.7592351315797856</v>
+        <v>1.070621731656018</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.125937056655722</v>
+        <v>1.457919748390303</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.662527579337166</v>
+        <v>1.926744677061386</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.238052413183759</v>
+        <v>2.369716870132009</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.05306766620636</v>
+        <v>3.131486070436289</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.697956133703798</v>
+        <v>4.005616506198642</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.002552</t>
+          <t>X &lt; -0.002545</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>665</v>
+        <v>690</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.450370922955777</v>
+        <v>-2.316075501559368</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.006920484061965</v>
+        <v>-2.487955529132392</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.577822065290384</v>
+        <v>-2.510666160640923</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.268599969792135</v>
+        <v>-1.577658850021514</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.420471285138113</v>
+        <v>-2.867709743744037</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.103007473601963</v>
+        <v>-1.551355847890882</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.341664244890048</v>
+        <v>-1.911655251427945</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.469725539492984</v>
+        <v>-1.781793086140915</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.878688808028727</v>
+        <v>-2.378501857616236</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.20115403361477</v>
+        <v>-2.594843207908035</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.927094391452847</v>
+        <v>-2.322608193303701</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.2538918429488817</v>
+        <v>-0.5702046405286154</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4247478919968017</v>
+        <v>0.1989612130350977</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9544197663009655</v>
+        <v>0.8202923689933002</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.4464266188705466</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.1603876603876557</v>
+        <v>-0.02519567523151522</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.00599550293517126</v>
+        <v>0.1607789855072355</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.351605249564436</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.318247381239516</v>
+        <v>1.691632469810258</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.655243341357689</v>
+        <v>2.051146451101133</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.563147623842106</v>
+        <v>1.918484558416047</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.730025589367457</v>
+        <v>2.133177108924521</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.154876241699135</v>
+        <v>2.521739130434788</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.229419928325491</v>
+        <v>2.794382744840973</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.001962</t>
+          <t>X &lt; -0.001957</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>764</v>
+        <v>794</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.05869963607104</v>
+        <v>-2.978009413179606</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.068888160486438</v>
+        <v>-2.657880297482805</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.495355023069578</v>
+        <v>-2.46461131350479</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.321402175060712</v>
+        <v>-1.479458579879513</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.146392654363254</v>
+        <v>-3.266351732573298</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.978546266705408</v>
+        <v>-2.101861451512242</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.158191332603586</v>
+        <v>-2.393165126213482</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.045268487917284</v>
+        <v>-2.068362647707737</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.00378130600258</v>
+        <v>-2.192322906789379</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.99442840316032</v>
+        <v>-2.106762311328609</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.850746857478192</v>
+        <v>-1.960471881107154</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.9560933926080608</v>
+        <v>-0.9776079917497285</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.1371721806922679</v>
+        <v>0.1745024096911791</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.437605690164844</v>
+        <v>0.5559912701724272</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.300974778503452</v>
+        <v>0.503559810201736</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.6691754573110487</v>
+        <v>-0.3205265991901953</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.1512021118895746</v>
+        <v>0.2053159109991611</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.6566038596477881</v>
+        <v>1.205933065283403</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.654763819450871</v>
+        <v>2.176062798726399</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.711231532939102</v>
+        <v>2.264704659402518</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.770535168044269</v>
+        <v>2.201038495553263</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.905955610498722</v>
+        <v>2.377765142363728</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.392249780257572</v>
+        <v>2.74734421202497</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.447307579390326</v>
+        <v>2.963038970884121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001372</t>
+          <t>X &lt; -0.001368</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>902</v>
+        <v>938</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.531676807755112</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.920979103038619</v>
+        <v>-3.629128675397887</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.225459153372945</v>
+        <v>-3.128334048684778</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.238316585951026</v>
+        <v>-2.174501004024393</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.392212014206294</v>
+        <v>-3.352552610157318</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.159065613576971</v>
+        <v>-2.129520923135779</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.772644675870481</v>
+        <v>-1.85850485434505</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.210069844193718</v>
+        <v>-2.163425297753669</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.107882759689637</v>
+        <v>-2.248716004274243</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.378950352535668</v>
+        <v>-2.511718458981854</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.822685346646452</v>
+        <v>-2.02626382817283</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.9976819907125432</v>
+        <v>-1.130137893518331</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3548396425576215</v>
+        <v>-0.4326632732292239</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.02404213931325927</v>
+        <v>-0.04123848604827174</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.09044149467349882</v>
+        <v>0.1294855968854378</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.3085490668272115</v>
+        <v>-0.1620888491136654</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.2197854518244498</v>
+        <v>0.3736895877754094</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.329072783323362</v>
+        <v>1.626732987944294</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.207215819876829</v>
+        <v>2.480854063704143</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.351740943932647</v>
+        <v>2.588830700660786</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.988019398271412</v>
+        <v>2.127996007382393</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.091394126990586</v>
+        <v>2.26605310163179</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>2.434622169712078</v>
+        <v>2.509687586910168</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>2.247925171477718</v>
+        <v>2.45415840072306</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0007826</t>
+          <t>X &lt; -0.0007792</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1070</v>
+        <v>1112</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.214904151150456</v>
+        <v>-2.288146441372248</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.870651536091174</v>
+        <v>-2.577771231975902</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.23391945850863</v>
+        <v>-1.991163033749139</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.975305467340377</v>
+        <v>-1.817121329024602</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.445766954187832</v>
+        <v>-2.403993760009293</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.561927736206329</v>
+        <v>-1.4377076360256</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.358193262344138</v>
+        <v>-1.243581015164786</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.492248062015499</v>
+        <v>-1.27871728591154</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.862407466446179</v>
+        <v>-1.870212836659078</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.841796531400114</v>
+        <v>-1.856911813892808</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.701241797912225</v>
+        <v>-1.674604856842436</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.277313033656327</v>
+        <v>-1.321690408436034</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.5417390410328835</v>
+        <v>-0.5480933172537021</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.5769443115315198</v>
+        <v>-0.5265432060249466</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.1198459734243471</v>
+        <v>-0.03963283970856679</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.08307986932521771</v>
+        <v>0.07203089134131346</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.03112340035473693</v>
+        <v>0.1480065947242153</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.793403925563851</v>
+        <v>1.094259180210102</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.530692384382192</v>
+        <v>1.848289752679612</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.960576607584805</v>
+        <v>2.152804255292551</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.568325215226594</v>
+        <v>1.675287811465772</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.643054430126071</v>
+        <v>1.779981404618404</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.508161415417753</v>
+        <v>1.573975602127</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.396028037383182</v>
+        <v>1.501764665391491</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0001928</t>
+          <t>X &lt; -0.0001905</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1282</v>
+        <v>1323</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.794693267278127</v>
+        <v>-1.810699017267225</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.243522295153603</v>
+        <v>-2.01762173261627</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.946770849872863</v>
+        <v>-1.800392069929273</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.155895361134462</v>
+        <v>-1.975252506023708</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.221646712062039</v>
+        <v>-3.041097370172515</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.530247521531663</v>
+        <v>-2.315100959462079</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.101465777489118</v>
+        <v>-1.976396123622237</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.182503282433132</v>
+        <v>-1.978973407544842</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.020936318697281</v>
+        <v>-1.92663028773223</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.131370849966359</v>
+        <v>-2.042409674108036</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.968996758936605</v>
+        <v>-1.921346239246716</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.359605003743503</v>
+        <v>-2.27351398358951</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.042004574755673</v>
+        <v>-1.952276093481707</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.564325687227104</v>
+        <v>-1.444652256199774</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.13551246306853</v>
+        <v>-0.9930197900122693</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.084603801995108</v>
+        <v>-0.8852305104216285</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.063241435866992</v>
+        <v>-0.8379393424036223</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.7022436303713988</v>
+        <v>-0.366137128593202</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.2851042221120892</v>
+        <v>-0.0005033217044143612</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.1033025981261204</v>
+        <v>0.3652547030975768</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.4708318809545133</v>
+        <v>-0.2777755881546611</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.1110256368288773</v>
+        <v>0.1005766291190753</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.4914121214534788</v>
+        <v>-0.3360609944460862</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.209086634493417</v>
+        <v>-0.04468524950651442</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0003969</t>
+          <t>X &lt; 0.0003983</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1504</v>
+        <v>1552</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.572560836347272</v>
+        <v>-1.519505340827365</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.07023626394998</v>
+        <v>-1.860512998261768</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.093458871397914</v>
+        <v>-1.859947922940769</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.916070664466041</v>
+        <v>-1.645925874810288</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.34783840737817</v>
+        <v>-2.079893735457134</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.927595179748891</v>
+        <v>-1.566110068718622</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.070441802935903</v>
+        <v>-1.716862184044111</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.718721237037492</v>
+        <v>-1.313019740854799</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.508516655678356</v>
+        <v>-1.249523820861405</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.51804027256177</v>
+        <v>-1.27237943979209</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.20661184677995</v>
+        <v>-1.000144425187756</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.712493301550346</v>
+        <v>-1.47002534873122</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.607098646798789</v>
+        <v>-1.360690662058282</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.761996186382362</v>
+        <v>-1.480058744109947</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.692144778469867</v>
+        <v>-1.389017249706335</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.627208551430925</v>
+        <v>-1.343177148412458</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.827307025271395</v>
+        <v>-1.511490549828189</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.695209777383042</v>
+        <v>-1.386642696226893</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.374604516383762</v>
+        <v>-1.17218046908112</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.215531943210699</v>
+        <v>-1.086460003403587</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.586817204954841</v>
+        <v>-1.589471515093599</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.291971634768572</v>
+        <v>-1.342469088595266</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.709435700948177</v>
+        <v>-1.678731510533389</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.347807715251534</v>
+        <v>-1.260973597606352</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.0009867</t>
+          <t>X &lt; 0.000987</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1748</v>
+        <v>1805</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.8159883563698216</v>
+        <v>-0.6696985513150224</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.686194855817959</v>
+        <v>-1.439169274151674</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.793733458550328</v>
+        <v>-1.503404656856482</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.287887302836161</v>
+        <v>-1.014711214818647</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.762500703085912</v>
+        <v>-1.42613817072656</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.261256960756398</v>
+        <v>-0.7958056451529174</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.002018476672859</v>
+        <v>-1.480084333285916</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.908678389109475</v>
+        <v>-1.34179148029564</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.77898638142505</v>
+        <v>-1.380067556761119</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.952523802020309</v>
+        <v>-1.566700769431982</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.987495701854151</v>
+        <v>-1.682277389176683</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.348226086231399</v>
+        <v>-2.069662667747693</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.472688793835793</v>
+        <v>-2.242726530350822</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.433829040274539</v>
+        <v>-2.269353943584484</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.750481159710539</v>
+        <v>-2.619098353170365</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-2.692931593842758</v>
+        <v>-2.556409292799465</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.452616955677293</v>
+        <v>-2.272478070175445</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-2.581886965569744</v>
+        <v>-2.349960513287186</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.21931756533855</v>
+        <v>-2.080096624091539</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.113936797685469</v>
+        <v>-1.976313503132289</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.566710389511051</v>
+        <v>-2.599159666562876</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.381252606121265</v>
+        <v>-2.286510554169134</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.588457220601555</v>
+        <v>-2.541491027339511</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.288396351504517</v>
+        <v>-2.14961340113036</v>
       </c>
     </row>
     <row r="24">
@@ -7304,981 +7304,981 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2058</v>
+        <v>2112</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.166075369078293</v>
+        <v>-1.112235033915219</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.283316219474088</v>
+        <v>-1.144529786666219</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.012488559658365</v>
+        <v>-0.8627836411429897</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5443063161554136</v>
+        <v>-0.3898831726428185</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.045921395990078</v>
+        <v>-0.828445687828733</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.8322613437767004</v>
+        <v>-0.5508485329580068</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.336526577101779</v>
+        <v>-1.035848478997792</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.587876477316051</v>
+        <v>-1.219787157287158</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.423023301711986</v>
+        <v>-1.139206732451534</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.589828422289152</v>
+        <v>-1.27237943979209</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.433360677052775</v>
+        <v>-1.189538364581701</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.636578877809839</v>
+        <v>-1.418771834204513</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.814151229454282</v>
+        <v>-1.634042739534067</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.055843882260568</v>
+        <v>-1.929625285815661</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-2.105690084189547</v>
+        <v>-2.043597849518896</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.870471413065793</v>
+        <v>-1.861081709487109</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-2.024921612727717</v>
+        <v>-1.964962121212118</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-2.004966438402597</v>
+        <v>-1.861103802131304</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.906523681631398</v>
+        <v>-1.930732484076437</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.982730228720634</v>
+        <v>-1.952888463259882</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.303382661902155</v>
+        <v>-2.330939025246671</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-2.254206836357042</v>
+        <v>-2.169359122959534</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-2.097425225908687</v>
+        <v>-2.209815546772063</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.048110632771127</v>
+        <v>-2.08786363197062</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.002166</t>
+          <t>X &lt; 0.002164</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2369</v>
+        <v>2419</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.048873869284805</v>
+        <v>-1.028199687714881</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.278007851555934</v>
+        <v>-1.211213976185597</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.229542542402733</v>
+        <v>-1.124085751514635</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5803433176351618</v>
+        <v>-0.4561003556409773</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9766253087491918</v>
+        <v>-0.8327404406169023</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.101562867040556</v>
+        <v>-0.9008880210855779</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.431276069623422</v>
+        <v>-1.177435584401955</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.770025839793277</v>
+        <v>-1.459465618208903</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.453557300682448</v>
+        <v>-1.207518519190366</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.909296922622111</v>
+        <v>-1.590176049961585</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.905536309441359</v>
+        <v>-1.607316810470927</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.950821868312346</v>
+        <v>-1.635862386273352</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.705870120974161</v>
+        <v>-1.469233213934963</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.818719072411653</v>
+        <v>-1.59344908603363</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-2.032124261698826</v>
+        <v>-1.862209503470567</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.834021748830338</v>
+        <v>-1.714299449099023</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.649068652128982</v>
+        <v>-1.57014348215516</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.813717968390357</v>
+        <v>-1.74436698376158</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.573439587953771</v>
+        <v>-1.61258354950543</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.952156726219371</v>
+        <v>-1.894069861784182</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.96462129178515</v>
+        <v>-2.048120398716804</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-2.058230373187598</v>
+        <v>-2.040604127782466</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-2.265668791770615</v>
+        <v>-2.334381796286642</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-2.275066276633929</v>
+        <v>-2.289823808352047</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.002756</t>
+          <t>X &lt; 0.002753</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2622</v>
+        <v>2667</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.164476603034991</v>
+        <v>-1.131411774839577</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.9877267862144663</v>
+        <v>-0.9463495697980093</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.7030867746606688</v>
+        <v>-0.6100065658182885</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.6761806290064598</v>
+        <v>-0.5832346549334346</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.293890671280643</v>
+        <v>-1.175134092221249</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.654209145493283</v>
+        <v>-1.447138293746612</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.799169874809479</v>
+        <v>-1.547463050038949</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.056438104977346</v>
+        <v>-1.756805579894042</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.652694896027995</v>
+        <v>-1.383245829837101</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.683717021488825</v>
+        <v>-1.391895750253276</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.691868653380801</v>
+        <v>-1.419623240335866</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.797462748706579</v>
+        <v>-1.508728629377842</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.607953248186298</v>
+        <v>-1.311284788823365</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.54119895272202</v>
+        <v>-1.297051658655413</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.569215020488308</v>
+        <v>-1.416776344252511</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.484906095172249</v>
+        <v>-1.380406708634951</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.444618290774855</v>
+        <v>-1.371801181102363</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.603431979445403</v>
+        <v>-1.504685286263964</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.555753380085186</v>
+        <v>-1.515194937633375</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.5372484649955</v>
+        <v>-1.525580371089582</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.562549501855017</v>
+        <v>-1.605585802354085</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.692402431905236</v>
+        <v>-1.68074832430937</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.776970148962995</v>
+        <v>-1.812066969889621</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.716313971641824</v>
+        <v>-1.711738772578045</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.003346</t>
+          <t>X &lt; 0.003342</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2830</v>
+        <v>2868</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5388492164813883</v>
+        <v>-0.6055394844540061</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4342494377284893</v>
+        <v>-0.4505641618673195</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4504721435556718</v>
+        <v>-0.4345320135321344</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.337123296044993</v>
+        <v>-0.2772443391141266</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.8288318192471564</v>
+        <v>-0.7771817393856182</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.9383426150200194</v>
+        <v>-0.8447836465263805</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.91811108161086</v>
+        <v>-0.8196255087235471</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.176600369347426</v>
+        <v>-1.035441523246405</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.9044808566678739</v>
+        <v>-0.7834907190586335</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.094984573014919</v>
+        <v>-0.9324212807962766</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.117456051037152</v>
+        <v>-0.9391262940859448</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.129961438230296</v>
+        <v>-0.9367682206632395</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.965924723596622</v>
+        <v>-0.796430212590991</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9552363687072898</v>
+        <v>-0.8005917496168564</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.029212458036575</v>
+        <v>-0.8899985722271566</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.083509513742072</v>
+        <v>-0.9214421126822501</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.9853553826702068</v>
+        <v>-0.8509850069735023</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.9637439501289151</v>
+        <v>-0.8443990981881058</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.220958491299697</v>
+        <v>-1.152949423343586</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.225265961169967</v>
+        <v>-1.18243550269186</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.11194186734339</v>
+        <v>-1.191999948284582</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.096426133159198</v>
+        <v>-1.197427463266365</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.225050084182676</v>
+        <v>-1.337335516342243</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.386244674878633</v>
+        <v>-1.464607007144956</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.003935</t>
+          <t>X &lt; 0.003931</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2983</v>
+        <v>3018</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.6468351373840591</v>
+        <v>-0.6713395993977258</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2651413826636499</v>
+        <v>-0.2725216787038747</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1872781139419359</v>
+        <v>-0.1555130025620528</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.05055919690065735</v>
+        <v>0.1952257681253045</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3997625360806083</v>
+        <v>-0.2601635498878991</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.727270650244229</v>
+        <v>-0.5145849771279174</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.5807032839290898</v>
+        <v>-0.4316115431233669</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6400195413975212</v>
+        <v>-0.4533306220372069</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.64633570776369</v>
+        <v>-0.4721916110188147</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.8998527323134624</v>
+        <v>-0.6537928790506129</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.9738714756131017</v>
+        <v>-0.7269656172407366</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.8329851265496799</v>
+        <v>-0.5730839955530911</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6010273822754755</v>
+        <v>-0.363472801745587</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.5686535910523816</v>
+        <v>-0.3468062009270412</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.5721052820142845</v>
+        <v>-0.3998215099644113</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.5596334457919241</v>
+        <v>-0.3683188156480597</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.4731793240657467</v>
+        <v>-0.2735237306843317</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.4578693304019481</v>
+        <v>-0.2739575047201015</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.5902876598256483</v>
+        <v>-0.4568462709518144</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.6180711515751511</v>
+        <v>-0.5402730709259416</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.5381499228673619</v>
+        <v>-0.5116910822404535</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.6611281744390354</v>
+        <v>-0.6530787697586504</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.8359621142443387</v>
+        <v>-0.8536947160735622</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.925601382914401</v>
+        <v>-0.9633606498632687</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.004525</t>
+          <t>X &lt; 0.004519</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3089</v>
+        <v>3122</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4596131802700114</v>
+        <v>-0.4814022383146792</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5522873640479347</v>
+        <v>-0.582791937020211</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.4940288129028048</v>
+        <v>-0.4484605948700562</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.2565423002941145</v>
+        <v>-0.1616432701957251</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5421815325968637</v>
+        <v>-0.4514178896710774</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.7234418653536281</v>
+        <v>-0.5642192660700118</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5116326679170697</v>
+        <v>-0.3832022255447214</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.7072239074261262</v>
+        <v>-0.5423361128059199</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.7441457598258836</v>
+        <v>-0.5882205276929611</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.9509834634313066</v>
+        <v>-0.7587081893923511</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.077598861106246</v>
+        <v>-0.8841815333131535</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>-0.6947263796590448</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.7977649434192671</v>
+        <v>-0.5616184971098264</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.8386608263924131</v>
+        <v>-0.6178525585429355</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.7032059058426725</v>
+        <v>-0.500006940427987</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.7677273216504759</v>
+        <v>-0.5787029216083326</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.6888854245038942</v>
+        <v>-0.522583333333337</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.6777601416749448</v>
+        <v>-0.5274674384949307</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.8306371205861609</v>
+        <v>-0.6970052113491647</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.7864806328590106</v>
+        <v>-0.7064187662901844</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.695611782394657</v>
+        <v>-0.6338632676709111</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.7199686943035388</v>
+        <v>-0.6902191314955957</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.8794084992795206</v>
+        <v>-0.8760528477355862</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.065706849447686</v>
+        <v>-1.083566173076747</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.005115</t>
+          <t>X &lt; 0.005108</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3157</v>
+        <v>3189</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4961930253816504</v>
+        <v>-0.5463720464626647</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.4682316500642543</v>
+        <v>-0.4947464891969204</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5678279828391979</v>
+        <v>-0.5460384089914996</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3507077766042741</v>
+        <v>-0.2779291459888142</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.731908863382138</v>
+        <v>-0.6299380046135994</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7793582745794225</v>
+        <v>-0.6745419884873556</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6201487785730819</v>
+        <v>-0.5455840656324753</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.8175448368868103</v>
+        <v>-0.7078696162212026</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.8843464202437161</v>
+        <v>-0.7501076692285693</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.9772243328638766</v>
+        <v>-0.8400633208562525</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.063707345100497</v>
+        <v>-0.9257862536160602</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9458902471593404</v>
+        <v>-0.7775876386631211</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.8515283842794759</v>
+        <v>-0.6528966925985458</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.8331587816186001</v>
+        <v>-0.6505041876156241</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.7147471891762862</v>
+        <v>-0.5494505494505475</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.7019244578486337</v>
+        <v>-0.5520563050669764</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.596028771655476</v>
+        <v>-0.4679667919799542</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.6505983451146591</v>
+        <v>-0.5381942555375474</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.7006595712537802</v>
+        <v>-0.6056869156098159</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.6533924060632472</v>
+        <v>-0.5790703953628693</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.6394030280756269</v>
+        <v>-0.5826051223074984</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.6965060769302909</v>
+        <v>-0.6393397977741202</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.8782607489726004</v>
+        <v>-0.8474853482349687</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.9671524338438005</v>
+        <v>-0.9599630361725602</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.005705</t>
+          <t>X &lt; 0.005697</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3215</v>
+        <v>3244</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4907544636481447</v>
+        <v>-0.5220808832777166</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.592862095285021</v>
+        <v>-0.6290243613604787</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5001695368325514</v>
+        <v>-0.4866152078969108</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4851750328057491</v>
+        <v>-0.4483984341889169</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.741917446618487</v>
+        <v>-0.6763092818626077</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.6923714677570629</v>
+        <v>-0.6252617696229024</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.6736075743581367</v>
+        <v>-0.6353579162245921</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.748670222337374</v>
+        <v>-0.6772439470657119</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.7515864734960545</v>
+        <v>-0.6550091619105913</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.8256689170333402</v>
+        <v>-0.7265614816125066</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.9056268272343431</v>
+        <v>-0.8059734008875381</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.8258769051725636</v>
+        <v>-0.6959571488898249</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.8153638874826186</v>
+        <v>-0.6853242527269359</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.7392739273927376</v>
+        <v>-0.6078328541094393</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.7278556037987727</v>
+        <v>-0.6126473345166588</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.6735443168890285</v>
+        <v>-0.574742330475317</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.5719567509947439</v>
+        <v>-0.49389367816093</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.5342852979218833</v>
+        <v>-0.472836896623015</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.5174081500681851</v>
+        <v>-0.4738919108565511</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.4675691262823634</v>
+        <v>-0.4440345298369763</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.463552786947794</v>
+        <v>-0.4391432183946549</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.5209390930878257</v>
+        <v>-0.4961459375005006</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.663316628536144</v>
+        <v>-0.6349567897099178</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.7830100579933372</v>
+        <v>-0.7482109398210071</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.006294</t>
+          <t>X &lt; 0.006286</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3259</v>
+        <v>3283</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.197824566204666</v>
+        <v>-0.2415970491281598</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.3029631376275574</v>
+        <v>-0.3501815492734224</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3831551559347233</v>
+        <v>-0.4371670596454464</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3473960043482265</v>
+        <v>-0.3764604192278256</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.5746510281536032</v>
+        <v>-0.5746203878761875</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.5232088773248762</v>
+        <v>-0.5222252812360892</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4844883877141939</v>
+        <v>-0.5117150516249396</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.6538256701579925</v>
+        <v>-0.6478835613888734</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4728541401293072</v>
+        <v>-0.442174939108277</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4951400452909738</v>
+        <v>-0.4619482220575009</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.5702363108783857</v>
+        <v>-0.5369001967551839</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.5257779142846672</v>
+        <v>-0.4923903115946331</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.5610085066036419</v>
+        <v>-0.5261169773529843</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.5194309580850955</v>
+        <v>-0.4830419778193118</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.5169602686289494</v>
+        <v>-0.478332974491245</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.4553106825834092</v>
+        <v>-0.4340605858418982</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3568290484993071</v>
+        <v>-0.3554592457420966</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.2903843663914927</v>
+        <v>-0.3058615990788809</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.2707497040811049</v>
+        <v>-0.3042947490620591</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2802809049235222</v>
+        <v>-0.315224364099727</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.1916114270542835</v>
+        <v>-0.2257902305437085</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.2491634134984864</v>
+        <v>-0.2829435978453745</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.4165062021405177</v>
+        <v>-0.4475983689032432</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.5662159856386211</v>
+        <v>-0.5918361164868102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.006884</t>
+          <t>X &lt; 0.006874</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3292</v>
+        <v>3317</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1566842175043632</v>
+        <v>-0.1593931951764702</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2942720711058655</v>
+        <v>-0.2994649804062632</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.357802332983006</v>
+        <v>-0.3697705057300098</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.4200752411250832</v>
+        <v>-0.4363490733845126</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.5578268970794369</v>
+        <v>-0.5754565897454995</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.5050285174606941</v>
+        <v>-0.5218705905195691</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4743871763437113</v>
+        <v>-0.4905481684967086</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5843480217091681</v>
+        <v>-0.598631291700606</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4349862606067916</v>
+        <v>-0.4538189409713098</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4345053522655462</v>
+        <v>-0.4524304755170903</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4153254364161043</v>
+        <v>-0.4333276083709379</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4043146628632286</v>
+        <v>-0.4224908735010473</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4503779150091134</v>
+        <v>-0.4685415740328978</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5022458635930178</v>
+        <v>-0.5189478395769029</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.5063741067262981</v>
+        <v>-0.5220971388645523</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4393939393939377</v>
+        <v>-0.4543119441647221</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3735443885780541</v>
+        <v>-0.3901549338146921</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.24817585355202</v>
+        <v>-0.2646206133369517</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.196233432604366</v>
+        <v>-0.2130172522883598</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1430962603799699</v>
+        <v>-0.1613877515355853</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.151753924139868</v>
+        <v>-0.1689957977913963</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.1791188564465216</v>
+        <v>-0.1961869827566645</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.3116453614280204</v>
+        <v>-0.3264931729433656</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.3998293796345749</v>
+        <v>-0.4105824541995347</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.007474</t>
+          <t>X &lt; 0.007463</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3325</v>
+        <v>3349</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1462234575179906</v>
+        <v>-0.1618438099611339</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2558748828006046</v>
+        <v>-0.2732561980476333</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.303063164040509</v>
+        <v>-0.3251267754983402</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3119482508085767</v>
+        <v>-0.3373217612195276</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4516219025635451</v>
+        <v>-0.4776963181527947</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3974673331128216</v>
+        <v>-0.4230990674601856</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.4046410457483631</v>
+        <v>-0.4293126437656483</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.5461740322838864</v>
+        <v>-0.5689671068571585</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4278067882844283</v>
+        <v>-0.4540330575335076</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4349673617677112</v>
+        <v>-0.4602325471367266</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.5031419788844929</v>
+        <v>-0.5279552520765094</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4650559588178282</v>
+        <v>-0.4901301285433206</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5517681924329523</v>
+        <v>-0.5761423066336278</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.5453708789169696</v>
+        <v>-0.5689237106715481</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.6459675149153128</v>
+        <v>-0.6381177206543143</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.6038103810381017</v>
+        <v>-0.5954512087694823</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.5399886564943728</v>
+        <v>-0.5329385180770743</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4169507576586398</v>
+        <v>-0.4099115517587251</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3634343004421652</v>
+        <v>-0.3567976979323504</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.2789828644215433</v>
+        <v>-0.2738318292189064</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.2929753260308416</v>
+        <v>-0.2868179216088649</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.3509206897658999</v>
+        <v>-0.3443442020404035</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.4794606528523317</v>
+        <v>-0.4711226476314039</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.5074221769376663</v>
+        <v>-0.4962815676728169</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.008064</t>
+          <t>X &lt; 0.008052</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3355</v>
+        <v>3379</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1180525604420311</v>
+        <v>-0.1034732889571544</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.140859327831528</v>
+        <v>-0.1572486476133506</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1707519655521068</v>
+        <v>-0.1902864892354543</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1858562395147771</v>
+        <v>-0.2075627859617626</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2383210627612939</v>
+        <v>-0.2608054266265469</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2422164045648785</v>
+        <v>-0.2641160412413726</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.167180152256492</v>
+        <v>-0.1889123825796872</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3098590577635534</v>
+        <v>-0.3299564124306471</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2217796733747832</v>
+        <v>-0.2443008379139471</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2060155291262973</v>
+        <v>-0.2279497315692751</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2710737627481308</v>
+        <v>-0.2925972553764353</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2654418544988957</v>
+        <v>-0.2869740941975323</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.3316234526098398</v>
+        <v>-0.3525329513871043</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3271887367042723</v>
+        <v>-0.3475096845388066</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.4029661746363971</v>
+        <v>-0.4220659723052052</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.4747519801043438</v>
+        <v>-0.4928405064917101</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.4424005433193017</v>
+        <v>-0.461305128962394</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3511206837476308</v>
+        <v>-0.3700671430739604</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.3258967629046339</v>
+        <v>-0.3450619489378184</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2405196440153006</v>
+        <v>-0.2609254171917428</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1698837994811555</v>
+        <v>-0.1901211032711458</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.2279524656897465</v>
+        <v>-0.2477752720278517</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.3230557754713246</v>
+        <v>-0.3416516593774048</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.3513987353232082</v>
+        <v>-0.3679884223425276</v>
       </c>
     </row>
   </sheetData>
